--- a/H2coco/PO.xlsx
+++ b/H2coco/PO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leo/Github/XeroAPI/H2coco/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B4A7E48-D11E-AA44-B8F7-E493087C5EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C25829-AFCB-0D43-B330-D86C0BAD0C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19780" yWindow="-25520" windowWidth="38400" windowHeight="20980" xr2:uid="{4B9AE9D0-272D-6147-B144-109295B6F9E3}"/>
   </bookViews>
@@ -50,13 +50,13 @@
     <t>Amount</t>
   </si>
   <si>
-    <t>4844/1</t>
+    <t>Extra4858</t>
   </si>
   <si>
-    <t>4870/1</t>
+    <t>Extra4859</t>
   </si>
   <si>
-    <t>DEC25</t>
+    <t>Extra4976</t>
   </si>
 </sst>
 </file>
@@ -110,16 +110,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -475,43 +472,43 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3">
+        <v>45854</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.66977399999999998</v>
+      </c>
+      <c r="D2" s="5">
+        <v>11025</v>
+      </c>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
         <v>4230</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B3" s="3">
         <v>45848</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C3" s="2">
         <v>0.62860000000000005</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D3" s="5">
         <v>7603.2</v>
       </c>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
-        <v>1</v>
-      </c>
-      <c r="B3" s="7">
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3">
         <v>45854</v>
       </c>
-      <c r="C3" s="6">
-        <v>0.65175000000000005</v>
-      </c>
-      <c r="D3" s="5">
-        <v>11025</v>
-      </c>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
-        <v>2</v>
-      </c>
-      <c r="B4" s="7">
-        <v>45854</v>
-      </c>
-      <c r="C4" s="6">
+      <c r="C4" s="2">
         <v>0.65176000000000001</v>
       </c>
       <c r="D4" s="5">
@@ -520,179 +517,179 @@
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
-        <v>4358</v>
-      </c>
-      <c r="B5" s="7">
-        <v>45890</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0.6573</v>
+      <c r="A5" s="2">
+        <v>4354</v>
+      </c>
+      <c r="B5" s="3">
+        <v>45898</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.65766999999999998</v>
       </c>
       <c r="D5" s="5">
+        <v>4374</v>
+      </c>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3">
+        <v>45923</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.66078999999999999</v>
+      </c>
+      <c r="D6" s="5">
+        <v>10350</v>
+      </c>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3">
+        <v>45923</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.66080000000000005</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1040</v>
+      </c>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3">
+        <v>45923</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.66078999999999999</v>
+      </c>
+      <c r="D8" s="5">
+        <v>10350</v>
+      </c>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3">
+        <v>45923</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.66080000000000005</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1040</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3">
+        <v>45925</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.65937000000000001</v>
+      </c>
+      <c r="D10" s="5">
+        <v>14204.8</v>
+      </c>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>4504</v>
+      </c>
+      <c r="B11" s="3">
+        <v>45932</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.66049999999999998</v>
+      </c>
+      <c r="D11" s="5">
         <v>3801.6</v>
       </c>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
-        <v>4354</v>
-      </c>
-      <c r="B6" s="7">
-        <v>45898</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0.65766999999999998</v>
-      </c>
-      <c r="D6" s="5">
-        <v>4374</v>
-      </c>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="6">
-        <v>4447</v>
-      </c>
-      <c r="B7" s="7">
-        <v>45918</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.66420000000000001</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>4550</v>
+      </c>
+      <c r="B12" s="3">
+        <v>45946</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.65949000000000002</v>
+      </c>
+      <c r="D12" s="5">
         <v>3801.6</v>
       </c>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="6">
-        <v>4465</v>
-      </c>
-      <c r="B8" s="7">
-        <v>45918</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0.66420000000000001</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>4571</v>
+      </c>
+      <c r="B13" s="3">
+        <v>45953</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.66034000000000004</v>
+      </c>
+      <c r="D13" s="5">
         <v>3801.6</v>
       </c>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="6">
-        <v>4530</v>
-      </c>
-      <c r="B9" s="7">
-        <v>45918</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0.66420000000000001</v>
-      </c>
-      <c r="D9" s="5">
-        <v>3801.6</v>
-      </c>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="6">
-        <v>3</v>
-      </c>
-      <c r="B10" s="7">
-        <v>45923</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0.66078999999999999</v>
-      </c>
-      <c r="D10" s="5">
-        <v>10350</v>
-      </c>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="6">
-        <v>4</v>
-      </c>
-      <c r="B11" s="7">
-        <v>45923</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0.66080000000000005</v>
-      </c>
-      <c r="D11" s="5">
-        <v>1040</v>
-      </c>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="6">
-        <v>5</v>
-      </c>
-      <c r="B12" s="7">
-        <v>45923</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0.66078999999999999</v>
-      </c>
-      <c r="D12" s="5">
-        <v>10350</v>
-      </c>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="6">
-        <v>6</v>
-      </c>
-      <c r="B13" s="7">
-        <v>45923</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0.66080000000000005</v>
-      </c>
-      <c r="D13" s="5">
-        <v>1040</v>
-      </c>
       <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="6">
-        <v>7</v>
-      </c>
-      <c r="B14" s="7">
-        <v>45925</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0.65937000000000001</v>
+      <c r="A14" s="2">
+        <v>4668</v>
+      </c>
+      <c r="B14" s="3">
+        <v>45960</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.65659999999999996</v>
       </c>
       <c r="D14" s="5">
-        <v>14204.8</v>
+        <v>3864</v>
       </c>
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="6">
-        <v>4504</v>
-      </c>
-      <c r="B15" s="7">
-        <v>45932</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0.66049999999999998</v>
+      <c r="A15" s="2">
+        <v>8</v>
+      </c>
+      <c r="B15" s="3">
+        <v>45966</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.65044999999999997</v>
       </c>
       <c r="D15" s="5">
-        <v>3801.6</v>
+        <v>20700</v>
       </c>
       <c r="F15" s="2"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="6">
-        <v>4554</v>
-      </c>
-      <c r="B16" s="7">
-        <v>45939</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.65790000000000004</v>
+      <c r="A16" s="2">
+        <v>4692</v>
+      </c>
+      <c r="B16" s="3">
+        <v>45974</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.65493000000000001</v>
       </c>
       <c r="D16" s="5">
         <v>3801.6</v>
@@ -700,591 +697,591 @@
       <c r="F16" s="2"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="6">
-        <v>4550</v>
-      </c>
-      <c r="B17" s="7">
-        <v>45946</v>
-      </c>
-      <c r="C17" s="6">
+      <c r="A17" s="2">
+        <v>4687</v>
+      </c>
+      <c r="B17" s="3">
+        <v>45981</v>
+      </c>
+      <c r="C17" s="2">
         <v>0.65949000000000002</v>
       </c>
       <c r="D17" s="5">
-        <v>3801.6</v>
+        <v>3941.82</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="6">
-        <v>4552</v>
-      </c>
-      <c r="B18" s="7">
-        <v>45946</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.65949000000000002</v>
+      <c r="A18" s="2">
+        <v>4596</v>
+      </c>
+      <c r="B18" s="3">
+        <v>45989</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0.65205000000000002</v>
       </c>
       <c r="D18" s="5">
         <v>3801.6</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="6">
-        <v>4675</v>
-      </c>
-      <c r="B19" s="7">
-        <v>45946</v>
-      </c>
-      <c r="C19" s="6">
-        <v>0.65949000000000002</v>
+      <c r="A19" s="2">
+        <v>4639</v>
+      </c>
+      <c r="B19" s="3">
+        <v>45989</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0.65205000000000002</v>
       </c>
       <c r="D19" s="5">
-        <v>4101.45</v>
+        <v>4114.95</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="6">
-        <v>4466</v>
-      </c>
-      <c r="B20" s="7">
-        <v>45953</v>
-      </c>
-      <c r="C20" s="6">
-        <v>0.66034000000000004</v>
+      <c r="A20" s="2">
+        <v>4704</v>
+      </c>
+      <c r="B20" s="3">
+        <v>45989</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0.65205000000000002</v>
       </c>
       <c r="D20" s="5">
         <v>3801.6</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="6">
-        <v>4569</v>
-      </c>
-      <c r="B21" s="7">
-        <v>45953</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0.66034000000000004</v>
+      <c r="A21" s="2">
+        <v>4723</v>
+      </c>
+      <c r="B21" s="3">
+        <v>45989</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0.65205000000000002</v>
       </c>
       <c r="D21" s="5">
-        <v>3801.6</v>
+        <v>3858.3</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="6">
-        <v>4571</v>
-      </c>
-      <c r="B22" s="7">
-        <v>45953</v>
-      </c>
-      <c r="C22" s="6">
-        <v>0.66034000000000004</v>
+      <c r="A22" s="2">
+        <v>4760</v>
+      </c>
+      <c r="B22" s="3">
+        <v>45989</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0.65205000000000002</v>
       </c>
       <c r="D22" s="5">
-        <v>3801.6</v>
+        <v>3736.8</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="6">
-        <v>4573</v>
-      </c>
-      <c r="B23" s="7">
-        <v>45953</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0.66034000000000004</v>
+      <c r="A23" s="2">
+        <v>4765</v>
+      </c>
+      <c r="B23" s="3">
+        <v>45989</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0.65205000000000002</v>
       </c>
       <c r="D23" s="5">
-        <v>3801.6</v>
+        <v>3315.6</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="6">
-        <v>4630</v>
-      </c>
-      <c r="B24" s="7">
-        <v>45953</v>
-      </c>
-      <c r="C24" s="6">
-        <v>0.66034000000000004</v>
+      <c r="A24" s="2">
+        <v>4825</v>
+      </c>
+      <c r="B24" s="3">
+        <v>45989</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0.65205000000000002</v>
       </c>
       <c r="D24" s="5">
-        <v>3979.95</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="6">
-        <v>4634</v>
-      </c>
-      <c r="B25" s="7">
-        <v>45953</v>
-      </c>
-      <c r="C25" s="6">
-        <v>0.66034000000000004</v>
+      <c r="A25" s="2">
+        <v>4829</v>
+      </c>
+      <c r="B25" s="3">
+        <v>45989</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0.65205000000000002</v>
       </c>
       <c r="D25" s="5">
+        <v>3736.8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="2">
+        <v>4945</v>
+      </c>
+      <c r="B26" s="3">
+        <v>45989</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0.65332999999999997</v>
+      </c>
+      <c r="D26" s="5">
+        <v>6734.4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="2">
+        <v>4943</v>
+      </c>
+      <c r="B27" s="3">
+        <v>45989</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0.65322999999999998</v>
+      </c>
+      <c r="D27" s="5">
+        <v>7470.4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="2">
+        <v>4658</v>
+      </c>
+      <c r="B28" s="3">
+        <v>45989</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0.65268999999999999</v>
+      </c>
+      <c r="D28" s="5">
+        <v>6772.8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="2">
+        <v>4659</v>
+      </c>
+      <c r="B29" s="3">
+        <v>45989</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0.65268999999999999</v>
+      </c>
+      <c r="D29" s="5">
+        <v>13545.6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="2">
+        <v>4666</v>
+      </c>
+      <c r="B30" s="3">
+        <v>45989</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0.65268999999999999</v>
+      </c>
+      <c r="D30" s="5">
+        <v>6772.8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="2">
+        <v>4833</v>
+      </c>
+      <c r="B31" s="3">
+        <v>46000</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0.66039000000000003</v>
+      </c>
+      <c r="D31" s="5">
+        <v>4158</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
+        <v>4834</v>
+      </c>
+      <c r="B32" s="3">
+        <v>46000</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0.66039000000000003</v>
+      </c>
+      <c r="D32" s="5">
+        <v>4158</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="2">
+        <v>4842</v>
+      </c>
+      <c r="B33" s="3">
+        <v>46002</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0.67545999999999995</v>
+      </c>
+      <c r="D33" s="5">
         <v>4114.95</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="6">
-        <v>4635</v>
-      </c>
-      <c r="B26" s="7">
-        <v>45953</v>
-      </c>
-      <c r="C26" s="6">
-        <v>0.66034000000000004</v>
-      </c>
-      <c r="D26" s="5">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="2">
+        <v>4868</v>
+      </c>
+      <c r="B34" s="3">
+        <v>46002</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0.66720000000000002</v>
+      </c>
+      <c r="D34" s="5">
+        <v>4158</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="2">
+        <v>4996</v>
+      </c>
+      <c r="B35" s="3">
+        <v>46002</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0.66720000000000002</v>
+      </c>
+      <c r="D35" s="5">
         <v>3888.15</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="6">
-        <v>4636</v>
-      </c>
-      <c r="B27" s="7">
-        <v>45953</v>
-      </c>
-      <c r="C27" s="6">
-        <v>0.66034000000000004</v>
-      </c>
-      <c r="D27" s="5">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="2">
+        <v>4830</v>
+      </c>
+      <c r="B36" s="3">
+        <v>46009</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0.65088999999999997</v>
+      </c>
+      <c r="D36" s="5">
+        <v>3647.78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="2">
+        <v>4840</v>
+      </c>
+      <c r="B37" s="3">
+        <v>46009</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0.65088999999999997</v>
+      </c>
+      <c r="D37" s="5">
         <v>4158</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="6">
-        <v>4595</v>
-      </c>
-      <c r="B28" s="7">
-        <v>45960</v>
-      </c>
-      <c r="C28" s="6">
-        <v>0.65659999999999996</v>
-      </c>
-      <c r="D28" s="5">
-        <v>3979.95</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="6">
-        <v>4667</v>
-      </c>
-      <c r="B29" s="7">
-        <v>45960</v>
-      </c>
-      <c r="C29" s="6">
-        <v>0.65659999999999996</v>
-      </c>
-      <c r="D29" s="5">
-        <v>3864</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="6">
-        <v>4668</v>
-      </c>
-      <c r="B30" s="7">
-        <v>45960</v>
-      </c>
-      <c r="C30" s="6">
-        <v>0.65659999999999996</v>
-      </c>
-      <c r="D30" s="5">
-        <v>3864</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="6">
-        <v>4669</v>
-      </c>
-      <c r="B31" s="7">
-        <v>45960</v>
-      </c>
-      <c r="C31" s="6">
-        <v>0.65659999999999996</v>
-      </c>
-      <c r="D31" s="5">
-        <v>3864</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="6">
-        <v>4693</v>
-      </c>
-      <c r="B32" s="7">
-        <v>45960</v>
-      </c>
-      <c r="C32" s="6">
-        <v>0.65659999999999996</v>
-      </c>
-      <c r="D32" s="5">
-        <v>3979.95</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="6">
-        <v>8</v>
-      </c>
-      <c r="B33" s="7">
-        <v>45966</v>
-      </c>
-      <c r="C33" s="6">
-        <v>0.65044999999999997</v>
-      </c>
-      <c r="D33" s="5">
-        <v>20700</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="6">
-        <v>4726</v>
-      </c>
-      <c r="B34" s="7">
-        <v>45967</v>
-      </c>
-      <c r="C34" s="6">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="2">
+        <v>4874</v>
+      </c>
+      <c r="B38" s="3">
+        <v>46009</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0.65088999999999997</v>
+      </c>
+      <c r="D38" s="5">
+        <v>4414.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="2">
+        <v>4953</v>
+      </c>
+      <c r="B39" s="3">
+        <v>46009</v>
+      </c>
+      <c r="C39" s="2">
+        <v>0.65088999999999997</v>
+      </c>
+      <c r="D39" s="5">
+        <v>4302.1400000000003</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="2">
+        <v>4845</v>
+      </c>
+      <c r="B40" s="3">
+        <v>46009</v>
+      </c>
+      <c r="C40" s="2">
         <v>0.65051999999999999</v>
-      </c>
-      <c r="D34" s="5">
-        <v>3801.6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="6">
-        <v>4744</v>
-      </c>
-      <c r="B35" s="7">
-        <v>45967</v>
-      </c>
-      <c r="C35" s="6">
-        <v>0.65051999999999999</v>
-      </c>
-      <c r="D35" s="5">
-        <v>4184.25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="6">
-        <v>4746</v>
-      </c>
-      <c r="B36" s="7">
-        <v>45967</v>
-      </c>
-      <c r="C36" s="6">
-        <v>0.69787999999999994</v>
-      </c>
-      <c r="D36" s="5">
-        <v>4414.5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="6">
-        <v>4796</v>
-      </c>
-      <c r="B37" s="7">
-        <v>45974</v>
-      </c>
-      <c r="C37" s="6">
-        <v>0.65317999999999998</v>
-      </c>
-      <c r="D37" s="5">
-        <v>7350</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="6">
-        <v>4728</v>
-      </c>
-      <c r="B38" s="7">
-        <v>45974</v>
-      </c>
-      <c r="C38" s="6">
-        <v>0.65620000000000001</v>
-      </c>
-      <c r="D38" s="5">
-        <v>7603.2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="6">
-        <v>4729</v>
-      </c>
-      <c r="B39" s="7">
-        <v>45974</v>
-      </c>
-      <c r="C39" s="6">
-        <v>0.65620000000000001</v>
-      </c>
-      <c r="D39" s="5">
-        <v>3801.6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="6">
-        <v>4730</v>
-      </c>
-      <c r="B40" s="7">
-        <v>45974</v>
-      </c>
-      <c r="C40" s="6">
-        <v>0.65620000000000001</v>
       </c>
       <c r="D40" s="5">
         <v>3801.6</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="6">
-        <v>4692</v>
-      </c>
-      <c r="B41" s="7">
-        <v>45974</v>
-      </c>
-      <c r="C41" s="6">
-        <v>0.65493000000000001</v>
+      <c r="A41" s="2">
+        <v>4871</v>
+      </c>
+      <c r="B41" s="3">
+        <v>46009</v>
+      </c>
+      <c r="C41" s="2">
+        <v>0.66720000000000002</v>
       </c>
       <c r="D41" s="5">
+        <v>4293</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="2">
+        <v>4873</v>
+      </c>
+      <c r="B42" s="3">
+        <v>46009</v>
+      </c>
+      <c r="C42" s="2">
+        <v>0.66720000000000002</v>
+      </c>
+      <c r="D42" s="5">
+        <v>4158</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" s="2">
+        <v>4875</v>
+      </c>
+      <c r="B43" s="3">
+        <v>46009</v>
+      </c>
+      <c r="C43" s="2">
+        <v>0.65949000000000002</v>
+      </c>
+      <c r="D43" s="5">
+        <v>3426.12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" s="2">
+        <v>4876</v>
+      </c>
+      <c r="B44" s="3">
+        <v>46009</v>
+      </c>
+      <c r="C44" s="2">
+        <v>0.66039000000000003</v>
+      </c>
+      <c r="D44" s="5">
         <v>3801.6</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="6">
-        <v>4700</v>
-      </c>
-      <c r="B42" s="7">
-        <v>45974</v>
-      </c>
-      <c r="C42" s="6">
-        <v>0.65493000000000001</v>
-      </c>
-      <c r="D42" s="5">
-        <v>4160.7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="6">
-        <v>4725</v>
-      </c>
-      <c r="B43" s="7">
-        <v>45974</v>
-      </c>
-      <c r="C43" s="6">
-        <v>0.65493000000000001</v>
-      </c>
-      <c r="D43" s="5">
-        <v>3888.15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="6">
-        <v>4749</v>
-      </c>
-      <c r="B44" s="7">
-        <v>45974</v>
-      </c>
-      <c r="C44" s="6">
-        <v>0.65493000000000001</v>
-      </c>
-      <c r="D44" s="5">
-        <v>4293</v>
-      </c>
-    </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="6">
-        <v>4731</v>
-      </c>
-      <c r="B45" s="7">
-        <v>45974</v>
-      </c>
-      <c r="C45" s="6">
-        <v>0.65620000000000001</v>
+      <c r="A45" s="2">
+        <v>4883</v>
+      </c>
+      <c r="B45" s="3">
+        <v>46022</v>
+      </c>
+      <c r="C45" s="2">
+        <v>0.65081999999999995</v>
       </c>
       <c r="D45" s="5">
-        <v>3801.6</v>
+        <v>4276.74</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="6">
-        <v>4766</v>
-      </c>
-      <c r="B46" s="7">
-        <v>45974</v>
-      </c>
-      <c r="C46" s="6">
-        <v>0.65532999999999997</v>
+      <c r="A46" s="2">
+        <v>4884</v>
+      </c>
+      <c r="B46" s="3">
+        <v>46022</v>
+      </c>
+      <c r="C46" s="2">
+        <v>0.65081999999999995</v>
       </c>
       <c r="D46" s="5">
-        <v>3801.6</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="6">
-        <v>4767</v>
-      </c>
-      <c r="B47" s="7">
-        <v>45974</v>
-      </c>
-      <c r="C47" s="6">
-        <v>0.65532999999999997</v>
-      </c>
-      <c r="D47" s="5">
-        <v>3801.6</v>
+      <c r="A47" s="2">
+        <v>4885</v>
+      </c>
+      <c r="B47" s="3">
+        <v>46022</v>
+      </c>
+      <c r="C47" s="2">
+        <v>0.65081999999999995</v>
+      </c>
+      <c r="D47" s="4">
+        <v>4410</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="6">
-        <v>4685</v>
-      </c>
-      <c r="B48" s="7">
-        <v>45981</v>
-      </c>
-      <c r="C48" s="6">
-        <v>0.65949000000000002</v>
-      </c>
-      <c r="D48" s="5">
-        <v>4101.45</v>
+      <c r="A48" s="2">
+        <v>4924</v>
+      </c>
+      <c r="B48" s="3">
+        <v>46022</v>
+      </c>
+      <c r="C48" s="2">
+        <v>0.65081999999999995</v>
+      </c>
+      <c r="D48" s="4">
+        <v>4276.74</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="6">
-        <v>4686</v>
-      </c>
-      <c r="B49" s="7">
-        <v>45981</v>
-      </c>
-      <c r="C49" s="6">
-        <v>0.65949000000000002</v>
-      </c>
-      <c r="D49" s="5">
-        <v>3315.6</v>
+      <c r="A49" s="2">
+        <v>4925</v>
+      </c>
+      <c r="B49" s="3">
+        <v>46022</v>
+      </c>
+      <c r="C49" s="2">
+        <v>0.65081999999999995</v>
+      </c>
+      <c r="D49" s="4">
+        <v>4410</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="6">
-        <v>4687</v>
-      </c>
-      <c r="B50" s="7">
-        <v>45981</v>
-      </c>
-      <c r="C50" s="6">
-        <v>0.65949000000000002</v>
-      </c>
-      <c r="D50" s="5">
-        <v>3941.82</v>
+      <c r="A50" s="2">
+        <v>4661</v>
+      </c>
+      <c r="B50" s="3">
+        <v>46022</v>
+      </c>
+      <c r="C50" s="2">
+        <v>0.66910000000000003</v>
+      </c>
+      <c r="D50" s="4">
+        <v>7293</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="6">
-        <v>4688</v>
-      </c>
-      <c r="B51" s="7">
-        <v>45981</v>
-      </c>
-      <c r="C51" s="6">
-        <v>0.65949000000000002</v>
-      </c>
-      <c r="D51" s="5">
-        <v>3801.6</v>
+      <c r="A51" s="2">
+        <v>4662</v>
+      </c>
+      <c r="B51" s="3">
+        <v>46022</v>
+      </c>
+      <c r="C51" s="2">
+        <v>0.66910000000000003</v>
+      </c>
+      <c r="D51" s="4">
+        <v>7293</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="6">
-        <v>4697</v>
-      </c>
-      <c r="B52" s="7">
-        <v>45981</v>
-      </c>
-      <c r="C52" s="6">
-        <v>0.65949000000000002</v>
-      </c>
-      <c r="D52" s="5">
-        <v>3426.12</v>
+      <c r="A52" s="2">
+        <v>4663</v>
+      </c>
+      <c r="B52" s="3">
+        <v>46022</v>
+      </c>
+      <c r="C52" s="2">
+        <v>0.66908999999999996</v>
+      </c>
+      <c r="D52" s="4">
+        <v>14586</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="6">
-        <v>4699</v>
-      </c>
-      <c r="B53" s="7">
-        <v>45981</v>
-      </c>
-      <c r="C53" s="6">
-        <v>0.65949000000000002</v>
-      </c>
-      <c r="D53" s="5">
-        <v>3979.95</v>
+      <c r="A53" s="2">
+        <v>4664</v>
+      </c>
+      <c r="B53" s="3">
+        <v>46022</v>
+      </c>
+      <c r="C53" s="2">
+        <v>0.66908999999999996</v>
+      </c>
+      <c r="D53" s="4">
+        <v>14586</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="6">
-        <v>4703</v>
-      </c>
-      <c r="B54" s="7">
-        <v>45981</v>
-      </c>
-      <c r="C54" s="6">
-        <v>0.65949000000000002</v>
-      </c>
-      <c r="D54" s="5">
-        <v>4066.2</v>
+      <c r="A54" s="2">
+        <v>4665</v>
+      </c>
+      <c r="B54" s="3">
+        <v>46022</v>
+      </c>
+      <c r="C54" s="2">
+        <v>0.66908999999999996</v>
+      </c>
+      <c r="D54" s="4">
+        <v>14586</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>4712</v>
+        <v>5000</v>
       </c>
       <c r="B55" s="3">
-        <v>45981</v>
+        <v>46022</v>
       </c>
       <c r="C55" s="2">
-        <v>0.65949000000000002</v>
+        <v>0.66918</v>
       </c>
       <c r="D55" s="4">
-        <v>4114.95</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>4727</v>
+        <v>5016</v>
       </c>
       <c r="B56" s="3">
-        <v>45981</v>
+        <v>46022</v>
       </c>
       <c r="C56" s="2">
-        <v>0.65949000000000002</v>
+        <v>0.66918</v>
       </c>
       <c r="D56" s="4">
-        <v>3979.95</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>4736</v>
+        <v>5018</v>
       </c>
       <c r="B57" s="3">
-        <v>45981</v>
+        <v>46022</v>
       </c>
       <c r="C57" s="2">
-        <v>0.65949000000000002</v>
+        <v>0.66918</v>
       </c>
       <c r="D57" s="4">
-        <v>3970.95</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>4755</v>
+        <v>4756</v>
       </c>
       <c r="B58" s="3">
-        <v>45981</v>
+        <v>46022</v>
       </c>
       <c r="C58" s="2">
-        <v>0.65949000000000002</v>
+        <v>0.66935</v>
       </c>
       <c r="D58" s="4">
-        <v>4158</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
@@ -1292,10 +1289,10 @@
         <v>4763</v>
       </c>
       <c r="B59" s="3">
-        <v>45981</v>
+        <v>46022</v>
       </c>
       <c r="C59" s="2">
-        <v>0.65949000000000002</v>
+        <v>0.66935</v>
       </c>
       <c r="D59" s="4">
         <v>3426.12</v>
@@ -1303,699 +1300,699 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>4850</v>
+        <v>4828</v>
       </c>
       <c r="B60" s="3">
-        <v>45981</v>
+        <v>46022</v>
       </c>
       <c r="C60" s="2">
-        <v>0.65949000000000002</v>
+        <v>0.66935</v>
       </c>
       <c r="D60" s="4">
-        <v>4158</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>4852</v>
+        <v>4831</v>
       </c>
       <c r="B61" s="3">
-        <v>45981</v>
+        <v>46022</v>
       </c>
       <c r="C61" s="2">
-        <v>0.65949000000000002</v>
+        <v>0.66935</v>
       </c>
       <c r="D61" s="4">
-        <v>4179.17</v>
+        <v>4374</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>4854</v>
+        <v>4838</v>
       </c>
       <c r="B62" s="3">
-        <v>45981</v>
+        <v>46022</v>
       </c>
       <c r="C62" s="2">
-        <v>0.65949000000000002</v>
+        <v>0.66935</v>
       </c>
       <c r="D62" s="4">
-        <v>4208.3999999999996</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>4803</v>
+        <v>4843</v>
       </c>
       <c r="B63" s="3">
-        <v>45981</v>
+        <v>46022</v>
       </c>
       <c r="C63" s="2">
-        <v>0.65895000000000004</v>
+        <v>0.66935</v>
       </c>
       <c r="D63" s="4">
-        <v>3801.6</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>4804</v>
+        <v>4844</v>
       </c>
       <c r="B64" s="3">
-        <v>45981</v>
+        <v>46022</v>
       </c>
       <c r="C64" s="2">
-        <v>0.65895000000000004</v>
+        <v>0.66935</v>
       </c>
       <c r="D64" s="4">
-        <v>3801.6</v>
+        <v>4279.5</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>4805</v>
+        <v>4847</v>
       </c>
       <c r="B65" s="3">
-        <v>45981</v>
+        <v>46022</v>
       </c>
       <c r="C65" s="2">
-        <v>0.65895000000000004</v>
+        <v>0.66935</v>
       </c>
       <c r="D65" s="4">
-        <v>3801.6</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
-        <v>4806</v>
+        <v>4870</v>
       </c>
       <c r="B66" s="3">
-        <v>45981</v>
+        <v>46022</v>
       </c>
       <c r="C66" s="2">
-        <v>0.65895000000000004</v>
+        <v>0.66935</v>
       </c>
       <c r="D66" s="4">
-        <v>3801.6</v>
+        <v>3847.32</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
-        <v>4848</v>
+        <v>4926</v>
       </c>
       <c r="B67" s="3">
-        <v>45981</v>
+        <v>46022</v>
       </c>
       <c r="C67" s="2">
-        <v>0.64800000000000002</v>
+        <v>0.66935</v>
       </c>
       <c r="D67" s="4">
-        <v>7146</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
-        <v>4608</v>
+        <v>4927</v>
       </c>
       <c r="B68" s="3">
-        <v>45981</v>
+        <v>46022</v>
       </c>
       <c r="C68" s="2">
-        <v>0.64827999999999997</v>
+        <v>0.66935</v>
       </c>
       <c r="D68" s="4">
-        <v>4375.8</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
-        <v>4612</v>
+        <v>4928</v>
       </c>
       <c r="B69" s="3">
-        <v>45981</v>
+        <v>46022</v>
       </c>
       <c r="C69" s="2">
-        <v>0.64827999999999997</v>
+        <v>0.66935</v>
       </c>
       <c r="D69" s="4">
-        <v>4375.8</v>
+        <v>4428</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
-        <v>4596</v>
+        <v>4930</v>
       </c>
       <c r="B70" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="C70" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.66935</v>
       </c>
       <c r="D70" s="4">
-        <v>3801.6</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
-        <v>4637</v>
+        <v>4946</v>
       </c>
       <c r="B71" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="C71" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.66935</v>
       </c>
       <c r="D71" s="4">
-        <v>3979.95</v>
+        <v>4232.45</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
-        <v>4639</v>
+        <v>4947</v>
       </c>
       <c r="B72" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="C72" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.66935</v>
       </c>
       <c r="D72" s="4">
-        <v>4114.95</v>
+        <v>4371.84</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
-        <v>4696</v>
+        <v>4948</v>
       </c>
       <c r="B73" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="C73" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.66935</v>
       </c>
       <c r="D73" s="4">
-        <v>3558.75</v>
+        <v>4302.1400000000003</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
-        <v>4704</v>
+        <v>4965</v>
       </c>
       <c r="B74" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="C74" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.66935</v>
       </c>
       <c r="D74" s="4">
-        <v>3801.6</v>
+        <v>4212</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
-        <v>4722</v>
+        <v>4966</v>
       </c>
       <c r="B75" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="C75" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.66935</v>
       </c>
       <c r="D75" s="4">
-        <v>4114.95</v>
+        <v>4259.2299999999996</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
-        <v>4723</v>
+        <v>4969</v>
       </c>
       <c r="B76" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="C76" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.66935</v>
       </c>
       <c r="D76" s="4">
-        <v>3858.3</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
-        <v>4750</v>
+        <v>4971</v>
       </c>
       <c r="B77" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="C77" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.66935</v>
       </c>
       <c r="D77" s="4">
-        <v>3884.7</v>
+        <v>3986.54</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
-        <v>4752</v>
+        <v>4972</v>
       </c>
       <c r="B78" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="C78" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.66935</v>
       </c>
       <c r="D78" s="4">
-        <v>4114.95</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
-        <v>4753</v>
+        <v>4979</v>
       </c>
       <c r="B79" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="C79" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.66935</v>
       </c>
       <c r="D79" s="4">
-        <v>3645</v>
+        <v>4302.1400000000003</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
-        <v>4754</v>
+        <v>4993</v>
       </c>
       <c r="B80" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="C80" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.66935</v>
       </c>
       <c r="D80" s="4">
-        <v>3941.82</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
-        <v>4756</v>
+        <v>4994</v>
       </c>
       <c r="B81" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="C81" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.66935</v>
       </c>
       <c r="D81" s="4">
-        <v>4293</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
-        <v>4760</v>
+        <v>5010</v>
       </c>
       <c r="B82" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="C82" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.66935</v>
       </c>
       <c r="D82" s="4">
-        <v>3736.8</v>
+        <v>4266</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
-        <v>4762</v>
+        <v>4865</v>
       </c>
       <c r="B83" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="C83" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.66857</v>
       </c>
       <c r="D83" s="4">
-        <v>3858.3</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
-        <v>4764</v>
+        <v>4867</v>
       </c>
       <c r="B84" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="C84" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.66857</v>
       </c>
       <c r="D84" s="4">
-        <v>4293</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
-        <v>4765</v>
+        <v>4918</v>
       </c>
       <c r="B85" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="C85" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.66857</v>
       </c>
       <c r="D85" s="4">
-        <v>3315.6</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
-        <v>4824</v>
+        <v>4919</v>
       </c>
       <c r="B86" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="C86" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.66857</v>
       </c>
       <c r="D86" s="4">
-        <v>3847.32</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
-        <v>4825</v>
+        <v>4973</v>
       </c>
       <c r="B87" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="C87" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.66857</v>
       </c>
       <c r="D87" s="4">
-        <v>4158</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
-        <v>4827</v>
+        <v>4644</v>
       </c>
       <c r="B88" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="C88" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.66942000000000002</v>
       </c>
       <c r="D88" s="4">
-        <v>4158</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
-        <v>4829</v>
+        <v>4645</v>
       </c>
       <c r="B89" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="C89" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.66942000000000002</v>
       </c>
       <c r="D89" s="4">
-        <v>3736.8</v>
+        <v>8751.6</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
-        <v>4945</v>
+        <v>4647</v>
       </c>
       <c r="B90" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="C90" s="2">
-        <v>0.65332999999999997</v>
+        <v>0.66942000000000002</v>
       </c>
       <c r="D90" s="4">
-        <v>6734.4</v>
+        <v>8751.6</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
-        <v>4943</v>
+        <v>4649</v>
       </c>
       <c r="B91" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="C91" s="2">
-        <v>0.65322999999999998</v>
+        <v>0.66942000000000002</v>
       </c>
       <c r="D91" s="4">
-        <v>7470.4</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
-        <v>4658</v>
+        <v>4808</v>
       </c>
       <c r="B92" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="C92" s="2">
-        <v>0.65268999999999999</v>
+        <v>0.66942000000000002</v>
       </c>
       <c r="D92" s="4">
-        <v>6772.8</v>
+        <v>8751.6</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
-        <v>4659</v>
+        <v>4757</v>
       </c>
       <c r="B93" s="3">
-        <v>45989</v>
+        <v>46030</v>
       </c>
       <c r="C93" s="2">
-        <v>0.65268999999999999</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D93" s="4">
-        <v>13545.6</v>
+        <v>4066.2</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
-        <v>4660</v>
+        <v>4872</v>
       </c>
       <c r="B94" s="3">
-        <v>45989</v>
+        <v>46030</v>
       </c>
       <c r="C94" s="2">
-        <v>0.65268999999999999</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D94" s="4">
-        <v>6772.8</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
-        <v>4666</v>
+        <v>4878</v>
       </c>
       <c r="B95" s="3">
-        <v>45989</v>
+        <v>46030</v>
       </c>
       <c r="C95" s="2">
-        <v>0.65268999999999999</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D95" s="4">
-        <v>6772.8</v>
+        <v>3558.75</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
-        <v>4863</v>
+        <v>4957</v>
       </c>
       <c r="B96" s="3">
-        <v>45991</v>
+        <v>46030</v>
       </c>
       <c r="C96" s="2">
-        <v>0.65456999999999999</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D96" s="4">
-        <v>3801.6</v>
+        <v>4302.1400000000003</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
-        <v>4864</v>
+        <v>4959</v>
       </c>
       <c r="B97" s="3">
-        <v>45995</v>
+        <v>46030</v>
       </c>
       <c r="C97" s="2">
-        <v>0.65085999999999999</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D97" s="4">
-        <v>3801.6</v>
+        <v>4105.5</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
-        <v>4977</v>
+        <v>4960</v>
       </c>
       <c r="B98" s="3">
-        <v>45995</v>
+        <v>46030</v>
       </c>
       <c r="C98" s="2">
-        <v>0.65085999999999999</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D98" s="4">
-        <v>1350</v>
+        <v>4302.1400000000003</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
-        <v>4799</v>
+        <v>4961</v>
       </c>
       <c r="B99" s="3">
-        <v>45995</v>
+        <v>46030</v>
       </c>
       <c r="C99" s="2">
-        <v>0.65085000000000004</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D99" s="4">
-        <v>4276.74</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
-        <v>4800</v>
+        <v>4964</v>
       </c>
       <c r="B100" s="3">
-        <v>45995</v>
+        <v>46030</v>
       </c>
       <c r="C100" s="2">
-        <v>0.65085000000000004</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D100" s="4">
-        <v>4410</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
-        <v>4801</v>
+        <v>4980</v>
       </c>
       <c r="B101" s="3">
-        <v>45995</v>
+        <v>46030</v>
       </c>
       <c r="C101" s="2">
-        <v>0.65085000000000004</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D101" s="4">
-        <v>4410</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
-        <v>4802</v>
+        <v>4984</v>
       </c>
       <c r="B102" s="3">
-        <v>45995</v>
+        <v>46030</v>
       </c>
       <c r="C102" s="2">
-        <v>0.65085000000000004</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D102" s="4">
-        <v>4276.74</v>
+        <v>3558.6</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
-        <v>4853</v>
+        <v>4985</v>
       </c>
       <c r="B103" s="3">
-        <v>45995</v>
+        <v>46030</v>
       </c>
       <c r="C103" s="2">
-        <v>0.65085000000000004</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D103" s="4">
-        <v>4304.9399999999996</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
-        <v>4857</v>
+        <v>4986</v>
       </c>
       <c r="B104" s="3">
-        <v>45995</v>
+        <v>46030</v>
       </c>
       <c r="C104" s="2">
-        <v>0.65085000000000004</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D104" s="4">
-        <v>4362.0600000000004</v>
+        <v>4117.92</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
-        <v>4879</v>
+        <v>4987</v>
       </c>
       <c r="B105" s="3">
-        <v>45995</v>
+        <v>46030</v>
       </c>
       <c r="C105" s="2">
-        <v>0.65085000000000004</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D105" s="4">
-        <v>4410</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
-        <v>4880</v>
+        <v>5006</v>
       </c>
       <c r="B106" s="3">
-        <v>45995</v>
+        <v>46030</v>
       </c>
       <c r="C106" s="2">
-        <v>0.65085000000000004</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D106" s="4">
-        <v>4410</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
-        <v>4881</v>
+        <v>5007</v>
       </c>
       <c r="B107" s="3">
-        <v>45995</v>
+        <v>46030</v>
       </c>
       <c r="C107" s="2">
-        <v>0.65085000000000004</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D107" s="4">
-        <v>4333.5</v>
+        <v>4066.2</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
-        <v>4882</v>
+        <v>5013</v>
       </c>
       <c r="B108" s="3">
-        <v>45995</v>
+        <v>46030</v>
       </c>
       <c r="C108" s="2">
-        <v>0.65085000000000004</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D108" s="4">
-        <v>4410</v>
+        <v>3864</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
-        <v>4833</v>
+        <v>5023</v>
       </c>
       <c r="B109" s="3">
-        <v>46000</v>
+        <v>46030</v>
       </c>
       <c r="C109" s="2">
-        <v>0.66039000000000003</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D109" s="4">
         <v>4158</v>
@@ -2003,55 +2000,55 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
-        <v>4834</v>
+        <v>5025</v>
       </c>
       <c r="B110" s="3">
-        <v>46000</v>
+        <v>46030</v>
       </c>
       <c r="C110" s="2">
-        <v>0.66039000000000003</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D110" s="4">
-        <v>4158</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
-        <v>4835</v>
+        <v>4807</v>
       </c>
       <c r="B111" s="3">
-        <v>46000</v>
+        <v>46030</v>
       </c>
       <c r="C111" s="2">
-        <v>0.66039000000000003</v>
+        <v>0.67181000000000002</v>
       </c>
       <c r="D111" s="4">
-        <v>4428</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
-        <v>4836</v>
+        <v>4809</v>
       </c>
       <c r="B112" s="3">
-        <v>46000</v>
+        <v>46030</v>
       </c>
       <c r="C112" s="2">
-        <v>0.66039000000000003</v>
+        <v>0.67181000000000002</v>
       </c>
       <c r="D112" s="4">
-        <v>4252.5</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
-        <v>4838</v>
+        <v>4920</v>
       </c>
       <c r="B113" s="3">
-        <v>46000</v>
+        <v>46030</v>
       </c>
       <c r="C113" s="2">
-        <v>0.66039000000000003</v>
+        <v>0.67154999999999998</v>
       </c>
       <c r="D113" s="4">
         <v>3801.6</v>
@@ -2059,422 +2056,422 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
-        <v>4641</v>
+        <v>4921</v>
       </c>
       <c r="B114" s="3">
-        <v>46002</v>
+        <v>46030</v>
       </c>
       <c r="C114" s="2">
-        <v>0.65095000000000003</v>
+        <v>0.67154999999999998</v>
       </c>
       <c r="D114" s="4">
-        <v>8751.6</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
-        <v>4642</v>
+        <v>5020</v>
       </c>
       <c r="B115" s="3">
-        <v>46002</v>
+        <v>46030</v>
       </c>
       <c r="C115" s="2">
-        <v>0.65095000000000003</v>
+        <v>0.67154999999999998</v>
       </c>
       <c r="D115" s="4">
-        <v>8751.6</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
-        <v>4643</v>
+        <v>5022</v>
       </c>
       <c r="B116" s="3">
-        <v>46002</v>
+        <v>46030</v>
       </c>
       <c r="C116" s="2">
-        <v>0.65095000000000003</v>
+        <v>0.67154999999999998</v>
       </c>
       <c r="D116" s="4">
-        <v>8751.6</v>
+        <v>7603.2</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
-        <v>4841</v>
+        <v>5041</v>
       </c>
       <c r="B117" s="3">
-        <v>46002</v>
+        <v>46030</v>
       </c>
       <c r="C117" s="2">
-        <v>0.65939000000000003</v>
+        <v>0.67154999999999998</v>
       </c>
       <c r="D117" s="4">
-        <v>4428</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
-        <v>4842</v>
+        <v>4998</v>
       </c>
       <c r="B118" s="3">
-        <v>46002</v>
+        <v>46030</v>
       </c>
       <c r="C118" s="2">
-        <v>0.67545999999999995</v>
+        <v>0.65098999999999996</v>
       </c>
       <c r="D118" s="4">
-        <v>4114.95</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
-        <v>4843</v>
+        <v>5015</v>
       </c>
       <c r="B119" s="3">
-        <v>46002</v>
+        <v>46030</v>
       </c>
       <c r="C119" s="2">
-        <v>0.66720000000000002</v>
+        <v>0.65098999999999996</v>
       </c>
       <c r="D119" s="4">
-        <v>4158</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A120" s="2">
-        <v>4847</v>
+        <v>5017</v>
       </c>
       <c r="B120" s="3">
-        <v>46002</v>
+        <v>46030</v>
       </c>
       <c r="C120" s="2">
-        <v>0.66720000000000002</v>
+        <v>0.65098999999999996</v>
       </c>
       <c r="D120" s="4">
-        <v>4293</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
-        <v>4868</v>
+        <v>5067</v>
       </c>
       <c r="B121" s="3">
-        <v>46002</v>
+        <v>46030</v>
       </c>
       <c r="C121" s="2">
-        <v>0.66720000000000002</v>
+        <v>0.65098999999999996</v>
       </c>
       <c r="D121" s="4">
-        <v>4158</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122" s="2">
-        <v>4995</v>
+        <v>5068</v>
       </c>
       <c r="B122" s="3">
-        <v>46002</v>
+        <v>46030</v>
       </c>
       <c r="C122" s="2">
-        <v>0.66720000000000002</v>
+        <v>0.65098999999999996</v>
       </c>
       <c r="D122" s="4">
-        <v>3801.9</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123" s="2">
-        <v>4996</v>
+        <v>4702</v>
       </c>
       <c r="B123" s="3">
-        <v>46002</v>
+        <v>46030</v>
       </c>
       <c r="C123" s="2">
-        <v>0.66720000000000002</v>
+        <v>0.6573</v>
       </c>
       <c r="D123" s="4">
-        <v>3888.15</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124" s="2">
-        <v>4646</v>
+        <v>4958</v>
       </c>
       <c r="B124" s="3">
-        <v>46009</v>
+        <v>46030</v>
       </c>
       <c r="C124" s="2">
-        <v>0.66088000000000002</v>
+        <v>0.65086999999999995</v>
       </c>
       <c r="D124" s="4">
-        <v>8751.6</v>
+        <v>4074.3</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125" s="2">
-        <v>4648</v>
+        <v>4983</v>
       </c>
       <c r="B125" s="3">
-        <v>46009</v>
+        <v>46030</v>
       </c>
       <c r="C125" s="2">
-        <v>0.66088000000000002</v>
+        <v>0.66037000000000001</v>
       </c>
       <c r="D125" s="4">
-        <v>4375.8</v>
+        <v>3801.75</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A126" s="2">
-        <v>4839</v>
+        <v>4997</v>
       </c>
       <c r="B126" s="3">
-        <v>46009</v>
+        <v>46030</v>
       </c>
       <c r="C126" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.66039000000000003</v>
       </c>
       <c r="D126" s="4">
-        <v>4293</v>
+        <v>3801.9</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127" s="2">
-        <v>4845</v>
+        <v>5004</v>
       </c>
       <c r="B127" s="3">
-        <v>46009</v>
+        <v>46030</v>
       </c>
       <c r="C127" s="2">
-        <v>0.65051999999999999</v>
+        <v>0.65952</v>
       </c>
       <c r="D127" s="4">
-        <v>3801.6</v>
+        <v>3801.75</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128" s="2">
-        <v>4871</v>
+        <v>5014</v>
       </c>
       <c r="B128" s="3">
-        <v>46009</v>
+        <v>46030</v>
       </c>
       <c r="C128" s="2">
-        <v>0.66720000000000002</v>
+        <v>0.65051999999999999</v>
       </c>
       <c r="D128" s="4">
-        <v>4293</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" s="2">
-        <v>4873</v>
+        <v>5043</v>
       </c>
       <c r="B129" s="3">
-        <v>46009</v>
+        <v>46037</v>
       </c>
       <c r="C129" s="2">
-        <v>0.66720000000000002</v>
+        <v>0.66808000000000001</v>
       </c>
       <c r="D129" s="4">
-        <v>4158</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130" s="2">
-        <v>4875</v>
+        <v>5044</v>
       </c>
       <c r="B130" s="3">
-        <v>46009</v>
+        <v>46037</v>
       </c>
       <c r="C130" s="2">
-        <v>0.65949000000000002</v>
+        <v>0.66808000000000001</v>
       </c>
       <c r="D130" s="4">
-        <v>3426.12</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" s="2">
-        <v>4876</v>
+        <v>4967</v>
       </c>
       <c r="B131" s="3">
-        <v>46009</v>
+        <v>46037</v>
       </c>
       <c r="C131" s="2">
-        <v>0.66039000000000003</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="D131" s="4">
-        <v>3801.6</v>
+        <v>4331.46</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" s="2">
-        <v>4830</v>
+        <v>4970</v>
       </c>
       <c r="B132" s="3">
-        <v>46009</v>
+        <v>46037</v>
       </c>
       <c r="C132" s="2">
-        <v>0.65088999999999997</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="D132" s="4">
-        <v>3647.78</v>
+        <v>4357.16</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A133" s="2">
-        <v>4832</v>
+        <v>5011</v>
       </c>
       <c r="B133" s="3">
-        <v>46009</v>
+        <v>46037</v>
       </c>
       <c r="C133" s="2">
-        <v>0.65088999999999997</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="D133" s="4">
-        <v>3979.95</v>
+        <v>4287.6000000000004</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A134" s="2">
-        <v>4840</v>
+        <v>5019</v>
       </c>
       <c r="B134" s="3">
-        <v>46009</v>
+        <v>46037</v>
       </c>
       <c r="C134" s="2">
-        <v>0.65088999999999997</v>
+        <v>0.66796</v>
       </c>
       <c r="D134" s="4">
-        <v>4158</v>
+        <v>4101.45</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A135" s="2">
-        <v>4874</v>
+        <v>5028</v>
       </c>
       <c r="B135" s="3">
-        <v>46009</v>
+        <v>46037</v>
       </c>
       <c r="C135" s="2">
-        <v>0.65088999999999997</v>
+        <v>0.66796</v>
       </c>
       <c r="D135" s="4">
-        <v>4414.5</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A136" s="2">
-        <v>4953</v>
+        <v>4968</v>
       </c>
       <c r="B136" s="3">
-        <v>46009</v>
+        <v>46044</v>
       </c>
       <c r="C136" s="2">
-        <v>0.65088999999999997</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D136" s="4">
-        <v>4302.1400000000003</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A137" s="2">
-        <v>4963</v>
+        <v>5008</v>
       </c>
       <c r="B137" s="3">
-        <v>46009</v>
+        <v>46044</v>
       </c>
       <c r="C137" s="2">
-        <v>0.65088999999999997</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D137" s="4">
-        <v>4074.45</v>
+        <v>3888.15</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138" s="2">
-        <v>4883</v>
+        <v>5029</v>
       </c>
       <c r="B138" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C138" s="2">
-        <v>0.65081999999999995</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D138" s="4">
-        <v>4276.74</v>
+        <v>4279.5</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A139" s="2">
-        <v>4884</v>
+        <v>5032</v>
       </c>
       <c r="B139" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C139" s="2">
-        <v>0.65081999999999995</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D139" s="4">
-        <v>4410</v>
+        <v>4101.45</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A140" s="2">
-        <v>4885</v>
+        <v>5033</v>
       </c>
       <c r="B140" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C140" s="2">
-        <v>0.65081999999999995</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D140" s="4">
-        <v>4410</v>
+        <v>3426.12</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A141" s="2">
-        <v>4924</v>
+        <v>5034</v>
       </c>
       <c r="B141" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C141" s="2">
-        <v>0.65081999999999995</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D141" s="4">
-        <v>4276.74</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142" s="2">
-        <v>4925</v>
+        <v>5035</v>
       </c>
       <c r="B142" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C142" s="2">
-        <v>0.65081999999999995</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D142" s="4">
-        <v>4410</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143" s="2">
-        <v>4661</v>
+        <v>5036</v>
       </c>
       <c r="B143" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C143" s="2">
-        <v>0.66910000000000003</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D143" s="4">
-        <v>7293</v>
+        <v>4114.95</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" s="2"/>
@@ -2484,69 +2481,69 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A144" s="2">
-        <v>4662</v>
+        <v>5037</v>
       </c>
       <c r="B144" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C144" s="2">
-        <v>0.66910000000000003</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D144" s="4">
-        <v>7293</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A145" s="2">
-        <v>4663</v>
+        <v>5038</v>
       </c>
       <c r="B145" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C145" s="2">
-        <v>0.66908999999999996</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D145" s="4">
-        <v>14586</v>
+        <v>4316.72</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146" s="2">
-        <v>4664</v>
+        <v>5073</v>
       </c>
       <c r="B146" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C146" s="2">
-        <v>0.66908999999999996</v>
+        <v>0.67552999999999996</v>
       </c>
       <c r="D146" s="4">
-        <v>14586</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147" s="2">
-        <v>4665</v>
+        <v>5074</v>
       </c>
       <c r="B147" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C147" s="2">
-        <v>0.66908999999999996</v>
+        <v>0.67552999999999996</v>
       </c>
       <c r="D147" s="4">
-        <v>14586</v>
+        <v>7603.2</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A148" s="2">
-        <v>5000</v>
+        <v>5076</v>
       </c>
       <c r="B148" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C148" s="2">
-        <v>0.66918</v>
+        <v>0.67552999999999996</v>
       </c>
       <c r="D148" s="4">
         <v>3801.6</v>
@@ -2554,789 +2551,941 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A149" s="2">
-        <v>5016</v>
+        <v>5069</v>
       </c>
       <c r="B149" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C149" s="2">
-        <v>0.66918</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="D149" s="4">
-        <v>3801.6</v>
+        <v>4143.4799999999996</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A150" s="2">
-        <v>5018</v>
+        <v>5070</v>
       </c>
       <c r="B150" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C150" s="2">
-        <v>0.66918</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="D150" s="4">
-        <v>3801.6</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A151" s="2">
-        <v>4644</v>
+        <v>5071</v>
       </c>
       <c r="B151" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C151" s="2">
-        <v>0.66942000000000002</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="D151" s="4">
-        <v>4375.8</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A152" s="2">
-        <v>4645</v>
+        <v>5072</v>
       </c>
       <c r="B152" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C152" s="2">
-        <v>0.66942000000000002</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="D152" s="4">
-        <v>8751.6</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A153" s="2">
-        <v>4647</v>
+        <v>5101</v>
       </c>
       <c r="B153" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C153" s="2">
-        <v>0.66942000000000002</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="D153" s="4">
-        <v>8751.6</v>
+        <v>4143.4799999999996</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A154" s="2">
-        <v>4649</v>
+        <v>5102</v>
       </c>
       <c r="B154" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C154" s="2">
-        <v>0.66942000000000002</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="D154" s="4">
-        <v>4375.8</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A155" s="2">
-        <v>4808</v>
+        <v>5042</v>
       </c>
       <c r="B155" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C155" s="2">
-        <v>0.66942000000000002</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D155" s="4">
-        <v>8751.6</v>
+        <v>3832.95</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A156" s="2">
-        <v>4828</v>
+        <v>5046</v>
       </c>
       <c r="B156" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C156" s="2">
-        <v>0.66935</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D156" s="4">
-        <v>3801.6</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A157" s="2">
-        <v>4831</v>
+        <v>5047</v>
       </c>
       <c r="B157" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C157" s="2">
-        <v>0.66935</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D157" s="4">
-        <v>4374</v>
+        <v>3888.15</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A158" s="2" t="s">
-        <v>4</v>
+      <c r="A158" s="2">
+        <v>5048</v>
       </c>
       <c r="B158" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C158" s="2">
-        <v>0.66935</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D158" s="4">
-        <v>4279.5</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A159" s="2" t="s">
-        <v>5</v>
+      <c r="A159" s="2">
+        <v>5051</v>
       </c>
       <c r="B159" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C159" s="2">
-        <v>0.66935</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D159" s="4">
-        <v>3847.32</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A160" s="2">
-        <v>4877</v>
+        <v>5052</v>
       </c>
       <c r="B160" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C160" s="2">
-        <v>0.66935</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D160" s="4">
-        <v>3979.95</v>
+        <v>3888.15</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A161" s="2">
-        <v>4926</v>
+        <v>5053</v>
       </c>
       <c r="B161" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C161" s="2">
-        <v>0.66935</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D161" s="4">
-        <v>4293</v>
+        <v>4279.5</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A162" s="2">
-        <v>4927</v>
+        <v>5054</v>
       </c>
       <c r="B162" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C162" s="2">
-        <v>0.66935</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D162" s="4">
-        <v>4158</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A163" s="2">
-        <v>4928</v>
+        <v>5055</v>
       </c>
       <c r="B163" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C163" s="2">
-        <v>0.66935</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D163" s="4">
-        <v>4428</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A164" s="2">
-        <v>4930</v>
+        <v>5056</v>
       </c>
       <c r="B164" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C164" s="2">
-        <v>0.66935</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D164" s="4">
-        <v>4293</v>
+        <v>3888.15</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A165" s="2">
-        <v>4946</v>
+        <v>5057</v>
       </c>
       <c r="B165" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C165" s="2">
-        <v>0.66935</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D165" s="4">
-        <v>4232.45</v>
+        <v>4302.1400000000003</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A166" s="2">
-        <v>4947</v>
+        <v>5077</v>
       </c>
       <c r="B166" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C166" s="2">
-        <v>0.66935</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D166" s="4">
-        <v>4371.84</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A167" s="2">
-        <v>4948</v>
+        <v>5138</v>
       </c>
       <c r="B167" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C167" s="2">
-        <v>0.66935</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D167" s="4">
-        <v>4302.1400000000003</v>
+        <v>4347</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A168" s="2">
-        <v>4965</v>
+        <v>4974</v>
       </c>
       <c r="B168" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C168" s="2">
-        <v>0.66935</v>
+        <v>0.68022000000000005</v>
       </c>
       <c r="D168" s="4">
-        <v>4212</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A169" s="2">
-        <v>4966</v>
+        <v>5104</v>
       </c>
       <c r="B169" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C169" s="2">
-        <v>0.66935</v>
+        <v>0.68022000000000005</v>
       </c>
       <c r="D169" s="4">
-        <v>4259.2299999999996</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A170" s="2">
-        <v>4969</v>
+        <v>5106</v>
       </c>
       <c r="B170" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C170" s="2">
-        <v>0.66935</v>
+        <v>0.68022000000000005</v>
       </c>
       <c r="D170" s="4">
-        <v>4230</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A171" s="2">
-        <v>4971</v>
+      <c r="A171" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="B171" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C171" s="2">
-        <v>0.66935</v>
+        <v>0.68022000000000005</v>
       </c>
       <c r="D171" s="4">
-        <v>3986.54</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A172" s="2">
-        <v>4972</v>
+      <c r="A172" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B172" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C172" s="2">
-        <v>0.66935</v>
+        <v>0.68022000000000005</v>
       </c>
       <c r="D172" s="4">
-        <v>4158</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A173" s="2">
-        <v>4979</v>
+      <c r="A173" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="B173" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C173" s="2">
-        <v>0.66935</v>
+        <v>0.68022000000000005</v>
       </c>
       <c r="D173" s="4">
-        <v>4302.1400000000003</v>
+        <v>2418.3000000000002</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A174" s="2">
-        <v>4993</v>
+        <v>4810</v>
       </c>
       <c r="B174" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C174" s="2">
-        <v>0.66935</v>
+        <v>0.68022000000000005</v>
       </c>
       <c r="D174" s="4">
-        <v>5400</v>
+        <v>8751.6</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A175" s="2">
-        <v>4994</v>
+        <v>4811</v>
       </c>
       <c r="B175" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C175" s="2">
-        <v>0.66935</v>
+        <v>0.68022000000000005</v>
       </c>
       <c r="D175" s="4">
-        <v>5400</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A176" s="2">
-        <v>5010</v>
+        <v>4812</v>
       </c>
       <c r="B176" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C176" s="2">
-        <v>0.66935</v>
+        <v>0.68022000000000005</v>
       </c>
       <c r="D176" s="4">
-        <v>4266</v>
+        <v>8751.6</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A177" s="2">
-        <v>4865</v>
+        <v>4813</v>
       </c>
       <c r="B177" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C177" s="2">
-        <v>0.66857</v>
+        <v>0.68022000000000005</v>
       </c>
       <c r="D177" s="4">
-        <v>3801.6</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A178" s="2">
-        <v>4867</v>
+        <v>4814</v>
       </c>
       <c r="B178" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C178" s="2">
-        <v>0.66857</v>
+        <v>0.68022000000000005</v>
       </c>
       <c r="D178" s="4">
-        <v>3801.6</v>
+        <v>8751.6</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A179" s="2">
-        <v>4918</v>
+        <v>4815</v>
       </c>
       <c r="B179" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C179" s="2">
-        <v>0.66857</v>
+        <v>0.68022000000000005</v>
       </c>
       <c r="D179" s="4">
-        <v>3801.6</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A180" s="2">
-        <v>4919</v>
+        <v>4816</v>
       </c>
       <c r="B180" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C180" s="2">
-        <v>0.66857</v>
+        <v>0.68022000000000005</v>
       </c>
       <c r="D180" s="4">
-        <v>3801.6</v>
+        <v>8751.6</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A181" s="2">
-        <v>4973</v>
+        <v>5096</v>
       </c>
       <c r="B181" s="3">
-        <v>46022</v>
+        <v>46051</v>
       </c>
       <c r="C181" s="2">
-        <v>0.66857</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="D181" s="4">
         <v>3801.6</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A182" s="8" t="s">
-        <v>6</v>
+      <c r="A182" s="2">
+        <v>5107</v>
       </c>
       <c r="B182" s="3">
-        <v>46022</v>
+        <v>46051</v>
       </c>
       <c r="C182" s="2">
-        <v>0.66857</v>
-      </c>
-      <c r="D182" s="2">
-        <v>668.1</v>
+        <v>0.65100000000000002</v>
+      </c>
+      <c r="D182" s="4">
+        <v>3801.6</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A183" s="2">
-        <v>4718</v>
+        <v>5108</v>
       </c>
       <c r="B183" s="3">
-        <v>46022</v>
+        <v>46051</v>
       </c>
       <c r="C183" s="2">
-        <v>0.65080000000000005</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="D183" s="4">
-        <v>29172</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A184" s="2">
-        <v>4747</v>
+        <v>5110</v>
       </c>
       <c r="B184" s="3">
-        <v>46022</v>
+        <v>46051</v>
       </c>
       <c r="C184" s="2">
-        <v>0.65080000000000005</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="D184" s="4">
-        <v>29172</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A185" s="2">
-        <v>4819</v>
+        <v>5166</v>
       </c>
       <c r="B185" s="3">
-        <v>46022</v>
+        <v>46051</v>
       </c>
       <c r="C185" s="2">
-        <v>0.65080000000000005</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="D185" s="4">
-        <v>29172</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A186" s="2">
-        <v>4855</v>
+        <v>5030</v>
       </c>
       <c r="B186" s="3">
-        <v>46022</v>
+        <v>46051</v>
       </c>
       <c r="C186" s="2">
-        <v>0.65081</v>
+        <v>0.70299</v>
       </c>
       <c r="D186" s="4">
-        <v>14586</v>
+        <v>4873.5</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A187" s="2">
-        <v>4912</v>
+        <v>5058</v>
       </c>
       <c r="B187" s="3">
-        <v>46022</v>
+        <v>46051</v>
       </c>
       <c r="C187" s="2">
-        <v>0.65081</v>
+        <v>0.70299</v>
       </c>
       <c r="D187" s="4">
-        <v>14586</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A188" s="2">
-        <v>4447</v>
+        <v>5059</v>
       </c>
       <c r="B188" s="3">
-        <v>45918</v>
+        <v>46051</v>
       </c>
       <c r="C188" s="2">
-        <v>0.66935</v>
+        <v>0.70299</v>
       </c>
       <c r="D188" s="4">
-        <v>8870.4</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A189" s="2">
-        <v>4634</v>
+        <v>5060</v>
       </c>
       <c r="B189" s="3">
-        <v>45953</v>
+        <v>46051</v>
       </c>
       <c r="C189" s="2">
-        <v>0.66935</v>
+        <v>0.70299</v>
       </c>
       <c r="D189" s="4">
-        <v>10050.09</v>
+        <v>3801.9</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A190" s="2">
-        <v>4635</v>
+        <v>5061</v>
       </c>
       <c r="B190" s="3">
-        <v>45953</v>
+        <v>46051</v>
       </c>
       <c r="C190" s="2">
-        <v>0.66935</v>
+        <v>0.70299</v>
       </c>
       <c r="D190" s="4">
-        <v>9072.35</v>
+        <v>4187.7</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A191" s="2">
-        <v>4746</v>
+        <v>5062</v>
       </c>
       <c r="B191" s="3">
-        <v>45967</v>
+        <v>46051</v>
       </c>
       <c r="C191" s="2">
-        <v>0.66935</v>
+        <v>0.70299</v>
       </c>
       <c r="D191" s="4">
-        <v>10300.5</v>
+        <v>3315.6</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A192" s="2">
-        <v>4700</v>
+        <v>5063</v>
       </c>
       <c r="B192" s="3">
-        <v>45974</v>
+        <v>46051</v>
       </c>
       <c r="C192" s="2">
-        <v>0.66935</v>
+        <v>0.70299</v>
       </c>
       <c r="D192" s="4">
-        <v>9708.2999999999993</v>
+        <v>3700.32</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A193" s="2">
-        <v>4686</v>
+        <v>5064</v>
       </c>
       <c r="B193" s="3">
-        <v>45981</v>
+        <v>46051</v>
       </c>
       <c r="C193" s="2">
-        <v>0.66935</v>
+        <v>0.70299</v>
       </c>
       <c r="D193" s="4">
-        <v>7740.9</v>
+        <v>4299.74</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A194" s="2">
-        <v>4699</v>
+        <v>5065</v>
       </c>
       <c r="B194" s="3">
-        <v>45981</v>
+        <v>46051</v>
       </c>
       <c r="C194" s="2">
-        <v>0.66935</v>
+        <v>0.70299</v>
       </c>
       <c r="D194" s="4">
-        <v>9286.5499999999993</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A195" s="2">
-        <v>4854</v>
+        <v>5066</v>
       </c>
       <c r="B195" s="3">
-        <v>45981</v>
+        <v>46051</v>
       </c>
       <c r="C195" s="2">
-        <v>0.66935</v>
+        <v>0.70299</v>
       </c>
       <c r="D195" s="4">
-        <v>9819.6</v>
+        <v>3558.75</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A196" s="2">
-        <v>4806</v>
+        <v>5078</v>
       </c>
       <c r="B196" s="3">
-        <v>45981</v>
+        <v>46051</v>
       </c>
       <c r="C196" s="2">
-        <v>0.66857</v>
+        <v>0.70299</v>
       </c>
       <c r="D196" s="4">
+        <v>3979.95</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A197" s="2">
+        <v>5080</v>
+      </c>
+      <c r="B197" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C197" s="2">
+        <v>0.70299</v>
+      </c>
+      <c r="D197" s="4">
+        <v>4158</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A198" s="2">
+        <v>5086</v>
+      </c>
+      <c r="B198" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C198" s="2">
+        <v>0.70299</v>
+      </c>
+      <c r="D198" s="4">
+        <v>4158</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A199" s="2">
+        <v>5088</v>
+      </c>
+      <c r="B199" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C199" s="2">
+        <v>0.70299</v>
+      </c>
+      <c r="D199" s="4">
+        <v>4428</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A200" s="2">
+        <v>5090</v>
+      </c>
+      <c r="B200" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C200" s="2">
+        <v>0.70299</v>
+      </c>
+      <c r="D200" s="4">
+        <v>4199.58</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A201" s="2">
+        <v>5093</v>
+      </c>
+      <c r="B201" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C201" s="2">
+        <v>0.70299</v>
+      </c>
+      <c r="D201" s="4">
+        <v>4158</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A202" s="2">
+        <v>5095</v>
+      </c>
+      <c r="B202" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C202" s="2">
+        <v>0.70299</v>
+      </c>
+      <c r="D202" s="4">
+        <v>4150.32</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A203" s="2">
+        <v>4962</v>
+      </c>
+      <c r="B203" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C203" s="2">
+        <v>0.78613999999999995</v>
+      </c>
+      <c r="D203" s="4">
+        <v>9981.5</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A204" s="2">
+        <v>4855</v>
+      </c>
+      <c r="B204" s="3">
+        <v>46022</v>
+      </c>
+      <c r="C204" s="2">
+        <v>0.65081</v>
+      </c>
+      <c r="D204" s="4">
+        <v>14586</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A205" s="2">
+        <v>4571</v>
+      </c>
+      <c r="B205" s="3">
+        <v>46044</v>
+      </c>
+      <c r="C205" s="2">
+        <v>0.67835000000000001</v>
+      </c>
+      <c r="D205" s="4">
         <v>8870.4</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A197" s="2"/>
-      <c r="B197" s="2"/>
-      <c r="C197" s="2"/>
-      <c r="D197" s="2"/>
-    </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A198" s="2"/>
-      <c r="B198" s="2"/>
-      <c r="C198" s="2"/>
-      <c r="D198" s="2"/>
-    </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A199" s="2"/>
-      <c r="B199" s="2"/>
-      <c r="C199" s="2"/>
-      <c r="D199" s="2"/>
-    </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A200" s="2"/>
-      <c r="B200" s="2"/>
-      <c r="C200" s="2"/>
-      <c r="D200" s="2"/>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A201" s="2"/>
-      <c r="B201" s="2"/>
-      <c r="C201" s="2"/>
-      <c r="D201" s="2"/>
-    </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A202" s="2"/>
-      <c r="B202" s="2"/>
-      <c r="C202" s="2"/>
-      <c r="D202" s="2"/>
-    </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A203" s="2"/>
-      <c r="B203" s="2"/>
-      <c r="C203" s="2"/>
-      <c r="D203" s="2"/>
-    </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A204" s="2"/>
-      <c r="B204" s="2"/>
-      <c r="C204" s="2"/>
-      <c r="D204" s="2"/>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A205" s="2"/>
-      <c r="B205" s="2"/>
-      <c r="C205" s="2"/>
-      <c r="D205" s="2"/>
-    </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A206" s="2"/>
-      <c r="B206" s="2"/>
-      <c r="C206" s="2"/>
-      <c r="D206" s="2"/>
+      <c r="A206" s="2">
+        <v>4704</v>
+      </c>
+      <c r="B206" s="3">
+        <v>46044</v>
+      </c>
+      <c r="C206" s="2">
+        <v>0.67835000000000001</v>
+      </c>
+      <c r="D206" s="4">
+        <v>8870.4</v>
+      </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A207" s="2"/>
-      <c r="B207" s="2"/>
-      <c r="C207" s="2"/>
-      <c r="D207" s="2"/>
+      <c r="A207" s="2">
+        <v>4639</v>
+      </c>
+      <c r="B207" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C207" s="2">
+        <v>0.70299</v>
+      </c>
+      <c r="D207" s="4">
+        <v>7477.33</v>
+      </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A208" s="2"/>
-      <c r="B208" s="2"/>
-      <c r="C208" s="2"/>
-      <c r="D208" s="2"/>
+      <c r="A208" s="2">
+        <v>4825</v>
+      </c>
+      <c r="B208" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C208" s="2">
+        <v>0.70299</v>
+      </c>
+      <c r="D208" s="4">
+        <v>9702</v>
+      </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A209" s="2"/>
-      <c r="B209" s="2"/>
-      <c r="C209" s="2"/>
-      <c r="D209" s="2"/>
+      <c r="A209" s="2">
+        <v>4996</v>
+      </c>
+      <c r="B209" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C209" s="2">
+        <v>0.70299</v>
+      </c>
+      <c r="D209" s="4">
+        <v>9072.35</v>
+      </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A210" s="2"/>
-      <c r="B210" s="2"/>
-      <c r="C210" s="2"/>
-      <c r="D210" s="2"/>
+      <c r="A210" s="2">
+        <v>4784</v>
+      </c>
+      <c r="B210" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C210" s="2">
+        <v>0.70325000000000004</v>
+      </c>
+      <c r="D210" s="4">
+        <v>14586</v>
+      </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A211" s="2"/>
-      <c r="B211" s="2"/>
-      <c r="C211" s="2"/>
-      <c r="D211" s="2"/>
+      <c r="A211" s="2">
+        <v>4788</v>
+      </c>
+      <c r="B211" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C211" s="2">
+        <v>0.70325000000000004</v>
+      </c>
+      <c r="D211" s="4">
+        <v>29172</v>
+      </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A212" s="2"/>
-      <c r="B212" s="2"/>
-      <c r="C212" s="2"/>
-      <c r="D212" s="2"/>
+      <c r="A212" s="2">
+        <v>4792</v>
+      </c>
+      <c r="B212" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C212" s="2">
+        <v>0.70325000000000004</v>
+      </c>
+      <c r="D212" s="4">
+        <v>14586</v>
+      </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A213" s="2"/>
-      <c r="B213" s="2"/>
-      <c r="C213" s="2"/>
-      <c r="D213" s="2"/>
+      <c r="A213" s="2">
+        <v>4887</v>
+      </c>
+      <c r="B213" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C213" s="2">
+        <v>0.70325000000000004</v>
+      </c>
+      <c r="D213" s="4">
+        <v>14586</v>
+      </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A214" s="2"/>
-      <c r="B214" s="2"/>
-      <c r="C214" s="2"/>
-      <c r="D214" s="2"/>
+      <c r="A214" s="2">
+        <v>4932</v>
+      </c>
+      <c r="B214" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C214" s="2">
+        <v>0.70325000000000004</v>
+      </c>
+      <c r="D214" s="4">
+        <v>15390</v>
+      </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A215" s="2"/>
-      <c r="B215" s="2"/>
-      <c r="C215" s="2"/>
-      <c r="D215" s="2"/>
+      <c r="A215" s="2">
+        <v>4934</v>
+      </c>
+      <c r="B215" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C215" s="2">
+        <v>0.70325000000000004</v>
+      </c>
+      <c r="D215" s="4">
+        <v>15444</v>
+      </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A216" s="2"/>

--- a/H2coco/PO.xlsx
+++ b/H2coco/PO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leo/Github/XeroAPI/H2coco/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C25829-AFCB-0D43-B330-D86C0BAD0C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E9D0BC-B538-0A40-8513-C6054041ABF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19780" yWindow="-25520" windowWidth="38400" windowHeight="20980" xr2:uid="{4B9AE9D0-272D-6147-B144-109295B6F9E3}"/>
+    <workbookView xWindow="34200" yWindow="-20980" windowWidth="21600" windowHeight="37780" xr2:uid="{4B9AE9D0-272D-6147-B144-109295B6F9E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>PO</t>
   </si>
@@ -50,13 +50,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t>Extra4858</t>
-  </si>
-  <si>
-    <t>Extra4859</t>
-  </si>
-  <si>
-    <t>Extra4976</t>
+    <t>4702/1</t>
   </si>
 </sst>
 </file>
@@ -488,419 +482,419 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>4230</v>
+        <v>3</v>
       </c>
       <c r="B3" s="3">
-        <v>45848</v>
+        <v>45923</v>
       </c>
       <c r="C3" s="2">
-        <v>0.62860000000000005</v>
+        <v>0.66079399999999999</v>
       </c>
       <c r="D3" s="5">
-        <v>7603.2</v>
+        <v>5061.8</v>
       </c>
       <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B4" s="3">
-        <v>45854</v>
+        <v>45923</v>
       </c>
       <c r="C4" s="2">
-        <v>0.65176000000000001</v>
+        <v>0.66079399999999999</v>
       </c>
       <c r="D4" s="5">
-        <v>1040</v>
+        <v>5134.68</v>
       </c>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>4354</v>
+        <v>4230</v>
       </c>
       <c r="B5" s="3">
-        <v>45898</v>
+        <v>45848</v>
       </c>
       <c r="C5" s="2">
-        <v>0.65766999999999998</v>
+        <v>0.62860000000000005</v>
       </c>
       <c r="D5" s="5">
-        <v>4374</v>
+        <v>7603.2</v>
       </c>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B6" s="3">
-        <v>45923</v>
+        <v>45925</v>
       </c>
       <c r="C6" s="2">
-        <v>0.66078999999999999</v>
+        <v>0.65937000000000001</v>
       </c>
       <c r="D6" s="5">
-        <v>10350</v>
+        <v>14204.8</v>
       </c>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B7" s="3">
-        <v>45923</v>
+        <v>45966</v>
       </c>
       <c r="C7" s="2">
-        <v>0.66080000000000005</v>
+        <v>0.65044999999999997</v>
       </c>
       <c r="D7" s="5">
-        <v>1040</v>
+        <v>20700</v>
       </c>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>5</v>
+        <v>4687</v>
       </c>
       <c r="B8" s="3">
-        <v>45923</v>
+        <v>45981</v>
       </c>
       <c r="C8" s="2">
-        <v>0.66078999999999999</v>
+        <v>0.65949000000000002</v>
       </c>
       <c r="D8" s="5">
-        <v>10350</v>
+        <v>3941.82</v>
       </c>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>6</v>
+        <v>4953</v>
       </c>
       <c r="B9" s="3">
-        <v>45923</v>
+        <v>46009</v>
       </c>
       <c r="C9" s="2">
-        <v>0.66080000000000005</v>
+        <v>0.65088999999999997</v>
       </c>
       <c r="D9" s="5">
-        <v>1040</v>
+        <v>4302.1400000000003</v>
       </c>
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>7</v>
+        <v>4876</v>
       </c>
       <c r="B10" s="3">
-        <v>45925</v>
+        <v>46009</v>
       </c>
       <c r="C10" s="2">
-        <v>0.65937000000000001</v>
+        <v>0.66039000000000003</v>
       </c>
       <c r="D10" s="5">
-        <v>14204.8</v>
+        <v>3801.6</v>
       </c>
       <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>4504</v>
+        <v>4831</v>
       </c>
       <c r="B11" s="3">
-        <v>45932</v>
+        <v>46022</v>
       </c>
       <c r="C11" s="2">
-        <v>0.66049999999999998</v>
+        <v>0.66935</v>
       </c>
       <c r="D11" s="5">
-        <v>3801.6</v>
+        <v>4374</v>
       </c>
       <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>4550</v>
+        <v>4927</v>
       </c>
       <c r="B12" s="3">
-        <v>45946</v>
+        <v>46022</v>
       </c>
       <c r="C12" s="2">
-        <v>0.65949000000000002</v>
+        <v>0.66935</v>
       </c>
       <c r="D12" s="5">
-        <v>3801.6</v>
+        <v>4158</v>
       </c>
       <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>4571</v>
+        <v>4928</v>
       </c>
       <c r="B13" s="3">
-        <v>45953</v>
+        <v>46022</v>
       </c>
       <c r="C13" s="2">
-        <v>0.66034000000000004</v>
+        <v>0.66935</v>
       </c>
       <c r="D13" s="5">
-        <v>3801.6</v>
+        <v>4428</v>
       </c>
       <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>4668</v>
+        <v>4946</v>
       </c>
       <c r="B14" s="3">
-        <v>45960</v>
+        <v>46022</v>
       </c>
       <c r="C14" s="2">
-        <v>0.65659999999999996</v>
+        <v>0.66935</v>
       </c>
       <c r="D14" s="5">
-        <v>3864</v>
+        <v>4232.45</v>
       </c>
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>8</v>
+        <v>4947</v>
       </c>
       <c r="B15" s="3">
-        <v>45966</v>
+        <v>46022</v>
       </c>
       <c r="C15" s="2">
-        <v>0.65044999999999997</v>
+        <v>0.66935</v>
       </c>
       <c r="D15" s="5">
-        <v>20700</v>
+        <v>4371.84</v>
       </c>
       <c r="F15" s="2"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>4692</v>
+        <v>4948</v>
       </c>
       <c r="B16" s="3">
-        <v>45974</v>
+        <v>46022</v>
       </c>
       <c r="C16" s="2">
-        <v>0.65493000000000001</v>
+        <v>0.66935</v>
       </c>
       <c r="D16" s="5">
-        <v>3801.6</v>
+        <v>4302.1400000000003</v>
       </c>
       <c r="F16" s="2"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>4687</v>
+        <v>4979</v>
       </c>
       <c r="B17" s="3">
-        <v>45981</v>
+        <v>46022</v>
       </c>
       <c r="C17" s="2">
-        <v>0.65949000000000002</v>
+        <v>0.66935</v>
       </c>
       <c r="D17" s="5">
-        <v>3941.82</v>
+        <v>4302.1400000000003</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>4596</v>
+        <v>4994</v>
       </c>
       <c r="B18" s="3">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="C18" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.66935</v>
       </c>
       <c r="D18" s="5">
-        <v>3801.6</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>4639</v>
+        <v>4757</v>
       </c>
       <c r="B19" s="3">
-        <v>45989</v>
+        <v>46030</v>
       </c>
       <c r="C19" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D19" s="5">
-        <v>4114.95</v>
+        <v>4066.2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>4704</v>
+        <v>4878</v>
       </c>
       <c r="B20" s="3">
-        <v>45989</v>
+        <v>46030</v>
       </c>
       <c r="C20" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D20" s="5">
-        <v>3801.6</v>
+        <v>3558.75</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>4723</v>
+        <v>4957</v>
       </c>
       <c r="B21" s="3">
-        <v>45989</v>
+        <v>46030</v>
       </c>
       <c r="C21" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D21" s="5">
-        <v>3858.3</v>
+        <v>4302.1400000000003</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>4760</v>
+        <v>4959</v>
       </c>
       <c r="B22" s="3">
-        <v>45989</v>
+        <v>46030</v>
       </c>
       <c r="C22" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D22" s="5">
-        <v>3736.8</v>
+        <v>4105.5</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>4765</v>
+        <v>4960</v>
       </c>
       <c r="B23" s="3">
-        <v>45989</v>
+        <v>46030</v>
       </c>
       <c r="C23" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D23" s="5">
-        <v>3315.6</v>
+        <v>4302.1400000000003</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>4825</v>
+        <v>4980</v>
       </c>
       <c r="B24" s="3">
-        <v>45989</v>
+        <v>46030</v>
       </c>
       <c r="C24" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D24" s="5">
-        <v>4158</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>4829</v>
+        <v>4985</v>
       </c>
       <c r="B25" s="3">
-        <v>45989</v>
+        <v>46030</v>
       </c>
       <c r="C25" s="2">
-        <v>0.65205000000000002</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D25" s="5">
-        <v>3736.8</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>4945</v>
+        <v>4986</v>
       </c>
       <c r="B26" s="3">
-        <v>45989</v>
+        <v>46030</v>
       </c>
       <c r="C26" s="2">
-        <v>0.65332999999999997</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D26" s="5">
-        <v>6734.4</v>
+        <v>4117.92</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>4943</v>
+        <v>4987</v>
       </c>
       <c r="B27" s="3">
-        <v>45989</v>
+        <v>46030</v>
       </c>
       <c r="C27" s="2">
-        <v>0.65322999999999998</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D27" s="5">
-        <v>7470.4</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>4658</v>
+        <v>5006</v>
       </c>
       <c r="B28" s="3">
-        <v>45989</v>
+        <v>46030</v>
       </c>
       <c r="C28" s="2">
-        <v>0.65268999999999999</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D28" s="5">
-        <v>6772.8</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>4659</v>
+        <v>5007</v>
       </c>
       <c r="B29" s="3">
-        <v>45989</v>
+        <v>46030</v>
       </c>
       <c r="C29" s="2">
-        <v>0.65268999999999999</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D29" s="5">
-        <v>13545.6</v>
+        <v>4066.2</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>4666</v>
+        <v>5013</v>
       </c>
       <c r="B30" s="3">
-        <v>45989</v>
+        <v>46030</v>
       </c>
       <c r="C30" s="2">
-        <v>0.65268999999999999</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D30" s="5">
-        <v>6772.8</v>
+        <v>3864</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>4833</v>
+        <v>5023</v>
       </c>
       <c r="B31" s="3">
-        <v>46000</v>
+        <v>46030</v>
       </c>
       <c r="C31" s="2">
-        <v>0.66039000000000003</v>
+        <v>0.67149000000000003</v>
       </c>
       <c r="D31" s="5">
         <v>4158</v>
@@ -908,122 +902,122 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>4834</v>
+        <v>4809</v>
       </c>
       <c r="B32" s="3">
-        <v>46000</v>
+        <v>46030</v>
       </c>
       <c r="C32" s="2">
-        <v>0.66039000000000003</v>
+        <v>0.67181000000000002</v>
       </c>
       <c r="D32" s="5">
-        <v>4158</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>4842</v>
+        <v>4920</v>
       </c>
       <c r="B33" s="3">
-        <v>46002</v>
+        <v>46030</v>
       </c>
       <c r="C33" s="2">
-        <v>0.67545999999999995</v>
+        <v>0.67154999999999998</v>
       </c>
       <c r="D33" s="5">
-        <v>4114.95</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>4868</v>
+        <v>4998</v>
       </c>
       <c r="B34" s="3">
-        <v>46002</v>
+        <v>46030</v>
       </c>
       <c r="C34" s="2">
-        <v>0.66720000000000002</v>
+        <v>0.65098999999999996</v>
       </c>
       <c r="D34" s="5">
-        <v>4158</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>4996</v>
+        <v>5017</v>
       </c>
       <c r="B35" s="3">
-        <v>46002</v>
+        <v>46030</v>
       </c>
       <c r="C35" s="2">
-        <v>0.66720000000000002</v>
+        <v>0.65098999999999996</v>
       </c>
       <c r="D35" s="5">
-        <v>3888.15</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>4830</v>
+        <v>5068</v>
       </c>
       <c r="B36" s="3">
-        <v>46009</v>
+        <v>46030</v>
       </c>
       <c r="C36" s="2">
-        <v>0.65088999999999997</v>
+        <v>0.65098999999999996</v>
       </c>
       <c r="D36" s="5">
-        <v>3647.78</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="2">
-        <v>4840</v>
+      <c r="A37" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="B37" s="3">
-        <v>46009</v>
+        <v>46030</v>
       </c>
       <c r="C37" s="2">
-        <v>0.65088999999999997</v>
+        <v>0.6573</v>
       </c>
       <c r="D37" s="5">
-        <v>4158</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>4874</v>
+        <v>4958</v>
       </c>
       <c r="B38" s="3">
-        <v>46009</v>
+        <v>46030</v>
       </c>
       <c r="C38" s="2">
-        <v>0.65088999999999997</v>
+        <v>0.65086999999999995</v>
       </c>
       <c r="D38" s="5">
-        <v>4414.5</v>
+        <v>4074.3</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>4953</v>
+        <v>4983</v>
       </c>
       <c r="B39" s="3">
-        <v>46009</v>
+        <v>46030</v>
       </c>
       <c r="C39" s="2">
-        <v>0.65088999999999997</v>
+        <v>0.66037000000000001</v>
       </c>
       <c r="D39" s="5">
-        <v>4302.1400000000003</v>
+        <v>3801.75</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>4845</v>
+        <v>5014</v>
       </c>
       <c r="B40" s="3">
-        <v>46009</v>
+        <v>46030</v>
       </c>
       <c r="C40" s="2">
         <v>0.65051999999999999</v>
@@ -1034,209 +1028,209 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>4871</v>
+        <v>5043</v>
       </c>
       <c r="B41" s="3">
-        <v>46009</v>
+        <v>46037</v>
       </c>
       <c r="C41" s="2">
-        <v>0.66720000000000002</v>
+        <v>0.66808000000000001</v>
       </c>
       <c r="D41" s="5">
-        <v>4293</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>4873</v>
+        <v>4970</v>
       </c>
       <c r="B42" s="3">
-        <v>46009</v>
+        <v>46037</v>
       </c>
       <c r="C42" s="2">
-        <v>0.66720000000000002</v>
-      </c>
-      <c r="D42" s="5">
-        <v>4158</v>
+        <v>0.65100000000000002</v>
+      </c>
+      <c r="D42" s="4">
+        <v>4357.16</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>4875</v>
+        <v>5011</v>
       </c>
       <c r="B43" s="3">
-        <v>46009</v>
+        <v>46037</v>
       </c>
       <c r="C43" s="2">
-        <v>0.65949000000000002</v>
-      </c>
-      <c r="D43" s="5">
-        <v>3426.12</v>
+        <v>0.65100000000000002</v>
+      </c>
+      <c r="D43" s="4">
+        <v>4287.6000000000004</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>4876</v>
+        <v>5019</v>
       </c>
       <c r="B44" s="3">
-        <v>46009</v>
+        <v>46037</v>
       </c>
       <c r="C44" s="2">
-        <v>0.66039000000000003</v>
-      </c>
-      <c r="D44" s="5">
-        <v>3801.6</v>
+        <v>0.66796</v>
+      </c>
+      <c r="D44" s="4">
+        <v>4101.45</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>4883</v>
+        <v>5028</v>
       </c>
       <c r="B45" s="3">
-        <v>46022</v>
+        <v>46037</v>
       </c>
       <c r="C45" s="2">
-        <v>0.65081999999999995</v>
-      </c>
-      <c r="D45" s="5">
-        <v>4276.74</v>
+        <v>0.66796</v>
+      </c>
+      <c r="D45" s="4">
+        <v>3979.95</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>4884</v>
+        <v>4968</v>
       </c>
       <c r="B46" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C46" s="2">
-        <v>0.65081999999999995</v>
-      </c>
-      <c r="D46" s="5">
-        <v>4410</v>
+        <v>0.67835000000000001</v>
+      </c>
+      <c r="D46" s="4">
+        <v>4158</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>4885</v>
+        <v>5008</v>
       </c>
       <c r="B47" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C47" s="2">
-        <v>0.65081999999999995</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D47" s="4">
-        <v>4410</v>
+        <v>3888.15</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>4924</v>
+        <v>5029</v>
       </c>
       <c r="B48" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C48" s="2">
-        <v>0.65081999999999995</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D48" s="4">
-        <v>4276.74</v>
+        <v>4279.5</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>4925</v>
+        <v>5032</v>
       </c>
       <c r="B49" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C49" s="2">
-        <v>0.65081999999999995</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D49" s="4">
-        <v>4410</v>
+        <v>4101.45</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>4661</v>
+        <v>5033</v>
       </c>
       <c r="B50" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C50" s="2">
-        <v>0.66910000000000003</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D50" s="4">
-        <v>7293</v>
+        <v>3426.12</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>4662</v>
+        <v>5034</v>
       </c>
       <c r="B51" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C51" s="2">
-        <v>0.66910000000000003</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D51" s="4">
-        <v>7293</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>4663</v>
+        <v>5036</v>
       </c>
       <c r="B52" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C52" s="2">
-        <v>0.66908999999999996</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D52" s="4">
-        <v>14586</v>
+        <v>4114.95</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>4664</v>
+        <v>5037</v>
       </c>
       <c r="B53" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C53" s="2">
-        <v>0.66908999999999996</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D53" s="4">
-        <v>14586</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>4665</v>
+        <v>5038</v>
       </c>
       <c r="B54" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C54" s="2">
-        <v>0.66908999999999996</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D54" s="4">
-        <v>14586</v>
+        <v>4316.72</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>5000</v>
+        <v>5073</v>
       </c>
       <c r="B55" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C55" s="2">
-        <v>0.66918</v>
+        <v>0.67552999999999996</v>
       </c>
       <c r="D55" s="4">
         <v>3801.6</v>
@@ -1244,27 +1238,27 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>5016</v>
+        <v>5074</v>
       </c>
       <c r="B56" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C56" s="2">
-        <v>0.66918</v>
+        <v>0.67552999999999996</v>
       </c>
       <c r="D56" s="4">
-        <v>3801.6</v>
+        <v>7603.2</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>5018</v>
+        <v>5076</v>
       </c>
       <c r="B57" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C57" s="2">
-        <v>0.66918</v>
+        <v>0.67552999999999996</v>
       </c>
       <c r="D57" s="4">
         <v>3801.6</v>
@@ -1272,363 +1266,363 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>4756</v>
+        <v>5070</v>
       </c>
       <c r="B58" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C58" s="2">
-        <v>0.66935</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="D58" s="4">
-        <v>4293</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>4763</v>
+        <v>5071</v>
       </c>
       <c r="B59" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C59" s="2">
-        <v>0.66935</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="D59" s="4">
-        <v>3426.12</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>4828</v>
+        <v>5072</v>
       </c>
       <c r="B60" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C60" s="2">
-        <v>0.66935</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="D60" s="4">
-        <v>3801.6</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>4831</v>
+        <v>5101</v>
       </c>
       <c r="B61" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C61" s="2">
-        <v>0.66935</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="D61" s="4">
-        <v>4374</v>
+        <v>4143.4799999999996</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>4838</v>
+        <v>5102</v>
       </c>
       <c r="B62" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C62" s="2">
-        <v>0.66935</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="D62" s="4">
-        <v>3801.6</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>4843</v>
+        <v>5042</v>
       </c>
       <c r="B63" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C63" s="2">
-        <v>0.66935</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D63" s="4">
-        <v>4158</v>
+        <v>3832.95</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>4844</v>
+        <v>5046</v>
       </c>
       <c r="B64" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C64" s="2">
-        <v>0.66935</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D64" s="4">
-        <v>4279.5</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>4847</v>
+        <v>5047</v>
       </c>
       <c r="B65" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C65" s="2">
-        <v>0.66935</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D65" s="4">
-        <v>4293</v>
+        <v>3888.15</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
-        <v>4870</v>
+        <v>5048</v>
       </c>
       <c r="B66" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C66" s="2">
-        <v>0.66935</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D66" s="4">
-        <v>3847.32</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
-        <v>4926</v>
+        <v>5051</v>
       </c>
       <c r="B67" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C67" s="2">
-        <v>0.66935</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D67" s="4">
-        <v>4293</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
-        <v>4927</v>
+        <v>5052</v>
       </c>
       <c r="B68" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C68" s="2">
-        <v>0.66935</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D68" s="4">
-        <v>4158</v>
+        <v>3888.15</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
-        <v>4928</v>
+        <v>5053</v>
       </c>
       <c r="B69" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C69" s="2">
-        <v>0.66935</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D69" s="4">
-        <v>4428</v>
+        <v>4279.5</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
-        <v>4930</v>
+        <v>5055</v>
       </c>
       <c r="B70" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C70" s="2">
-        <v>0.66935</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D70" s="4">
-        <v>4293</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
-        <v>4946</v>
+        <v>5056</v>
       </c>
       <c r="B71" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C71" s="2">
-        <v>0.66935</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D71" s="4">
-        <v>4232.45</v>
+        <v>3888.15</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
-        <v>4947</v>
+        <v>5057</v>
       </c>
       <c r="B72" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C72" s="2">
-        <v>0.66935</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D72" s="4">
-        <v>4371.84</v>
+        <v>4302.1400000000003</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
-        <v>4948</v>
+        <v>5077</v>
       </c>
       <c r="B73" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C73" s="2">
-        <v>0.66935</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D73" s="4">
-        <v>4302.1400000000003</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
-        <v>4965</v>
+        <v>5138</v>
       </c>
       <c r="B74" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C74" s="2">
-        <v>0.66935</v>
+        <v>0.67835000000000001</v>
       </c>
       <c r="D74" s="4">
-        <v>4212</v>
+        <v>4347</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
-        <v>4966</v>
+        <v>4974</v>
       </c>
       <c r="B75" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C75" s="2">
-        <v>0.66935</v>
+        <v>0.68022000000000005</v>
       </c>
       <c r="D75" s="4">
-        <v>4259.2299999999996</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
-        <v>4969</v>
+        <v>5104</v>
       </c>
       <c r="B76" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C76" s="2">
-        <v>0.66935</v>
+        <v>0.68022000000000005</v>
       </c>
       <c r="D76" s="4">
-        <v>4230</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
-        <v>4971</v>
+        <v>5106</v>
       </c>
       <c r="B77" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C77" s="2">
-        <v>0.66935</v>
+        <v>0.68022000000000005</v>
       </c>
       <c r="D77" s="4">
-        <v>3986.54</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
-        <v>4972</v>
+        <v>4810</v>
       </c>
       <c r="B78" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C78" s="2">
-        <v>0.66935</v>
+        <v>0.68022000000000005</v>
       </c>
       <c r="D78" s="4">
-        <v>4158</v>
+        <v>8751.6</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
-        <v>4979</v>
+        <v>4814</v>
       </c>
       <c r="B79" s="3">
-        <v>46022</v>
+        <v>46044</v>
       </c>
       <c r="C79" s="2">
-        <v>0.66935</v>
+        <v>0.68022000000000005</v>
       </c>
       <c r="D79" s="4">
-        <v>4302.1400000000003</v>
+        <v>8751.6</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
-        <v>4993</v>
+        <v>5096</v>
       </c>
       <c r="B80" s="3">
-        <v>46022</v>
+        <v>46051</v>
       </c>
       <c r="C80" s="2">
-        <v>0.66935</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="D80" s="4">
-        <v>5400</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
-        <v>4994</v>
+        <v>5107</v>
       </c>
       <c r="B81" s="3">
-        <v>46022</v>
+        <v>46051</v>
       </c>
       <c r="C81" s="2">
-        <v>0.66935</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="D81" s="4">
-        <v>5400</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
-        <v>5010</v>
+        <v>5108</v>
       </c>
       <c r="B82" s="3">
-        <v>46022</v>
+        <v>46051</v>
       </c>
       <c r="C82" s="2">
-        <v>0.66935</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="D82" s="4">
-        <v>4266</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
-        <v>4865</v>
+        <v>5110</v>
       </c>
       <c r="B83" s="3">
-        <v>46022</v>
+        <v>46051</v>
       </c>
       <c r="C83" s="2">
-        <v>0.66857</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="D83" s="4">
         <v>3801.6</v>
@@ -1636,237 +1630,237 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
-        <v>4867</v>
+        <v>5166</v>
       </c>
       <c r="B84" s="3">
-        <v>46022</v>
+        <v>46051</v>
       </c>
       <c r="C84" s="2">
-        <v>0.66857</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="D84" s="4">
-        <v>3801.6</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
-        <v>4918</v>
+        <v>5030</v>
       </c>
       <c r="B85" s="3">
-        <v>46022</v>
+        <v>46051</v>
       </c>
       <c r="C85" s="2">
-        <v>0.66857</v>
+        <v>0.70299</v>
       </c>
       <c r="D85" s="4">
-        <v>3801.6</v>
+        <v>4873.5</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
-        <v>4919</v>
+        <v>5058</v>
       </c>
       <c r="B86" s="3">
-        <v>46022</v>
+        <v>46051</v>
       </c>
       <c r="C86" s="2">
-        <v>0.66857</v>
+        <v>0.70299</v>
       </c>
       <c r="D86" s="4">
-        <v>3801.6</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
-        <v>4973</v>
+        <v>5059</v>
       </c>
       <c r="B87" s="3">
-        <v>46022</v>
+        <v>46051</v>
       </c>
       <c r="C87" s="2">
-        <v>0.66857</v>
+        <v>0.70299</v>
       </c>
       <c r="D87" s="4">
-        <v>3801.6</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
-        <v>4644</v>
+        <v>5060</v>
       </c>
       <c r="B88" s="3">
-        <v>46022</v>
+        <v>46051</v>
       </c>
       <c r="C88" s="2">
-        <v>0.66942000000000002</v>
+        <v>0.70299</v>
       </c>
       <c r="D88" s="4">
-        <v>4375.8</v>
+        <v>3801.9</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
-        <v>4645</v>
+        <v>5061</v>
       </c>
       <c r="B89" s="3">
-        <v>46022</v>
+        <v>46051</v>
       </c>
       <c r="C89" s="2">
-        <v>0.66942000000000002</v>
+        <v>0.70299</v>
       </c>
       <c r="D89" s="4">
-        <v>8751.6</v>
+        <v>4187.7</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
-        <v>4647</v>
+        <v>5062</v>
       </c>
       <c r="B90" s="3">
-        <v>46022</v>
+        <v>46051</v>
       </c>
       <c r="C90" s="2">
-        <v>0.66942000000000002</v>
+        <v>0.70299</v>
       </c>
       <c r="D90" s="4">
-        <v>8751.6</v>
+        <v>3315.6</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
-        <v>4649</v>
+        <v>5063</v>
       </c>
       <c r="B91" s="3">
-        <v>46022</v>
+        <v>46051</v>
       </c>
       <c r="C91" s="2">
-        <v>0.66942000000000002</v>
+        <v>0.70299</v>
       </c>
       <c r="D91" s="4">
-        <v>4375.8</v>
+        <v>3700.32</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
-        <v>4808</v>
+        <v>5064</v>
       </c>
       <c r="B92" s="3">
-        <v>46022</v>
+        <v>46051</v>
       </c>
       <c r="C92" s="2">
-        <v>0.66942000000000002</v>
+        <v>0.70299</v>
       </c>
       <c r="D92" s="4">
-        <v>8751.6</v>
+        <v>4299.74</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
-        <v>4757</v>
+        <v>5065</v>
       </c>
       <c r="B93" s="3">
-        <v>46030</v>
+        <v>46051</v>
       </c>
       <c r="C93" s="2">
-        <v>0.67149000000000003</v>
+        <v>0.70299</v>
       </c>
       <c r="D93" s="4">
-        <v>4066.2</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
-        <v>4872</v>
+        <v>5066</v>
       </c>
       <c r="B94" s="3">
-        <v>46030</v>
+        <v>46051</v>
       </c>
       <c r="C94" s="2">
-        <v>0.67149000000000003</v>
+        <v>0.70299</v>
       </c>
       <c r="D94" s="4">
-        <v>4293</v>
+        <v>3558.75</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
-        <v>4878</v>
+        <v>5078</v>
       </c>
       <c r="B95" s="3">
-        <v>46030</v>
+        <v>46051</v>
       </c>
       <c r="C95" s="2">
-        <v>0.67149000000000003</v>
+        <v>0.70299</v>
       </c>
       <c r="D95" s="4">
-        <v>3558.75</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
-        <v>4957</v>
+        <v>5080</v>
       </c>
       <c r="B96" s="3">
-        <v>46030</v>
+        <v>46051</v>
       </c>
       <c r="C96" s="2">
-        <v>0.67149000000000003</v>
+        <v>0.70299</v>
       </c>
       <c r="D96" s="4">
-        <v>4302.1400000000003</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
-        <v>4959</v>
+        <v>5086</v>
       </c>
       <c r="B97" s="3">
-        <v>46030</v>
+        <v>46051</v>
       </c>
       <c r="C97" s="2">
-        <v>0.67149000000000003</v>
+        <v>0.70299</v>
       </c>
       <c r="D97" s="4">
-        <v>4105.5</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
-        <v>4960</v>
+        <v>5088</v>
       </c>
       <c r="B98" s="3">
-        <v>46030</v>
+        <v>46051</v>
       </c>
       <c r="C98" s="2">
-        <v>0.67149000000000003</v>
+        <v>0.70299</v>
       </c>
       <c r="D98" s="4">
-        <v>4302.1400000000003</v>
+        <v>4428</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
-        <v>4961</v>
+        <v>5090</v>
       </c>
       <c r="B99" s="3">
-        <v>46030</v>
+        <v>46051</v>
       </c>
       <c r="C99" s="2">
-        <v>0.67149000000000003</v>
+        <v>0.70299</v>
       </c>
       <c r="D99" s="4">
-        <v>3645</v>
+        <v>4199.58</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
-        <v>4964</v>
+        <v>5093</v>
       </c>
       <c r="B100" s="3">
-        <v>46030</v>
+        <v>46051</v>
       </c>
       <c r="C100" s="2">
-        <v>0.67149000000000003</v>
+        <v>0.70299</v>
       </c>
       <c r="D100" s="4">
         <v>4158</v>
@@ -1874,321 +1868,321 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
-        <v>4980</v>
+        <v>5095</v>
       </c>
       <c r="B101" s="3">
-        <v>46030</v>
+        <v>46051</v>
       </c>
       <c r="C101" s="2">
-        <v>0.67149000000000003</v>
+        <v>0.70299</v>
       </c>
       <c r="D101" s="4">
-        <v>3979.95</v>
+        <v>4150.32</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
-        <v>4984</v>
+        <v>4962</v>
       </c>
       <c r="B102" s="3">
-        <v>46030</v>
+        <v>46051</v>
       </c>
       <c r="C102" s="2">
-        <v>0.67149000000000003</v>
+        <v>0.78613999999999995</v>
       </c>
       <c r="D102" s="4">
-        <v>3558.6</v>
+        <v>9981.5</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
-        <v>4985</v>
+        <v>5081</v>
       </c>
       <c r="B103" s="3">
-        <v>46030</v>
+        <v>46058</v>
       </c>
       <c r="C103" s="2">
-        <v>0.67149000000000003</v>
+        <v>0.66935</v>
       </c>
       <c r="D103" s="4">
-        <v>3979.95</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
-        <v>4986</v>
+        <v>5082</v>
       </c>
       <c r="B104" s="3">
-        <v>46030</v>
+        <v>46058</v>
       </c>
       <c r="C104" s="2">
-        <v>0.67149000000000003</v>
+        <v>0.65952</v>
       </c>
       <c r="D104" s="4">
-        <v>4117.92</v>
+        <v>4158.1499999999996</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
-        <v>4987</v>
+        <v>4899</v>
       </c>
       <c r="B105" s="3">
-        <v>46030</v>
+        <v>46058</v>
       </c>
       <c r="C105" s="2">
-        <v>0.67149000000000003</v>
+        <v>0.69811999999999996</v>
       </c>
       <c r="D105" s="4">
-        <v>3979.95</v>
+        <v>8751.6</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
-        <v>5006</v>
+        <v>4900</v>
       </c>
       <c r="B106" s="3">
-        <v>46030</v>
+        <v>46058</v>
       </c>
       <c r="C106" s="2">
-        <v>0.67149000000000003</v>
+        <v>0.69811999999999996</v>
       </c>
       <c r="D106" s="4">
-        <v>3979.95</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
-        <v>5007</v>
+        <v>4975</v>
       </c>
       <c r="B107" s="3">
-        <v>46030</v>
+        <v>46058</v>
       </c>
       <c r="C107" s="2">
-        <v>0.67149000000000003</v>
+        <v>0.69930000000000003</v>
       </c>
       <c r="D107" s="4">
-        <v>4066.2</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
-        <v>5013</v>
+        <v>5087</v>
       </c>
       <c r="B108" s="3">
-        <v>46030</v>
+        <v>46058</v>
       </c>
       <c r="C108" s="2">
-        <v>0.67149000000000003</v>
+        <v>0.69937000000000005</v>
       </c>
       <c r="D108" s="4">
-        <v>3864</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
-        <v>5023</v>
+        <v>5091</v>
       </c>
       <c r="B109" s="3">
-        <v>46030</v>
+        <v>46058</v>
       </c>
       <c r="C109" s="2">
-        <v>0.67149000000000003</v>
+        <v>0.69937000000000005</v>
       </c>
       <c r="D109" s="4">
-        <v>4158</v>
+        <v>4282.38</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
-        <v>5025</v>
+        <v>5094</v>
       </c>
       <c r="B110" s="3">
-        <v>46030</v>
+        <v>46058</v>
       </c>
       <c r="C110" s="2">
-        <v>0.67149000000000003</v>
+        <v>0.69937000000000005</v>
       </c>
       <c r="D110" s="4">
-        <v>3979.95</v>
+        <v>4303.92</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
-        <v>4807</v>
+        <v>5098</v>
       </c>
       <c r="B111" s="3">
-        <v>46030</v>
+        <v>46058</v>
       </c>
       <c r="C111" s="2">
-        <v>0.67181000000000002</v>
+        <v>0.69937000000000005</v>
       </c>
       <c r="D111" s="4">
-        <v>4375.8</v>
+        <v>4277.7</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
-        <v>4809</v>
+        <v>5103</v>
       </c>
       <c r="B112" s="3">
-        <v>46030</v>
+        <v>46058</v>
       </c>
       <c r="C112" s="2">
-        <v>0.67181000000000002</v>
+        <v>0.69937000000000005</v>
       </c>
       <c r="D112" s="4">
-        <v>4375.8</v>
+        <v>4333.5</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
-        <v>4920</v>
+        <v>5105</v>
       </c>
       <c r="B113" s="3">
-        <v>46030</v>
+        <v>46058</v>
       </c>
       <c r="C113" s="2">
-        <v>0.67154999999999998</v>
+        <v>0.69937000000000005</v>
       </c>
       <c r="D113" s="4">
-        <v>3801.6</v>
+        <v>4099.68</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
-        <v>4921</v>
+        <v>5127</v>
       </c>
       <c r="B114" s="3">
-        <v>46030</v>
+        <v>46058</v>
       </c>
       <c r="C114" s="2">
-        <v>0.67154999999999998</v>
+        <v>0.69937000000000005</v>
       </c>
       <c r="D114" s="4">
-        <v>3801.6</v>
+        <v>4156.4399999999996</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
-        <v>5020</v>
+        <v>5083</v>
       </c>
       <c r="B115" s="3">
-        <v>46030</v>
+        <v>46058</v>
       </c>
       <c r="C115" s="2">
-        <v>0.67154999999999998</v>
+        <v>0.66152999999999995</v>
       </c>
       <c r="D115" s="4">
-        <v>3801.6</v>
+        <v>4114.95</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
-        <v>5022</v>
+        <v>5084</v>
       </c>
       <c r="B116" s="3">
-        <v>46030</v>
+        <v>46058</v>
       </c>
       <c r="C116" s="2">
-        <v>0.67154999999999998</v>
+        <v>0.66152999999999995</v>
       </c>
       <c r="D116" s="4">
-        <v>7603.2</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
-        <v>5041</v>
+        <v>5085</v>
       </c>
       <c r="B117" s="3">
-        <v>46030</v>
+        <v>46058</v>
       </c>
       <c r="C117" s="2">
-        <v>0.67154999999999998</v>
+        <v>0.66152999999999995</v>
       </c>
       <c r="D117" s="4">
-        <v>3801.6</v>
+        <v>3873</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
-        <v>4998</v>
+        <v>5097</v>
       </c>
       <c r="B118" s="3">
-        <v>46030</v>
+        <v>46058</v>
       </c>
       <c r="C118" s="2">
-        <v>0.65098999999999996</v>
+        <v>0.66152999999999995</v>
       </c>
       <c r="D118" s="4">
-        <v>4410</v>
+        <v>4206.6000000000004</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
-        <v>5015</v>
+        <v>5099</v>
       </c>
       <c r="B119" s="3">
-        <v>46030</v>
+        <v>46058</v>
       </c>
       <c r="C119" s="2">
-        <v>0.65098999999999996</v>
+        <v>0.66152999999999995</v>
       </c>
       <c r="D119" s="4">
-        <v>4410</v>
+        <v>4044.09</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A120" s="2">
-        <v>5017</v>
+        <v>5115</v>
       </c>
       <c r="B120" s="3">
-        <v>46030</v>
+        <v>46058</v>
       </c>
       <c r="C120" s="2">
-        <v>0.65098999999999996</v>
+        <v>0.66152999999999995</v>
       </c>
       <c r="D120" s="4">
-        <v>4410</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
-        <v>5067</v>
+        <v>5116</v>
       </c>
       <c r="B121" s="3">
-        <v>46030</v>
+        <v>46058</v>
       </c>
       <c r="C121" s="2">
-        <v>0.65098999999999996</v>
+        <v>0.66152999999999995</v>
       </c>
       <c r="D121" s="4">
-        <v>4257</v>
+        <v>4114.95</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122" s="2">
-        <v>5068</v>
+        <v>5117</v>
       </c>
       <c r="B122" s="3">
-        <v>46030</v>
+        <v>46058</v>
       </c>
       <c r="C122" s="2">
-        <v>0.65098999999999996</v>
+        <v>0.66152999999999995</v>
       </c>
       <c r="D122" s="4">
-        <v>4257</v>
+        <v>4066.2</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123" s="2">
-        <v>4702</v>
+        <v>5155</v>
       </c>
       <c r="B123" s="3">
-        <v>46030</v>
+        <v>46065</v>
       </c>
       <c r="C123" s="2">
-        <v>0.6573</v>
+        <v>0.71289000000000002</v>
       </c>
       <c r="D123" s="4">
         <v>3801.6</v>
@@ -2196,282 +2190,282 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124" s="2">
-        <v>4958</v>
+        <v>5159</v>
       </c>
       <c r="B124" s="3">
-        <v>46030</v>
+        <v>46065</v>
       </c>
       <c r="C124" s="2">
-        <v>0.65086999999999995</v>
+        <v>0.71289000000000002</v>
       </c>
       <c r="D124" s="4">
-        <v>4074.3</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125" s="2">
-        <v>4983</v>
+        <v>5185</v>
       </c>
       <c r="B125" s="3">
-        <v>46030</v>
+        <v>46065</v>
       </c>
       <c r="C125" s="2">
-        <v>0.66037000000000001</v>
+        <v>0.71289000000000002</v>
       </c>
       <c r="D125" s="4">
-        <v>3801.75</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A126" s="2">
-        <v>4997</v>
+        <v>5186</v>
       </c>
       <c r="B126" s="3">
-        <v>46030</v>
+        <v>46065</v>
       </c>
       <c r="C126" s="2">
-        <v>0.66039000000000003</v>
+        <v>0.71289000000000002</v>
       </c>
       <c r="D126" s="4">
-        <v>3801.9</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127" s="2">
-        <v>5004</v>
+        <v>4898</v>
       </c>
       <c r="B127" s="3">
-        <v>46030</v>
+        <v>46065</v>
       </c>
       <c r="C127" s="2">
-        <v>0.65952</v>
+        <v>0.71289000000000002</v>
       </c>
       <c r="D127" s="4">
-        <v>3801.75</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128" s="2">
-        <v>5014</v>
+        <v>4902</v>
       </c>
       <c r="B128" s="3">
-        <v>46030</v>
+        <v>46065</v>
       </c>
       <c r="C128" s="2">
-        <v>0.65051999999999999</v>
+        <v>0.71289000000000002</v>
       </c>
       <c r="D128" s="4">
-        <v>3801.6</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" s="2">
-        <v>5043</v>
+        <v>4903</v>
       </c>
       <c r="B129" s="3">
-        <v>46037</v>
+        <v>46065</v>
       </c>
       <c r="C129" s="2">
-        <v>0.66808000000000001</v>
+        <v>0.71289000000000002</v>
       </c>
       <c r="D129" s="4">
-        <v>3801.6</v>
+        <v>8751.6</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130" s="2">
-        <v>5044</v>
+        <v>4904</v>
       </c>
       <c r="B130" s="3">
-        <v>46037</v>
+        <v>46065</v>
       </c>
       <c r="C130" s="2">
-        <v>0.66808000000000001</v>
+        <v>0.71289000000000002</v>
       </c>
       <c r="D130" s="4">
-        <v>3801.6</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" s="2">
-        <v>4967</v>
+        <v>4906</v>
       </c>
       <c r="B131" s="3">
-        <v>46037</v>
+        <v>46065</v>
       </c>
       <c r="C131" s="2">
-        <v>0.65100000000000002</v>
+        <v>0.71289000000000002</v>
       </c>
       <c r="D131" s="4">
-        <v>4331.46</v>
+        <v>8751.6</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" s="2">
-        <v>4970</v>
+        <v>5241</v>
       </c>
       <c r="B132" s="3">
-        <v>46037</v>
+        <v>46065</v>
       </c>
       <c r="C132" s="2">
-        <v>0.65100000000000002</v>
+        <v>0.71272000000000002</v>
       </c>
       <c r="D132" s="4">
-        <v>4357.16</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A133" s="2">
-        <v>5011</v>
+        <v>5153</v>
       </c>
       <c r="B133" s="3">
-        <v>46037</v>
+        <v>46065</v>
       </c>
       <c r="C133" s="2">
-        <v>0.65100000000000002</v>
+        <v>0.71289000000000002</v>
       </c>
       <c r="D133" s="4">
-        <v>4287.6000000000004</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A134" s="2">
-        <v>5019</v>
+        <v>5154</v>
       </c>
       <c r="B134" s="3">
-        <v>46037</v>
+        <v>46065</v>
       </c>
       <c r="C134" s="2">
-        <v>0.66796</v>
+        <v>0.71289000000000002</v>
       </c>
       <c r="D134" s="4">
-        <v>4101.45</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A135" s="2">
-        <v>5028</v>
+        <v>5157</v>
       </c>
       <c r="B135" s="3">
-        <v>46037</v>
+        <v>46065</v>
       </c>
       <c r="C135" s="2">
-        <v>0.66796</v>
+        <v>0.71289000000000002</v>
       </c>
       <c r="D135" s="4">
-        <v>3979.95</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A136" s="2">
-        <v>4968</v>
+        <v>5158</v>
       </c>
       <c r="B136" s="3">
-        <v>46044</v>
+        <v>46065</v>
       </c>
       <c r="C136" s="2">
-        <v>0.67835000000000001</v>
+        <v>0.71289000000000002</v>
       </c>
       <c r="D136" s="4">
-        <v>4158</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A137" s="2">
-        <v>5008</v>
+        <v>9</v>
       </c>
       <c r="B137" s="3">
-        <v>46044</v>
+        <v>46068</v>
       </c>
       <c r="C137" s="2">
-        <v>0.67835000000000001</v>
+        <v>0.70735000000000003</v>
       </c>
       <c r="D137" s="4">
-        <v>3888.15</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138" s="2">
-        <v>5029</v>
+        <v>10</v>
       </c>
       <c r="B138" s="3">
-        <v>46044</v>
+        <v>46068</v>
       </c>
       <c r="C138" s="2">
-        <v>0.67835000000000001</v>
+        <v>0.70735000000000003</v>
       </c>
       <c r="D138" s="4">
-        <v>4279.5</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A139" s="2">
-        <v>5032</v>
+        <v>5118</v>
       </c>
       <c r="B139" s="3">
-        <v>46044</v>
+        <v>46072</v>
       </c>
       <c r="C139" s="2">
-        <v>0.67835000000000001</v>
+        <v>0.70647000000000004</v>
       </c>
       <c r="D139" s="4">
-        <v>4101.45</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A140" s="2">
-        <v>5033</v>
+        <v>5228</v>
       </c>
       <c r="B140" s="3">
-        <v>46044</v>
+        <v>46072</v>
       </c>
       <c r="C140" s="2">
-        <v>0.67835000000000001</v>
+        <v>0.70647000000000004</v>
       </c>
       <c r="D140" s="4">
-        <v>3426.12</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A141" s="2">
-        <v>5034</v>
+        <v>4897</v>
       </c>
       <c r="B141" s="3">
-        <v>46044</v>
+        <v>46072</v>
       </c>
       <c r="C141" s="2">
-        <v>0.67835000000000001</v>
+        <v>0.70418000000000003</v>
       </c>
       <c r="D141" s="4">
-        <v>4158</v>
+        <v>8751.6</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142" s="2">
-        <v>5035</v>
+        <v>4988</v>
       </c>
       <c r="B142" s="3">
-        <v>46044</v>
+        <v>46079</v>
       </c>
       <c r="C142" s="2">
-        <v>0.67835000000000001</v>
+        <v>0.71192</v>
       </c>
       <c r="D142" s="4">
-        <v>3979.95</v>
+        <v>9752</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143" s="2">
-        <v>5036</v>
+        <v>4901</v>
       </c>
       <c r="B143" s="3">
-        <v>46044</v>
+        <v>46079</v>
       </c>
       <c r="C143" s="2">
-        <v>0.67835000000000001</v>
+        <v>0.71162999999999998</v>
       </c>
       <c r="D143" s="4">
-        <v>4114.95</v>
+        <v>8751.6</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" s="2"/>
@@ -2481,1011 +2475,555 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A144" s="2">
-        <v>5037</v>
+        <v>4905</v>
       </c>
       <c r="B144" s="3">
-        <v>46044</v>
+        <v>46079</v>
       </c>
       <c r="C144" s="2">
-        <v>0.67835000000000001</v>
+        <v>0.71162999999999998</v>
       </c>
       <c r="D144" s="4">
-        <v>3979.95</v>
+        <v>8751.6</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A145" s="2">
-        <v>5038</v>
+        <v>4908</v>
       </c>
       <c r="B145" s="3">
-        <v>46044</v>
+        <v>46079</v>
       </c>
       <c r="C145" s="2">
-        <v>0.67835000000000001</v>
+        <v>0.71162999999999998</v>
       </c>
       <c r="D145" s="4">
-        <v>4316.72</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146" s="2">
-        <v>5073</v>
+        <v>5089</v>
       </c>
       <c r="B146" s="3">
-        <v>46044</v>
+        <v>46079</v>
       </c>
       <c r="C146" s="2">
-        <v>0.67552999999999996</v>
+        <v>0.66139999999999999</v>
       </c>
       <c r="D146" s="4">
-        <v>3801.6</v>
+        <v>3950.56</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147" s="2">
-        <v>5074</v>
+        <v>5092</v>
       </c>
       <c r="B147" s="3">
-        <v>46044</v>
+        <v>46079</v>
       </c>
       <c r="C147" s="2">
-        <v>0.67552999999999996</v>
+        <v>0.66139999999999999</v>
       </c>
       <c r="D147" s="4">
-        <v>7603.2</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A148" s="2">
-        <v>5076</v>
+        <v>5113</v>
       </c>
       <c r="B148" s="3">
-        <v>46044</v>
+        <v>46079</v>
       </c>
       <c r="C148" s="2">
-        <v>0.67552999999999996</v>
+        <v>0.66139999999999999</v>
       </c>
       <c r="D148" s="4">
-        <v>3801.6</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A149" s="2">
-        <v>5069</v>
+        <v>5119</v>
       </c>
       <c r="B149" s="3">
-        <v>46044</v>
+        <v>46079</v>
       </c>
       <c r="C149" s="2">
-        <v>0.65100000000000002</v>
+        <v>0.66139999999999999</v>
       </c>
       <c r="D149" s="4">
-        <v>4143.4799999999996</v>
+        <v>4114.95</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A150" s="2">
-        <v>5070</v>
+        <v>5123</v>
       </c>
       <c r="B150" s="3">
-        <v>46044</v>
+        <v>46079</v>
       </c>
       <c r="C150" s="2">
-        <v>0.65100000000000002</v>
+        <v>0.66139999999999999</v>
       </c>
       <c r="D150" s="4">
-        <v>4410</v>
+        <v>3888.15</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A151" s="2">
-        <v>5071</v>
+        <v>5160</v>
       </c>
       <c r="B151" s="3">
-        <v>46044</v>
+        <v>46079</v>
       </c>
       <c r="C151" s="2">
-        <v>0.65100000000000002</v>
+        <v>0.66139999999999999</v>
       </c>
       <c r="D151" s="4">
-        <v>4257</v>
+        <v>3801.9</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A152" s="2">
-        <v>5072</v>
+        <v>5229</v>
       </c>
       <c r="B152" s="3">
-        <v>46044</v>
+        <v>46079</v>
       </c>
       <c r="C152" s="2">
-        <v>0.65100000000000002</v>
+        <v>0.66139999999999999</v>
       </c>
       <c r="D152" s="4">
-        <v>4410</v>
+        <v>4252.5</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A153" s="2">
-        <v>5101</v>
+        <v>5230</v>
       </c>
       <c r="B153" s="3">
-        <v>46044</v>
+        <v>46079</v>
       </c>
       <c r="C153" s="2">
-        <v>0.65100000000000002</v>
+        <v>0.66139999999999999</v>
       </c>
       <c r="D153" s="4">
-        <v>4143.4799999999996</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A154" s="2">
-        <v>5102</v>
+        <v>5231</v>
       </c>
       <c r="B154" s="3">
-        <v>46044</v>
+        <v>46079</v>
       </c>
       <c r="C154" s="2">
-        <v>0.65100000000000002</v>
+        <v>0.66139999999999999</v>
       </c>
       <c r="D154" s="4">
-        <v>4257</v>
+        <v>3801.9</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A155" s="2">
-        <v>5042</v>
+        <v>4909</v>
       </c>
       <c r="B155" s="3">
-        <v>46044</v>
+        <v>46079</v>
       </c>
       <c r="C155" s="2">
-        <v>0.67835000000000001</v>
+        <v>0.71162999999999998</v>
       </c>
       <c r="D155" s="4">
-        <v>3832.95</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A156" s="2">
-        <v>5046</v>
+        <v>5281</v>
       </c>
       <c r="B156" s="3">
-        <v>46044</v>
+        <v>46079</v>
       </c>
       <c r="C156" s="2">
-        <v>0.67835000000000001</v>
+        <v>0.71162999999999998</v>
       </c>
       <c r="D156" s="4">
-        <v>4293</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A157" s="2">
-        <v>5047</v>
+        <v>4855</v>
       </c>
       <c r="B157" s="3">
-        <v>46044</v>
+        <v>46022</v>
       </c>
       <c r="C157" s="2">
-        <v>0.67835000000000001</v>
+        <v>0.65081</v>
       </c>
       <c r="D157" s="4">
-        <v>3888.15</v>
+        <v>14586</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A158" s="2">
-        <v>5048</v>
+        <v>5045</v>
       </c>
       <c r="B158" s="3">
-        <v>46044</v>
+        <v>46079</v>
       </c>
       <c r="C158" s="2">
-        <v>0.67835000000000001</v>
+        <v>0.71177999999999997</v>
       </c>
       <c r="D158" s="4">
-        <v>4158</v>
+        <v>15444</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A159" s="2">
-        <v>5051</v>
-      </c>
-      <c r="B159" s="3">
-        <v>46044</v>
-      </c>
-      <c r="C159" s="2">
-        <v>0.67835000000000001</v>
-      </c>
-      <c r="D159" s="4">
-        <v>4158</v>
-      </c>
+      <c r="A159" s="2"/>
+      <c r="B159" s="3"/>
+      <c r="C159" s="2"/>
+      <c r="D159" s="4"/>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A160" s="2">
-        <v>5052</v>
-      </c>
-      <c r="B160" s="3">
-        <v>46044</v>
-      </c>
-      <c r="C160" s="2">
-        <v>0.67835000000000001</v>
-      </c>
-      <c r="D160" s="4">
-        <v>3888.15</v>
-      </c>
+      <c r="A160" s="2"/>
+      <c r="B160" s="3"/>
+      <c r="C160" s="2"/>
+      <c r="D160" s="4"/>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A161" s="2">
-        <v>5053</v>
-      </c>
-      <c r="B161" s="3">
-        <v>46044</v>
-      </c>
-      <c r="C161" s="2">
-        <v>0.67835000000000001</v>
-      </c>
-      <c r="D161" s="4">
-        <v>4279.5</v>
-      </c>
+      <c r="A161" s="2"/>
+      <c r="B161" s="3"/>
+      <c r="C161" s="2"/>
+      <c r="D161" s="4"/>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A162" s="2">
-        <v>5054</v>
-      </c>
-      <c r="B162" s="3">
-        <v>46044</v>
-      </c>
-      <c r="C162" s="2">
-        <v>0.67835000000000001</v>
-      </c>
-      <c r="D162" s="4">
-        <v>3979.95</v>
-      </c>
+      <c r="A162" s="2"/>
+      <c r="B162" s="3"/>
+      <c r="C162" s="2"/>
+      <c r="D162" s="4"/>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A163" s="2">
-        <v>5055</v>
-      </c>
-      <c r="B163" s="3">
-        <v>46044</v>
-      </c>
-      <c r="C163" s="2">
-        <v>0.67835000000000001</v>
-      </c>
-      <c r="D163" s="4">
-        <v>3979.95</v>
-      </c>
+      <c r="A163" s="2"/>
+      <c r="B163" s="3"/>
+      <c r="C163" s="2"/>
+      <c r="D163" s="4"/>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A164" s="2">
-        <v>5056</v>
-      </c>
-      <c r="B164" s="3">
-        <v>46044</v>
-      </c>
-      <c r="C164" s="2">
-        <v>0.67835000000000001</v>
-      </c>
-      <c r="D164" s="4">
-        <v>3888.15</v>
-      </c>
+      <c r="A164" s="2"/>
+      <c r="B164" s="3"/>
+      <c r="C164" s="2"/>
+      <c r="D164" s="4"/>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A165" s="2">
-        <v>5057</v>
-      </c>
-      <c r="B165" s="3">
-        <v>46044</v>
-      </c>
-      <c r="C165" s="2">
-        <v>0.67835000000000001</v>
-      </c>
-      <c r="D165" s="4">
-        <v>4302.1400000000003</v>
-      </c>
+      <c r="A165" s="2"/>
+      <c r="B165" s="3"/>
+      <c r="C165" s="2"/>
+      <c r="D165" s="4"/>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A166" s="2">
-        <v>5077</v>
-      </c>
-      <c r="B166" s="3">
-        <v>46044</v>
-      </c>
-      <c r="C166" s="2">
-        <v>0.67835000000000001</v>
-      </c>
-      <c r="D166" s="4">
-        <v>4158</v>
-      </c>
+      <c r="A166" s="2"/>
+      <c r="B166" s="3"/>
+      <c r="C166" s="2"/>
+      <c r="D166" s="4"/>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A167" s="2">
-        <v>5138</v>
-      </c>
-      <c r="B167" s="3">
-        <v>46044</v>
-      </c>
-      <c r="C167" s="2">
-        <v>0.67835000000000001</v>
-      </c>
-      <c r="D167" s="4">
-        <v>4347</v>
-      </c>
+      <c r="A167" s="2"/>
+      <c r="B167" s="3"/>
+      <c r="C167" s="2"/>
+      <c r="D167" s="4"/>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A168" s="2">
-        <v>4974</v>
-      </c>
-      <c r="B168" s="3">
-        <v>46044</v>
-      </c>
-      <c r="C168" s="2">
-        <v>0.68022000000000005</v>
-      </c>
-      <c r="D168" s="4">
-        <v>3801.6</v>
-      </c>
+      <c r="A168" s="2"/>
+      <c r="B168" s="3"/>
+      <c r="C168" s="2"/>
+      <c r="D168" s="4"/>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A169" s="2">
-        <v>5104</v>
-      </c>
-      <c r="B169" s="3">
-        <v>46044</v>
-      </c>
-      <c r="C169" s="2">
-        <v>0.68022000000000005</v>
-      </c>
-      <c r="D169" s="4">
-        <v>3801.6</v>
-      </c>
+      <c r="A169" s="2"/>
+      <c r="B169" s="3"/>
+      <c r="C169" s="2"/>
+      <c r="D169" s="4"/>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A170" s="2">
-        <v>5106</v>
-      </c>
-      <c r="B170" s="3">
-        <v>46044</v>
-      </c>
-      <c r="C170" s="2">
-        <v>0.68022000000000005</v>
-      </c>
-      <c r="D170" s="4">
-        <v>3801.6</v>
-      </c>
+      <c r="A170" s="2"/>
+      <c r="B170" s="3"/>
+      <c r="C170" s="2"/>
+      <c r="D170" s="4"/>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A171" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B171" s="3">
-        <v>46044</v>
-      </c>
-      <c r="C171" s="2">
-        <v>0.68022000000000005</v>
-      </c>
-      <c r="D171" s="4">
-        <v>1843</v>
-      </c>
+      <c r="A171" s="2"/>
+      <c r="B171" s="3"/>
+      <c r="C171" s="2"/>
+      <c r="D171" s="4"/>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A172" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B172" s="3">
-        <v>46044</v>
-      </c>
-      <c r="C172" s="2">
-        <v>0.68022000000000005</v>
-      </c>
-      <c r="D172" s="4">
-        <v>1843</v>
-      </c>
+      <c r="A172" s="2"/>
+      <c r="B172" s="3"/>
+      <c r="C172" s="2"/>
+      <c r="D172" s="4"/>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A173" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B173" s="3">
-        <v>46044</v>
-      </c>
-      <c r="C173" s="2">
-        <v>0.68022000000000005</v>
-      </c>
-      <c r="D173" s="4">
-        <v>2418.3000000000002</v>
-      </c>
+      <c r="A173" s="2"/>
+      <c r="B173" s="3"/>
+      <c r="C173" s="2"/>
+      <c r="D173" s="4"/>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A174" s="2">
-        <v>4810</v>
-      </c>
-      <c r="B174" s="3">
-        <v>46044</v>
-      </c>
-      <c r="C174" s="2">
-        <v>0.68022000000000005</v>
-      </c>
-      <c r="D174" s="4">
-        <v>8751.6</v>
-      </c>
+      <c r="A174" s="2"/>
+      <c r="B174" s="3"/>
+      <c r="C174" s="2"/>
+      <c r="D174" s="4"/>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A175" s="2">
-        <v>4811</v>
-      </c>
-      <c r="B175" s="3">
-        <v>46044</v>
-      </c>
-      <c r="C175" s="2">
-        <v>0.68022000000000005</v>
-      </c>
-      <c r="D175" s="4">
-        <v>4375.8</v>
-      </c>
+      <c r="A175" s="2"/>
+      <c r="B175" s="3"/>
+      <c r="C175" s="2"/>
+      <c r="D175" s="4"/>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A176" s="2">
-        <v>4812</v>
-      </c>
-      <c r="B176" s="3">
-        <v>46044</v>
-      </c>
-      <c r="C176" s="2">
-        <v>0.68022000000000005</v>
-      </c>
-      <c r="D176" s="4">
-        <v>8751.6</v>
-      </c>
+      <c r="A176" s="2"/>
+      <c r="B176" s="3"/>
+      <c r="C176" s="2"/>
+      <c r="D176" s="4"/>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A177" s="2">
-        <v>4813</v>
-      </c>
-      <c r="B177" s="3">
-        <v>46044</v>
-      </c>
-      <c r="C177" s="2">
-        <v>0.68022000000000005</v>
-      </c>
-      <c r="D177" s="4">
-        <v>4375.8</v>
-      </c>
+      <c r="A177" s="2"/>
+      <c r="B177" s="3"/>
+      <c r="C177" s="2"/>
+      <c r="D177" s="4"/>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A178" s="2">
-        <v>4814</v>
-      </c>
-      <c r="B178" s="3">
-        <v>46044</v>
-      </c>
-      <c r="C178" s="2">
-        <v>0.68022000000000005</v>
-      </c>
-      <c r="D178" s="4">
-        <v>8751.6</v>
-      </c>
+      <c r="A178" s="2"/>
+      <c r="B178" s="3"/>
+      <c r="C178" s="2"/>
+      <c r="D178" s="4"/>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A179" s="2">
-        <v>4815</v>
-      </c>
-      <c r="B179" s="3">
-        <v>46044</v>
-      </c>
-      <c r="C179" s="2">
-        <v>0.68022000000000005</v>
-      </c>
-      <c r="D179" s="4">
-        <v>4375.8</v>
-      </c>
+      <c r="A179" s="2"/>
+      <c r="B179" s="3"/>
+      <c r="C179" s="2"/>
+      <c r="D179" s="4"/>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A180" s="2">
-        <v>4816</v>
-      </c>
-      <c r="B180" s="3">
-        <v>46044</v>
-      </c>
-      <c r="C180" s="2">
-        <v>0.68022000000000005</v>
-      </c>
-      <c r="D180" s="4">
-        <v>8751.6</v>
-      </c>
+      <c r="A180" s="2"/>
+      <c r="B180" s="3"/>
+      <c r="C180" s="2"/>
+      <c r="D180" s="4"/>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A181" s="2">
-        <v>5096</v>
-      </c>
-      <c r="B181" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C181" s="2">
-        <v>0.65100000000000002</v>
-      </c>
-      <c r="D181" s="4">
-        <v>3801.6</v>
-      </c>
+      <c r="A181" s="2"/>
+      <c r="B181" s="3"/>
+      <c r="C181" s="2"/>
+      <c r="D181" s="4"/>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A182" s="2">
-        <v>5107</v>
-      </c>
-      <c r="B182" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C182" s="2">
-        <v>0.65100000000000002</v>
-      </c>
-      <c r="D182" s="4">
-        <v>3801.6</v>
-      </c>
+      <c r="A182" s="2"/>
+      <c r="B182" s="3"/>
+      <c r="C182" s="2"/>
+      <c r="D182" s="4"/>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A183" s="2">
-        <v>5108</v>
-      </c>
-      <c r="B183" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C183" s="2">
-        <v>0.65100000000000002</v>
-      </c>
-      <c r="D183" s="4">
-        <v>3801.6</v>
-      </c>
+      <c r="A183" s="2"/>
+      <c r="B183" s="3"/>
+      <c r="C183" s="2"/>
+      <c r="D183" s="4"/>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A184" s="2">
-        <v>5110</v>
-      </c>
-      <c r="B184" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C184" s="2">
-        <v>0.65100000000000002</v>
-      </c>
-      <c r="D184" s="4">
-        <v>3801.6</v>
-      </c>
+      <c r="A184" s="2"/>
+      <c r="B184" s="3"/>
+      <c r="C184" s="2"/>
+      <c r="D184" s="4"/>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A185" s="2">
-        <v>5166</v>
-      </c>
-      <c r="B185" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C185" s="2">
-        <v>0.65100000000000002</v>
-      </c>
-      <c r="D185" s="4">
-        <v>2700</v>
-      </c>
+      <c r="A185" s="2"/>
+      <c r="B185" s="3"/>
+      <c r="C185" s="2"/>
+      <c r="D185" s="4"/>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A186" s="2">
-        <v>5030</v>
-      </c>
-      <c r="B186" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C186" s="2">
-        <v>0.70299</v>
-      </c>
-      <c r="D186" s="4">
-        <v>4873.5</v>
-      </c>
+      <c r="A186" s="2"/>
+      <c r="B186" s="3"/>
+      <c r="C186" s="2"/>
+      <c r="D186" s="4"/>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A187" s="2">
-        <v>5058</v>
-      </c>
-      <c r="B187" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C187" s="2">
-        <v>0.70299</v>
-      </c>
-      <c r="D187" s="4">
-        <v>3979.95</v>
-      </c>
+      <c r="A187" s="2"/>
+      <c r="B187" s="3"/>
+      <c r="C187" s="2"/>
+      <c r="D187" s="4"/>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A188" s="2">
-        <v>5059</v>
-      </c>
-      <c r="B188" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C188" s="2">
-        <v>0.70299</v>
-      </c>
-      <c r="D188" s="4">
-        <v>4293</v>
-      </c>
+      <c r="A188" s="2"/>
+      <c r="B188" s="3"/>
+      <c r="C188" s="2"/>
+      <c r="D188" s="4"/>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A189" s="2">
-        <v>5060</v>
-      </c>
-      <c r="B189" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C189" s="2">
-        <v>0.70299</v>
-      </c>
-      <c r="D189" s="4">
-        <v>3801.9</v>
-      </c>
+      <c r="A189" s="2"/>
+      <c r="B189" s="3"/>
+      <c r="C189" s="2"/>
+      <c r="D189" s="4"/>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A190" s="2">
-        <v>5061</v>
-      </c>
-      <c r="B190" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C190" s="2">
-        <v>0.70299</v>
-      </c>
-      <c r="D190" s="4">
-        <v>4187.7</v>
-      </c>
+      <c r="A190" s="2"/>
+      <c r="B190" s="3"/>
+      <c r="C190" s="2"/>
+      <c r="D190" s="4"/>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A191" s="2">
-        <v>5062</v>
-      </c>
-      <c r="B191" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C191" s="2">
-        <v>0.70299</v>
-      </c>
-      <c r="D191" s="4">
-        <v>3315.6</v>
-      </c>
+      <c r="A191" s="2"/>
+      <c r="B191" s="3"/>
+      <c r="C191" s="2"/>
+      <c r="D191" s="4"/>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A192" s="2">
-        <v>5063</v>
-      </c>
-      <c r="B192" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C192" s="2">
-        <v>0.70299</v>
-      </c>
-      <c r="D192" s="4">
-        <v>3700.32</v>
-      </c>
+      <c r="A192" s="2"/>
+      <c r="B192" s="3"/>
+      <c r="C192" s="2"/>
+      <c r="D192" s="4"/>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A193" s="2">
-        <v>5064</v>
-      </c>
-      <c r="B193" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C193" s="2">
-        <v>0.70299</v>
-      </c>
-      <c r="D193" s="4">
-        <v>4299.74</v>
-      </c>
+      <c r="A193" s="2"/>
+      <c r="B193" s="3"/>
+      <c r="C193" s="2"/>
+      <c r="D193" s="4"/>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A194" s="2">
-        <v>5065</v>
-      </c>
-      <c r="B194" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C194" s="2">
-        <v>0.70299</v>
-      </c>
-      <c r="D194" s="4">
-        <v>3979.95</v>
-      </c>
+      <c r="A194" s="2"/>
+      <c r="B194" s="3"/>
+      <c r="C194" s="2"/>
+      <c r="D194" s="4"/>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A195" s="2">
-        <v>5066</v>
-      </c>
-      <c r="B195" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C195" s="2">
-        <v>0.70299</v>
-      </c>
-      <c r="D195" s="4">
-        <v>3558.75</v>
-      </c>
+      <c r="A195" s="2"/>
+      <c r="B195" s="3"/>
+      <c r="C195" s="2"/>
+      <c r="D195" s="4"/>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A196" s="2">
-        <v>5078</v>
-      </c>
-      <c r="B196" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C196" s="2">
-        <v>0.70299</v>
-      </c>
-      <c r="D196" s="4">
-        <v>3979.95</v>
-      </c>
+      <c r="A196" s="2"/>
+      <c r="B196" s="3"/>
+      <c r="C196" s="2"/>
+      <c r="D196" s="4"/>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A197" s="2">
-        <v>5080</v>
-      </c>
-      <c r="B197" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C197" s="2">
-        <v>0.70299</v>
-      </c>
-      <c r="D197" s="4">
-        <v>4158</v>
-      </c>
+      <c r="A197" s="2"/>
+      <c r="B197" s="3"/>
+      <c r="C197" s="2"/>
+      <c r="D197" s="4"/>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A198" s="2">
-        <v>5086</v>
-      </c>
-      <c r="B198" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C198" s="2">
-        <v>0.70299</v>
-      </c>
-      <c r="D198" s="4">
-        <v>4158</v>
-      </c>
+      <c r="A198" s="2"/>
+      <c r="B198" s="3"/>
+      <c r="C198" s="2"/>
+      <c r="D198" s="4"/>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A199" s="2">
-        <v>5088</v>
-      </c>
-      <c r="B199" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C199" s="2">
-        <v>0.70299</v>
-      </c>
-      <c r="D199" s="4">
-        <v>4428</v>
-      </c>
+      <c r="A199" s="2"/>
+      <c r="B199" s="3"/>
+      <c r="C199" s="2"/>
+      <c r="D199" s="4"/>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A200" s="2">
-        <v>5090</v>
-      </c>
-      <c r="B200" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C200" s="2">
-        <v>0.70299</v>
-      </c>
-      <c r="D200" s="4">
-        <v>4199.58</v>
-      </c>
+      <c r="A200" s="2"/>
+      <c r="B200" s="3"/>
+      <c r="C200" s="2"/>
+      <c r="D200" s="4"/>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A201" s="2">
-        <v>5093</v>
-      </c>
-      <c r="B201" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C201" s="2">
-        <v>0.70299</v>
-      </c>
-      <c r="D201" s="4">
-        <v>4158</v>
-      </c>
+      <c r="A201" s="2"/>
+      <c r="B201" s="3"/>
+      <c r="C201" s="2"/>
+      <c r="D201" s="4"/>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A202" s="2">
-        <v>5095</v>
-      </c>
-      <c r="B202" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C202" s="2">
-        <v>0.70299</v>
-      </c>
-      <c r="D202" s="4">
-        <v>4150.32</v>
-      </c>
+      <c r="A202" s="2"/>
+      <c r="B202" s="3"/>
+      <c r="C202" s="2"/>
+      <c r="D202" s="4"/>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A203" s="2">
-        <v>4962</v>
-      </c>
-      <c r="B203" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C203" s="2">
-        <v>0.78613999999999995</v>
-      </c>
-      <c r="D203" s="4">
-        <v>9981.5</v>
-      </c>
+      <c r="A203" s="2"/>
+      <c r="B203" s="3"/>
+      <c r="C203" s="2"/>
+      <c r="D203" s="4"/>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A204" s="2">
-        <v>4855</v>
-      </c>
-      <c r="B204" s="3">
-        <v>46022</v>
-      </c>
-      <c r="C204" s="2">
-        <v>0.65081</v>
-      </c>
-      <c r="D204" s="4">
-        <v>14586</v>
-      </c>
+      <c r="A204" s="2"/>
+      <c r="B204" s="3"/>
+      <c r="C204" s="2"/>
+      <c r="D204" s="4"/>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A205" s="2">
-        <v>4571</v>
-      </c>
-      <c r="B205" s="3">
-        <v>46044</v>
-      </c>
-      <c r="C205" s="2">
-        <v>0.67835000000000001</v>
-      </c>
-      <c r="D205" s="4">
-        <v>8870.4</v>
-      </c>
+      <c r="A205" s="2"/>
+      <c r="B205" s="3"/>
+      <c r="C205" s="2"/>
+      <c r="D205" s="4"/>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A206" s="2">
-        <v>4704</v>
-      </c>
-      <c r="B206" s="3">
-        <v>46044</v>
-      </c>
-      <c r="C206" s="2">
-        <v>0.67835000000000001</v>
-      </c>
-      <c r="D206" s="4">
-        <v>8870.4</v>
-      </c>
+      <c r="A206" s="2"/>
+      <c r="B206" s="3"/>
+      <c r="C206" s="2"/>
+      <c r="D206" s="4"/>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A207" s="2">
-        <v>4639</v>
-      </c>
-      <c r="B207" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C207" s="2">
-        <v>0.70299</v>
-      </c>
-      <c r="D207" s="4">
-        <v>7477.33</v>
-      </c>
+      <c r="A207" s="2"/>
+      <c r="B207" s="3"/>
+      <c r="C207" s="2"/>
+      <c r="D207" s="4"/>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A208" s="2">
-        <v>4825</v>
-      </c>
-      <c r="B208" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C208" s="2">
-        <v>0.70299</v>
-      </c>
-      <c r="D208" s="4">
-        <v>9702</v>
-      </c>
+      <c r="A208" s="2"/>
+      <c r="B208" s="3"/>
+      <c r="C208" s="2"/>
+      <c r="D208" s="4"/>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A209" s="2">
-        <v>4996</v>
-      </c>
-      <c r="B209" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C209" s="2">
-        <v>0.70299</v>
-      </c>
-      <c r="D209" s="4">
-        <v>9072.35</v>
-      </c>
+      <c r="A209" s="2"/>
+      <c r="B209" s="3"/>
+      <c r="C209" s="2"/>
+      <c r="D209" s="4"/>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A210" s="2">
-        <v>4784</v>
-      </c>
-      <c r="B210" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C210" s="2">
-        <v>0.70325000000000004</v>
-      </c>
-      <c r="D210" s="4">
-        <v>14586</v>
-      </c>
+      <c r="A210" s="2"/>
+      <c r="B210" s="3"/>
+      <c r="C210" s="2"/>
+      <c r="D210" s="4"/>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A211" s="2">
-        <v>4788</v>
-      </c>
-      <c r="B211" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C211" s="2">
-        <v>0.70325000000000004</v>
-      </c>
-      <c r="D211" s="4">
-        <v>29172</v>
-      </c>
+      <c r="A211" s="2"/>
+      <c r="B211" s="3"/>
+      <c r="C211" s="2"/>
+      <c r="D211" s="4"/>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A212" s="2">
-        <v>4792</v>
-      </c>
-      <c r="B212" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C212" s="2">
-        <v>0.70325000000000004</v>
-      </c>
-      <c r="D212" s="4">
-        <v>14586</v>
-      </c>
+      <c r="A212" s="2"/>
+      <c r="B212" s="3"/>
+      <c r="C212" s="2"/>
+      <c r="D212" s="4"/>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A213" s="2">
-        <v>4887</v>
-      </c>
-      <c r="B213" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C213" s="2">
-        <v>0.70325000000000004</v>
-      </c>
-      <c r="D213" s="4">
-        <v>14586</v>
-      </c>
+      <c r="A213" s="2"/>
+      <c r="B213" s="3"/>
+      <c r="C213" s="2"/>
+      <c r="D213" s="4"/>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A214" s="2">
-        <v>4932</v>
-      </c>
-      <c r="B214" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C214" s="2">
-        <v>0.70325000000000004</v>
-      </c>
-      <c r="D214" s="4">
-        <v>15390</v>
-      </c>
+      <c r="A214" s="2"/>
+      <c r="B214" s="3"/>
+      <c r="C214" s="2"/>
+      <c r="D214" s="4"/>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A215" s="2">
-        <v>4934</v>
-      </c>
-      <c r="B215" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C215" s="2">
-        <v>0.70325000000000004</v>
-      </c>
-      <c r="D215" s="4">
-        <v>15444</v>
-      </c>
+      <c r="A215" s="2"/>
+      <c r="B215" s="3"/>
+      <c r="C215" s="2"/>
+      <c r="D215" s="4"/>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A216" s="2"/>

--- a/H2coco/PO.xlsx
+++ b/H2coco/PO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leo/Github/XeroAPI/H2coco/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E5CCD13-9CF3-3D4F-99B5-840F12E748E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C1D24CF-D8FD-0845-A4A3-3B8BB90C01BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-8840" yWindow="-28180" windowWidth="25600" windowHeight="28180" xr2:uid="{4B9AE9D0-272D-6147-B144-109295B6F9E3}"/>
+    <workbookView xWindow="20300" yWindow="-28180" windowWidth="25600" windowHeight="28180" xr2:uid="{4B9AE9D0-272D-6147-B144-109295B6F9E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -101,15 +101,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -465,877 +463,877 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="6">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7">
-        <v>45854</v>
-      </c>
-      <c r="C2" s="6">
-        <v>0.66977399999999998</v>
+      <c r="A2" s="2">
+        <v>4876</v>
+      </c>
+      <c r="B2" s="3">
+        <v>46009</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.66039000000000003</v>
       </c>
       <c r="D2" s="5">
-        <v>11025</v>
+        <v>3801.6</v>
       </c>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
-        <v>3</v>
-      </c>
-      <c r="B3" s="7">
-        <v>45923</v>
-      </c>
-      <c r="C3" s="6">
-        <v>0.66079399999999999</v>
+      <c r="A3" s="2">
+        <v>4947</v>
+      </c>
+      <c r="B3" s="3">
+        <v>46022</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.66935</v>
       </c>
       <c r="D3" s="5">
-        <v>5061.8</v>
+        <v>4371.84</v>
       </c>
       <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
-        <v>5</v>
-      </c>
-      <c r="B4" s="7">
-        <v>45923</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0.66079399999999999</v>
+      <c r="A4" s="2">
+        <v>4948</v>
+      </c>
+      <c r="B4" s="3">
+        <v>46022</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.66935</v>
       </c>
       <c r="D4" s="5">
-        <v>5134.68</v>
+        <v>4302.1400000000003</v>
       </c>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
-        <v>9</v>
-      </c>
-      <c r="B5" s="7">
-        <v>46068</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0.70735000000000003</v>
-      </c>
-      <c r="D5" s="6">
-        <v>350.4</v>
+      <c r="A5" s="2">
+        <v>4979</v>
+      </c>
+      <c r="B5" s="3">
+        <v>46022</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.66935</v>
+      </c>
+      <c r="D5" s="5">
+        <v>4302.1400000000003</v>
       </c>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
-        <v>10</v>
-      </c>
-      <c r="B6" s="7">
-        <v>46068</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0.70735000000000003</v>
+      <c r="A6" s="2">
+        <v>4959</v>
+      </c>
+      <c r="B6" s="3">
+        <v>46030</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.67149000000000003</v>
       </c>
       <c r="D6" s="5">
-        <v>15050.4</v>
+        <v>4105.5</v>
       </c>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="6">
-        <v>7</v>
-      </c>
-      <c r="B7" s="7">
-        <v>45925</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.65937000000000001</v>
+      <c r="A7" s="2">
+        <v>4960</v>
+      </c>
+      <c r="B7" s="3">
+        <v>46030</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.67149000000000003</v>
       </c>
       <c r="D7" s="5">
-        <v>14204.8</v>
+        <v>4302.1400000000003</v>
       </c>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="6">
-        <v>8</v>
-      </c>
-      <c r="B8" s="7">
-        <v>45966</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0.65044999999999997</v>
+      <c r="A8" s="2">
+        <v>4986</v>
+      </c>
+      <c r="B8" s="3">
+        <v>46030</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.67149000000000003</v>
       </c>
       <c r="D8" s="5">
-        <v>20700</v>
+        <v>4117.92</v>
       </c>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="6">
-        <v>4876</v>
-      </c>
-      <c r="B9" s="7">
-        <v>46009</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0.66039000000000003</v>
+      <c r="A9" s="2">
+        <v>5013</v>
+      </c>
+      <c r="B9" s="3">
+        <v>46030</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.67149000000000003</v>
       </c>
       <c r="D9" s="5">
+        <v>3864</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>4702</v>
+      </c>
+      <c r="B10" s="3">
+        <v>46030</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.6573</v>
+      </c>
+      <c r="D10" s="5">
         <v>3801.6</v>
       </c>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="6">
-        <v>4947</v>
-      </c>
-      <c r="B10" s="7">
-        <v>46022</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0.66935</v>
-      </c>
-      <c r="D10" s="5">
-        <v>4371.84</v>
-      </c>
       <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="6">
-        <v>4948</v>
-      </c>
-      <c r="B11" s="7">
-        <v>46022</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0.66935</v>
+      <c r="A11" s="2">
+        <v>4958</v>
+      </c>
+      <c r="B11" s="3">
+        <v>46030</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.65086999999999995</v>
       </c>
       <c r="D11" s="5">
+        <v>4074.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>5014</v>
+      </c>
+      <c r="B12" s="3">
+        <v>46030</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.65051999999999999</v>
+      </c>
+      <c r="D12" s="5">
+        <v>3801.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>5033</v>
+      </c>
+      <c r="B13" s="3">
+        <v>46044</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.67835000000000001</v>
+      </c>
+      <c r="D13" s="5">
+        <v>3426.12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>5038</v>
+      </c>
+      <c r="B14" s="3">
+        <v>46044</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.67835000000000001</v>
+      </c>
+      <c r="D14" s="5">
+        <v>4316.72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>5042</v>
+      </c>
+      <c r="B15" s="3">
+        <v>46044</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.67835000000000001</v>
+      </c>
+      <c r="D15" s="5">
+        <v>3832.95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>5048</v>
+      </c>
+      <c r="B16" s="3">
+        <v>46044</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.67835000000000001</v>
+      </c>
+      <c r="D16" s="5">
+        <v>4158</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>5057</v>
+      </c>
+      <c r="B17" s="3">
+        <v>46044</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0.67835000000000001</v>
+      </c>
+      <c r="D17" s="5">
         <v>4302.1400000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="6">
-        <v>4979</v>
-      </c>
-      <c r="B12" s="7">
-        <v>46022</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0.66935</v>
-      </c>
-      <c r="D12" s="5">
-        <v>4302.1400000000003</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="6">
-        <v>4959</v>
-      </c>
-      <c r="B13" s="7">
-        <v>46030</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0.67149000000000003</v>
-      </c>
-      <c r="D13" s="5">
-        <v>4105.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="6">
-        <v>4960</v>
-      </c>
-      <c r="B14" s="7">
-        <v>46030</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0.67149000000000003</v>
-      </c>
-      <c r="D14" s="5">
-        <v>4302.1400000000003</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="6">
-        <v>4986</v>
-      </c>
-      <c r="B15" s="7">
-        <v>46030</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0.67149000000000003</v>
-      </c>
-      <c r="D15" s="5">
-        <v>4117.92</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="6">
-        <v>5013</v>
-      </c>
-      <c r="B16" s="7">
-        <v>46030</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.67149000000000003</v>
-      </c>
-      <c r="D16" s="5">
-        <v>3864</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="6">
-        <v>4702</v>
-      </c>
-      <c r="B17" s="7">
-        <v>46030</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.6573</v>
-      </c>
-      <c r="D17" s="5">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>5138</v>
+      </c>
+      <c r="B18" s="3">
+        <v>46044</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0.67835000000000001</v>
+      </c>
+      <c r="D18" s="5">
+        <v>4347</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>5030</v>
+      </c>
+      <c r="B19" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0.70299</v>
+      </c>
+      <c r="D19" s="5">
+        <v>4873.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>5062</v>
+      </c>
+      <c r="B20" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0.70299</v>
+      </c>
+      <c r="D20" s="5">
+        <v>3315.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>5063</v>
+      </c>
+      <c r="B21" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0.70299</v>
+      </c>
+      <c r="D21" s="5">
+        <v>3700.32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>5064</v>
+      </c>
+      <c r="B22" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0.70299</v>
+      </c>
+      <c r="D22" s="5">
+        <v>4299.74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
+        <v>5066</v>
+      </c>
+      <c r="B23" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0.70299</v>
+      </c>
+      <c r="D23" s="5">
+        <v>3558.75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <v>5084</v>
+      </c>
+      <c r="B24" s="3">
+        <v>46058</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0.66152999999999995</v>
+      </c>
+      <c r="D24" s="5">
+        <v>4158</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="2">
+        <v>5097</v>
+      </c>
+      <c r="B25" s="3">
+        <v>46058</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0.66152999999999995</v>
+      </c>
+      <c r="D25" s="5">
+        <v>4206.6000000000004</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="2">
+        <v>5099</v>
+      </c>
+      <c r="B26" s="3">
+        <v>46058</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0.66152999999999995</v>
+      </c>
+      <c r="D26" s="5">
+        <v>4044.09</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="2">
+        <v>5116</v>
+      </c>
+      <c r="B27" s="3">
+        <v>46058</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0.66152999999999995</v>
+      </c>
+      <c r="D27" s="5">
+        <v>4114.95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="2">
+        <v>5117</v>
+      </c>
+      <c r="B28" s="3">
+        <v>46058</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0.66152999999999995</v>
+      </c>
+      <c r="D28" s="5">
+        <v>4066.2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="2">
+        <v>5155</v>
+      </c>
+      <c r="B29" s="3">
+        <v>46065</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0.71289000000000002</v>
+      </c>
+      <c r="D29" s="5">
         <v>3801.6</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="6">
-        <v>4958</v>
-      </c>
-      <c r="B18" s="7">
-        <v>46030</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.65086999999999995</v>
-      </c>
-      <c r="D18" s="5">
-        <v>4074.3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="6">
-        <v>5014</v>
-      </c>
-      <c r="B19" s="7">
-        <v>46030</v>
-      </c>
-      <c r="C19" s="6">
-        <v>0.65051999999999999</v>
-      </c>
-      <c r="D19" s="5">
-        <v>3801.6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="6">
-        <v>5033</v>
-      </c>
-      <c r="B20" s="7">
-        <v>46044</v>
-      </c>
-      <c r="C20" s="6">
-        <v>0.67835000000000001</v>
-      </c>
-      <c r="D20" s="5">
-        <v>3426.12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="6">
-        <v>5038</v>
-      </c>
-      <c r="B21" s="7">
-        <v>46044</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0.67835000000000001</v>
-      </c>
-      <c r="D21" s="5">
-        <v>4316.72</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="6">
-        <v>5042</v>
-      </c>
-      <c r="B22" s="7">
-        <v>46044</v>
-      </c>
-      <c r="C22" s="6">
-        <v>0.67835000000000001</v>
-      </c>
-      <c r="D22" s="5">
-        <v>3832.95</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="6">
-        <v>5048</v>
-      </c>
-      <c r="B23" s="7">
-        <v>46044</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0.67835000000000001</v>
-      </c>
-      <c r="D23" s="5">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="2">
+        <v>5241</v>
+      </c>
+      <c r="B30" s="3">
+        <v>46065</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0.71272000000000002</v>
+      </c>
+      <c r="D30" s="5">
+        <v>3979.95</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="2">
+        <v>4905</v>
+      </c>
+      <c r="B31" s="3">
+        <v>46079</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0.71162999999999998</v>
+      </c>
+      <c r="D31" s="5">
+        <v>8751.6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
+        <v>4908</v>
+      </c>
+      <c r="B32" s="3">
+        <v>46079</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0.71162999999999998</v>
+      </c>
+      <c r="D32" s="5">
+        <v>4375.8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="2">
+        <v>5089</v>
+      </c>
+      <c r="B33" s="3">
+        <v>46079</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0.66139999999999999</v>
+      </c>
+      <c r="D33" s="5">
+        <v>3950.56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="2">
+        <v>5092</v>
+      </c>
+      <c r="B34" s="3">
+        <v>46079</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0.66139999999999999</v>
+      </c>
+      <c r="D34" s="4">
         <v>4158</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="6">
-        <v>5057</v>
-      </c>
-      <c r="B24" s="7">
-        <v>46044</v>
-      </c>
-      <c r="C24" s="6">
-        <v>0.67835000000000001</v>
-      </c>
-      <c r="D24" s="5">
-        <v>4302.1400000000003</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="6">
-        <v>5138</v>
-      </c>
-      <c r="B25" s="7">
-        <v>46044</v>
-      </c>
-      <c r="C25" s="6">
-        <v>0.67835000000000001</v>
-      </c>
-      <c r="D25" s="5">
-        <v>4347</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="6">
-        <v>5030</v>
-      </c>
-      <c r="B26" s="7">
-        <v>46051</v>
-      </c>
-      <c r="C26" s="6">
-        <v>0.70299</v>
-      </c>
-      <c r="D26" s="5">
-        <v>4873.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="6">
-        <v>5062</v>
-      </c>
-      <c r="B27" s="7">
-        <v>46051</v>
-      </c>
-      <c r="C27" s="6">
-        <v>0.70299</v>
-      </c>
-      <c r="D27" s="5">
-        <v>3315.6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="6">
-        <v>5063</v>
-      </c>
-      <c r="B28" s="7">
-        <v>46051</v>
-      </c>
-      <c r="C28" s="6">
-        <v>0.70299</v>
-      </c>
-      <c r="D28" s="5">
-        <v>3700.32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="6">
-        <v>5064</v>
-      </c>
-      <c r="B29" s="7">
-        <v>46051</v>
-      </c>
-      <c r="C29" s="6">
-        <v>0.70299</v>
-      </c>
-      <c r="D29" s="5">
-        <v>4299.74</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="6">
-        <v>5066</v>
-      </c>
-      <c r="B30" s="7">
-        <v>46051</v>
-      </c>
-      <c r="C30" s="6">
-        <v>0.70299</v>
-      </c>
-      <c r="D30" s="5">
-        <v>3558.75</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="6">
-        <v>5084</v>
-      </c>
-      <c r="B31" s="7">
-        <v>46058</v>
-      </c>
-      <c r="C31" s="6">
-        <v>0.66152999999999995</v>
-      </c>
-      <c r="D31" s="5">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="2">
+        <v>5113</v>
+      </c>
+      <c r="B35" s="3">
+        <v>46079</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0.66139999999999999</v>
+      </c>
+      <c r="D35" s="4">
         <v>4158</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="6">
-        <v>5097</v>
-      </c>
-      <c r="B32" s="7">
-        <v>46058</v>
-      </c>
-      <c r="C32" s="6">
-        <v>0.66152999999999995</v>
-      </c>
-      <c r="D32" s="5">
-        <v>4206.6000000000004</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="6">
-        <v>5099</v>
-      </c>
-      <c r="B33" s="7">
-        <v>46058</v>
-      </c>
-      <c r="C33" s="6">
-        <v>0.66152999999999995</v>
-      </c>
-      <c r="D33" s="5">
-        <v>4044.09</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="6">
-        <v>5116</v>
-      </c>
-      <c r="B34" s="7">
-        <v>46058</v>
-      </c>
-      <c r="C34" s="6">
-        <v>0.66152999999999995</v>
-      </c>
-      <c r="D34" s="5">
-        <v>4114.95</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="6">
-        <v>5117</v>
-      </c>
-      <c r="B35" s="7">
-        <v>46058</v>
-      </c>
-      <c r="C35" s="6">
-        <v>0.66152999999999995</v>
-      </c>
-      <c r="D35" s="5">
-        <v>4066.2</v>
-      </c>
-    </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="6">
-        <v>5155</v>
-      </c>
-      <c r="B36" s="7">
-        <v>46065</v>
-      </c>
-      <c r="C36" s="6">
-        <v>0.71289000000000002</v>
-      </c>
-      <c r="D36" s="5">
-        <v>3801.6</v>
+      <c r="A36" s="2">
+        <v>5229</v>
+      </c>
+      <c r="B36" s="3">
+        <v>46079</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0.66139999999999999</v>
+      </c>
+      <c r="D36" s="4">
+        <v>4252.5</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="6">
-        <v>5241</v>
-      </c>
-      <c r="B37" s="7">
-        <v>46065</v>
-      </c>
-      <c r="C37" s="6">
-        <v>0.71272000000000002</v>
-      </c>
-      <c r="D37" s="5">
-        <v>3979.95</v>
+      <c r="A37" s="2">
+        <v>5230</v>
+      </c>
+      <c r="B37" s="3">
+        <v>46079</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0.66139999999999999</v>
+      </c>
+      <c r="D37" s="4">
+        <v>4293</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="6">
-        <v>4905</v>
-      </c>
-      <c r="B38" s="7">
+      <c r="A38" s="2">
+        <v>5281</v>
+      </c>
+      <c r="B38" s="3">
         <v>46079</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="2">
         <v>0.71162999999999998</v>
       </c>
-      <c r="D38" s="5">
-        <v>8751.6</v>
+      <c r="D38" s="4">
+        <v>4375.8</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>4908</v>
+        <v>5192</v>
       </c>
       <c r="B39" s="3">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="C39" s="2">
-        <v>0.71162999999999998</v>
+        <v>0.70704</v>
       </c>
       <c r="D39" s="4">
-        <v>4375.8</v>
+        <v>4277.1000000000004</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>5089</v>
+        <v>5195</v>
       </c>
       <c r="B40" s="3">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="C40" s="2">
-        <v>0.66139999999999999</v>
+        <v>0.70704</v>
       </c>
       <c r="D40" s="4">
-        <v>3950.56</v>
+        <v>4288.4399999999996</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>5092</v>
+        <v>5200</v>
       </c>
       <c r="B41" s="3">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="C41" s="2">
-        <v>0.66139999999999999</v>
+        <v>0.70738999999999996</v>
       </c>
       <c r="D41" s="4">
-        <v>4158</v>
+        <v>4274.7</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>5113</v>
+        <v>5204</v>
       </c>
       <c r="B42" s="3">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="C42" s="2">
-        <v>0.66139999999999999</v>
+        <v>0.70733999999999997</v>
       </c>
       <c r="D42" s="4">
-        <v>4158</v>
+        <v>8286.9599999999991</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>5229</v>
+        <v>5205</v>
       </c>
       <c r="B43" s="3">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="C43" s="2">
-        <v>0.66139999999999999</v>
+        <v>0.70733999999999997</v>
       </c>
       <c r="D43" s="4">
-        <v>4252.5</v>
+        <v>8820</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>5230</v>
+        <v>5207</v>
       </c>
       <c r="B44" s="3">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="C44" s="2">
-        <v>0.66139999999999999</v>
+        <v>0.70733999999999997</v>
       </c>
       <c r="D44" s="4">
-        <v>4293</v>
+        <v>4143.4799999999996</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>5281</v>
+        <v>5208</v>
       </c>
       <c r="B45" s="3">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="C45" s="2">
-        <v>0.71162999999999998</v>
+        <v>0.70733999999999997</v>
       </c>
       <c r="D45" s="4">
-        <v>4375.8</v>
+        <v>4276.74</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>4907</v>
+        <v>5209</v>
       </c>
       <c r="B46" s="3">
         <v>46086</v>
       </c>
       <c r="C46" s="2">
-        <v>0.70499000000000001</v>
+        <v>0.70733999999999997</v>
       </c>
       <c r="D46" s="4">
-        <v>8751.6</v>
+        <v>4143.4799999999996</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>5139</v>
+        <v>5210</v>
       </c>
       <c r="B47" s="3">
         <v>46086</v>
       </c>
       <c r="C47" s="2">
-        <v>0.70499000000000001</v>
+        <v>0.70733999999999997</v>
       </c>
       <c r="D47" s="4">
-        <v>4375.8</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>5140</v>
+        <v>5242</v>
       </c>
       <c r="B48" s="3">
         <v>46086</v>
       </c>
       <c r="C48" s="2">
-        <v>0.70499000000000001</v>
+        <v>0.70733999999999997</v>
       </c>
       <c r="D48" s="4">
-        <v>4375.8</v>
+        <v>4143.4799999999996</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>5192</v>
+        <v>5243</v>
       </c>
       <c r="B49" s="3">
         <v>46086</v>
       </c>
       <c r="C49" s="2">
-        <v>0.70704</v>
+        <v>0.70733999999999997</v>
       </c>
       <c r="D49" s="4">
-        <v>4277.1000000000004</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>5195</v>
+        <v>5244</v>
       </c>
       <c r="B50" s="3">
         <v>46086</v>
       </c>
       <c r="C50" s="2">
-        <v>0.70704</v>
+        <v>0.70733999999999997</v>
       </c>
       <c r="D50" s="4">
-        <v>4288.4399999999996</v>
+        <v>4276.74</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>5200</v>
+        <v>5124</v>
       </c>
       <c r="B51" s="3">
         <v>46086</v>
       </c>
       <c r="C51" s="2">
-        <v>0.70738999999999996</v>
+        <v>0.70704</v>
       </c>
       <c r="D51" s="4">
-        <v>4274.7</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>5204</v>
+        <v>5125</v>
       </c>
       <c r="B52" s="3">
         <v>46086</v>
       </c>
       <c r="C52" s="2">
-        <v>0.70733999999999997</v>
+        <v>0.70704</v>
       </c>
       <c r="D52" s="4">
-        <v>8286.9599999999991</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>5205</v>
+        <v>5129</v>
       </c>
       <c r="B53" s="3">
         <v>46086</v>
       </c>
       <c r="C53" s="2">
-        <v>0.70733999999999997</v>
+        <v>0.70704</v>
       </c>
       <c r="D53" s="4">
-        <v>8820</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>5207</v>
+        <v>5167</v>
       </c>
       <c r="B54" s="3">
         <v>46086</v>
       </c>
       <c r="C54" s="2">
-        <v>0.70733999999999997</v>
+        <v>0.67017000000000004</v>
       </c>
       <c r="D54" s="4">
-        <v>4143.4799999999996</v>
+        <v>3864</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>5208</v>
+        <v>5191</v>
       </c>
       <c r="B55" s="3">
         <v>46086</v>
       </c>
       <c r="C55" s="2">
-        <v>0.70733999999999997</v>
+        <v>0.55949000000000004</v>
       </c>
       <c r="D55" s="4">
-        <v>4276.74</v>
+        <v>4094.66</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>5209</v>
+        <v>5194</v>
       </c>
       <c r="B56" s="3">
         <v>46086</v>
       </c>
       <c r="C56" s="2">
-        <v>0.70733999999999997</v>
+        <v>0.67017000000000004</v>
       </c>
       <c r="D56" s="4">
-        <v>4143.4799999999996</v>
+        <v>4101.72</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>5210</v>
+        <v>5197</v>
       </c>
       <c r="B57" s="3">
         <v>46086</v>
       </c>
       <c r="C57" s="2">
-        <v>0.70733999999999997</v>
+        <v>0.67017000000000004</v>
       </c>
       <c r="D57" s="4">
-        <v>4410</v>
+        <v>4090.34</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>5242</v>
+        <v>5201</v>
       </c>
       <c r="B58" s="3">
         <v>46086</v>
       </c>
       <c r="C58" s="2">
-        <v>0.70733999999999997</v>
+        <v>0.67017000000000004</v>
       </c>
       <c r="D58" s="4">
-        <v>4143.4799999999996</v>
+        <v>4064.34</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>5243</v>
+        <v>5232</v>
       </c>
       <c r="B59" s="3">
         <v>46086</v>
       </c>
       <c r="C59" s="2">
-        <v>0.70733999999999997</v>
+        <v>0.67017000000000004</v>
       </c>
       <c r="D59" s="4">
-        <v>4410</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>5244</v>
+        <v>5233</v>
       </c>
       <c r="B60" s="3">
         <v>46086</v>
       </c>
       <c r="C60" s="2">
-        <v>0.70733999999999997</v>
-      </c>
-      <c r="D60" s="4">
-        <v>4276.74</v>
+        <v>0.67020000000000002</v>
+      </c>
+      <c r="D60" s="2">
+        <v>86.55</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>5124</v>
+        <v>5234</v>
       </c>
       <c r="B61" s="3">
         <v>46086</v>
       </c>
       <c r="C61" s="2">
-        <v>0.70704</v>
+        <v>0.67017000000000004</v>
       </c>
       <c r="D61" s="4">
-        <v>3801.6</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>5125</v>
+        <v>5261</v>
       </c>
       <c r="B62" s="3">
         <v>46086</v>
       </c>
       <c r="C62" s="2">
-        <v>0.70704</v>
+        <v>0.67017000000000004</v>
       </c>
       <c r="D62" s="4">
-        <v>3801.6</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>5129</v>
+        <v>5198</v>
       </c>
       <c r="B63" s="3">
         <v>46086</v>
       </c>
       <c r="C63" s="2">
-        <v>0.70704</v>
+        <v>0.67017000000000004</v>
       </c>
       <c r="D63" s="4">
         <v>3801.6</v>
@@ -1343,7 +1341,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>5167</v>
+        <v>5226</v>
       </c>
       <c r="B64" s="3">
         <v>46086</v>
@@ -1352,264 +1350,264 @@
         <v>0.67017000000000004</v>
       </c>
       <c r="D64" s="4">
-        <v>3864</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>5191</v>
+        <v>5227</v>
       </c>
       <c r="B65" s="3">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="C65" s="2">
-        <v>0.55949000000000004</v>
+        <v>0.67018</v>
       </c>
       <c r="D65" s="4">
-        <v>4094.66</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
-        <v>5194</v>
+        <v>5287</v>
       </c>
       <c r="B66" s="3">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="C66" s="2">
-        <v>0.67017000000000004</v>
+        <v>0.67018</v>
       </c>
       <c r="D66" s="4">
-        <v>4101.72</v>
+        <v>7603.2</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
-        <v>5197</v>
+        <v>5288</v>
       </c>
       <c r="B67" s="3">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="C67" s="2">
-        <v>0.67017000000000004</v>
+        <v>0.67018</v>
       </c>
       <c r="D67" s="4">
-        <v>4090.34</v>
+        <v>7603.2</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
-        <v>5201</v>
+        <v>5130</v>
       </c>
       <c r="B68" s="3">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="C68" s="2">
-        <v>0.67017000000000004</v>
+        <v>0.71640999999999999</v>
       </c>
       <c r="D68" s="4">
-        <v>4064.34</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
-        <v>5232</v>
+        <v>5177</v>
       </c>
       <c r="B69" s="3">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="C69" s="2">
-        <v>0.67017000000000004</v>
+        <v>0.71640999999999999</v>
       </c>
       <c r="D69" s="4">
-        <v>3979.95</v>
+        <v>10350</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
-        <v>5233</v>
+        <v>5178</v>
       </c>
       <c r="B70" s="3">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="C70" s="2">
-        <v>0.67020000000000002</v>
-      </c>
-      <c r="D70" s="2">
-        <v>86.55</v>
+        <v>0.71640999999999999</v>
+      </c>
+      <c r="D70" s="4">
+        <v>10350</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
-        <v>5234</v>
+        <v>5179</v>
       </c>
       <c r="B71" s="3">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="C71" s="2">
-        <v>0.67017000000000004</v>
+        <v>0.71628999999999998</v>
       </c>
       <c r="D71" s="4">
-        <v>3979.95</v>
+        <v>5175</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
-        <v>5235</v>
+        <v>5180</v>
       </c>
       <c r="B72" s="3">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="C72" s="2">
-        <v>0.67017000000000004</v>
+        <v>0.71628999999999998</v>
       </c>
       <c r="D72" s="4">
-        <v>3888.15</v>
+        <v>5175</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
-        <v>5261</v>
+        <v>5181</v>
       </c>
       <c r="B73" s="3">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="C73" s="2">
-        <v>0.67017000000000004</v>
+        <v>0.71628999999999998</v>
       </c>
       <c r="D73" s="4">
-        <v>4158</v>
+        <v>5175</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
-        <v>5198</v>
+        <v>5182</v>
       </c>
       <c r="B74" s="3">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="C74" s="2">
-        <v>0.67017000000000004</v>
+        <v>0.71628999999999998</v>
       </c>
       <c r="D74" s="4">
-        <v>3801.6</v>
+        <v>5175</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
-        <v>5225</v>
+        <v>5183</v>
       </c>
       <c r="B75" s="3">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="C75" s="2">
-        <v>0.67018</v>
+        <v>0.71628999999999998</v>
       </c>
       <c r="D75" s="4">
-        <v>7603.2</v>
+        <v>5175</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
-        <v>5226</v>
+        <v>5184</v>
       </c>
       <c r="B76" s="3">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="C76" s="2">
-        <v>0.67017000000000004</v>
+        <v>0.71628999999999998</v>
       </c>
       <c r="D76" s="4">
-        <v>3801.6</v>
+        <v>5175</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
-        <v>5227</v>
+        <v>5187</v>
       </c>
       <c r="B77" s="3">
         <v>46092</v>
       </c>
       <c r="C77" s="2">
-        <v>0.67018</v>
+        <v>0.71628999999999998</v>
       </c>
       <c r="D77" s="4">
-        <v>3801.6</v>
+        <v>5175</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
-        <v>5287</v>
+        <v>5188</v>
       </c>
       <c r="B78" s="3">
         <v>46092</v>
       </c>
       <c r="C78" s="2">
-        <v>0.67018</v>
+        <v>0.71628999999999998</v>
       </c>
       <c r="D78" s="4">
-        <v>7603.2</v>
+        <v>5175</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
-        <v>5288</v>
+        <v>5189</v>
       </c>
       <c r="B79" s="3">
         <v>46092</v>
       </c>
       <c r="C79" s="2">
-        <v>0.67018</v>
+        <v>0.71628999999999998</v>
       </c>
       <c r="D79" s="4">
-        <v>7603.2</v>
+        <v>5175</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
-        <v>5130</v>
+        <v>5206</v>
       </c>
       <c r="B80" s="3">
         <v>46092</v>
       </c>
       <c r="C80" s="2">
-        <v>0.71640999999999999</v>
+        <v>0.71628999999999998</v>
       </c>
       <c r="D80" s="4">
-        <v>3801.6</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
-        <v>5177</v>
+        <v>5238</v>
       </c>
       <c r="B81" s="3">
         <v>46092</v>
       </c>
       <c r="C81" s="2">
-        <v>0.71640999999999999</v>
+        <v>0.71628999999999998</v>
       </c>
       <c r="D81" s="4">
-        <v>10350</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
-        <v>5178</v>
+        <v>5239</v>
       </c>
       <c r="B82" s="3">
         <v>46092</v>
       </c>
       <c r="C82" s="2">
-        <v>0.71640999999999999</v>
+        <v>0.71628999999999998</v>
       </c>
       <c r="D82" s="4">
-        <v>10350</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
-        <v>5179</v>
+        <v>5240</v>
       </c>
       <c r="B83" s="3">
         <v>46092</v>
@@ -1618,12 +1616,12 @@
         <v>0.71628999999999998</v>
       </c>
       <c r="D83" s="4">
-        <v>5175</v>
+        <v>4308</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
-        <v>5180</v>
+        <v>5246</v>
       </c>
       <c r="B84" s="3">
         <v>46092</v>
@@ -1632,236 +1630,236 @@
         <v>0.71628999999999998</v>
       </c>
       <c r="D84" s="4">
-        <v>5175</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
-        <v>5181</v>
+        <v>5141</v>
       </c>
       <c r="B85" s="3">
         <v>46092</v>
       </c>
       <c r="C85" s="2">
-        <v>0.71628999999999998</v>
+        <v>0.71577000000000002</v>
       </c>
       <c r="D85" s="4">
-        <v>5175</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
-        <v>5182</v>
+        <v>5142</v>
       </c>
       <c r="B86" s="3">
         <v>46092</v>
       </c>
       <c r="C86" s="2">
-        <v>0.71628999999999998</v>
+        <v>0.71577000000000002</v>
       </c>
       <c r="D86" s="4">
-        <v>5175</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
-        <v>5183</v>
+        <v>5144</v>
       </c>
       <c r="B87" s="3">
         <v>46092</v>
       </c>
       <c r="C87" s="2">
-        <v>0.71628999999999998</v>
+        <v>0.71577000000000002</v>
       </c>
       <c r="D87" s="4">
-        <v>5175</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
-        <v>5184</v>
+        <v>5145</v>
       </c>
       <c r="B88" s="3">
         <v>46092</v>
       </c>
       <c r="C88" s="2">
-        <v>0.71628999999999998</v>
+        <v>0.71577000000000002</v>
       </c>
       <c r="D88" s="4">
-        <v>5175</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
-        <v>5187</v>
+        <v>5009</v>
       </c>
       <c r="B89" s="3">
         <v>46092</v>
       </c>
       <c r="C89" s="2">
-        <v>0.71628999999999998</v>
+        <v>0.67017000000000004</v>
       </c>
       <c r="D89" s="4">
-        <v>5175</v>
+        <v>3589.8</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
-        <v>5188</v>
+        <v>5120</v>
       </c>
       <c r="B90" s="3">
         <v>46092</v>
       </c>
       <c r="C90" s="2">
-        <v>0.71628999999999998</v>
+        <v>0.67017000000000004</v>
       </c>
       <c r="D90" s="4">
-        <v>5175</v>
+        <v>4101.45</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
-        <v>5189</v>
+        <v>5121</v>
       </c>
       <c r="B91" s="3">
         <v>46092</v>
       </c>
       <c r="C91" s="2">
-        <v>0.71628999999999998</v>
+        <v>0.67017000000000004</v>
       </c>
       <c r="D91" s="4">
-        <v>5175</v>
+        <v>4105.5</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
-        <v>5206</v>
+        <v>5122</v>
       </c>
       <c r="B92" s="3">
         <v>46092</v>
       </c>
       <c r="C92" s="2">
-        <v>0.71628999999999998</v>
+        <v>0.67017000000000004</v>
       </c>
       <c r="D92" s="4">
-        <v>4257</v>
+        <v>4302.1400000000003</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
-        <v>5238</v>
+        <v>5236</v>
       </c>
       <c r="B93" s="3">
         <v>46092</v>
       </c>
       <c r="C93" s="2">
-        <v>0.71628999999999998</v>
+        <v>0.67017000000000004</v>
       </c>
       <c r="D93" s="4">
-        <v>4257</v>
+        <v>4066.2</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
-        <v>5239</v>
+        <v>5262</v>
       </c>
       <c r="B94" s="3">
         <v>46092</v>
       </c>
       <c r="C94" s="2">
-        <v>0.71628999999999998</v>
+        <v>0.67017000000000004</v>
       </c>
       <c r="D94" s="4">
-        <v>4257</v>
+        <v>3801.9</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
-        <v>5240</v>
+        <v>5263</v>
       </c>
       <c r="B95" s="3">
         <v>46092</v>
       </c>
       <c r="C95" s="2">
-        <v>0.71628999999999998</v>
+        <v>0.67017000000000004</v>
       </c>
       <c r="D95" s="4">
-        <v>4308</v>
+        <v>3801.9</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
-        <v>5246</v>
+        <v>5264</v>
       </c>
       <c r="B96" s="3">
         <v>46092</v>
       </c>
       <c r="C96" s="2">
-        <v>0.71628999999999998</v>
+        <v>0.67017000000000004</v>
       </c>
       <c r="D96" s="4">
-        <v>4257</v>
+        <v>3974.4</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
-        <v>5141</v>
+        <v>5265</v>
       </c>
       <c r="B97" s="3">
         <v>46092</v>
       </c>
       <c r="C97" s="2">
-        <v>0.71577000000000002</v>
+        <v>0.67017000000000004</v>
       </c>
       <c r="D97" s="4">
-        <v>4375.8</v>
+        <v>3801.9</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
-        <v>5142</v>
+        <v>5266</v>
       </c>
       <c r="B98" s="3">
         <v>46092</v>
       </c>
       <c r="C98" s="2">
-        <v>0.71577000000000002</v>
+        <v>0.69084999999999996</v>
       </c>
       <c r="D98" s="4">
-        <v>4375.8</v>
+        <v>3919.2</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
-        <v>5144</v>
+        <v>5267</v>
       </c>
       <c r="B99" s="3">
         <v>46092</v>
       </c>
       <c r="C99" s="2">
-        <v>0.71577000000000002</v>
+        <v>0.67017000000000004</v>
       </c>
       <c r="D99" s="4">
-        <v>4375.8</v>
+        <v>3801.9</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
-        <v>5145</v>
+        <v>5268</v>
       </c>
       <c r="B100" s="3">
         <v>46092</v>
       </c>
       <c r="C100" s="2">
-        <v>0.71577000000000002</v>
+        <v>0.67017000000000004</v>
       </c>
       <c r="D100" s="4">
-        <v>4375.8</v>
+        <v>4011</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
-        <v>5009</v>
+        <v>5282</v>
       </c>
       <c r="B101" s="3">
         <v>46092</v>
@@ -1870,194 +1868,194 @@
         <v>0.67017000000000004</v>
       </c>
       <c r="D101" s="4">
-        <v>3589.8</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
-        <v>5120</v>
+        <v>5390</v>
       </c>
       <c r="B102" s="3">
         <v>46092</v>
       </c>
       <c r="C102" s="2">
-        <v>0.67017000000000004</v>
-      </c>
-      <c r="D102" s="4">
-        <v>4101.45</v>
+        <v>0.67018999999999995</v>
+      </c>
+      <c r="D102" s="2">
+        <v>178.35</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
-        <v>5121</v>
+        <v>5219</v>
       </c>
       <c r="B103" s="3">
-        <v>46092</v>
+        <v>46100</v>
       </c>
       <c r="C103" s="2">
         <v>0.67017000000000004</v>
       </c>
       <c r="D103" s="4">
-        <v>4105.5</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
-        <v>5122</v>
+        <v>5220</v>
       </c>
       <c r="B104" s="3">
-        <v>46092</v>
+        <v>46100</v>
       </c>
       <c r="C104" s="2">
         <v>0.67017000000000004</v>
       </c>
       <c r="D104" s="4">
-        <v>4302.1400000000003</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
-        <v>5236</v>
+        <v>5221</v>
       </c>
       <c r="B105" s="3">
-        <v>46092</v>
+        <v>46100</v>
       </c>
       <c r="C105" s="2">
         <v>0.67017000000000004</v>
       </c>
       <c r="D105" s="4">
-        <v>4066.2</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
-        <v>5262</v>
+        <v>5289</v>
       </c>
       <c r="B106" s="3">
-        <v>46092</v>
+        <v>46100</v>
       </c>
       <c r="C106" s="2">
-        <v>0.67017000000000004</v>
+        <v>0.70416999999999996</v>
       </c>
       <c r="D106" s="4">
-        <v>3801.9</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
-        <v>5263</v>
+        <v>5290</v>
       </c>
       <c r="B107" s="3">
-        <v>46092</v>
+        <v>46100</v>
       </c>
       <c r="C107" s="2">
-        <v>0.67017000000000004</v>
+        <v>0.70416999999999996</v>
       </c>
       <c r="D107" s="4">
-        <v>3801.9</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
-        <v>5264</v>
+        <v>5333</v>
       </c>
       <c r="B108" s="3">
-        <v>46092</v>
+        <v>46100</v>
       </c>
       <c r="C108" s="2">
-        <v>0.67017000000000004</v>
+        <v>0.70416999999999996</v>
       </c>
       <c r="D108" s="4">
-        <v>3974.4</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
-        <v>5265</v>
+        <v>5336</v>
       </c>
       <c r="B109" s="3">
-        <v>46092</v>
+        <v>46100</v>
       </c>
       <c r="C109" s="2">
-        <v>0.67017000000000004</v>
+        <v>0.70416999999999996</v>
       </c>
       <c r="D109" s="4">
-        <v>3801.9</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
-        <v>5266</v>
+        <v>5190</v>
       </c>
       <c r="B110" s="3">
-        <v>46092</v>
+        <v>46100</v>
       </c>
       <c r="C110" s="2">
-        <v>0.69084999999999996</v>
+        <v>0.70416999999999996</v>
       </c>
       <c r="D110" s="4">
-        <v>3919.2</v>
+        <v>5175</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
-        <v>5267</v>
+        <v>5245</v>
       </c>
       <c r="B111" s="3">
-        <v>46092</v>
+        <v>46100</v>
       </c>
       <c r="C111" s="2">
-        <v>0.67017000000000004</v>
+        <v>0.70416999999999996</v>
       </c>
       <c r="D111" s="4">
-        <v>3801.9</v>
+        <v>4143.4799999999996</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
-        <v>5268</v>
+        <v>5247</v>
       </c>
       <c r="B112" s="3">
-        <v>46092</v>
+        <v>46100</v>
       </c>
       <c r="C112" s="2">
-        <v>0.67017000000000004</v>
+        <v>0.70416999999999996</v>
       </c>
       <c r="D112" s="4">
-        <v>4011</v>
+        <v>4276.74</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
-        <v>5282</v>
+        <v>5040</v>
       </c>
       <c r="B113" s="3">
-        <v>46092</v>
+        <v>46100</v>
       </c>
       <c r="C113" s="2">
         <v>0.67017000000000004</v>
       </c>
       <c r="D113" s="4">
-        <v>4248</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
-        <v>5390</v>
+        <v>5297</v>
       </c>
       <c r="B114" s="3">
-        <v>46092</v>
+        <v>46100</v>
       </c>
       <c r="C114" s="2">
-        <v>0.67018999999999995</v>
-      </c>
-      <c r="D114" s="2">
-        <v>178.35</v>
+        <v>0.67017000000000004</v>
+      </c>
+      <c r="D114" s="4">
+        <v>4158</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
-        <v>5219</v>
+        <v>5298</v>
       </c>
       <c r="B115" s="3">
         <v>46100</v>
@@ -2066,12 +2064,12 @@
         <v>0.67017000000000004</v>
       </c>
       <c r="D115" s="4">
-        <v>3801.6</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
-        <v>5220</v>
+        <v>5299</v>
       </c>
       <c r="B116" s="3">
         <v>46100</v>
@@ -2080,130 +2078,130 @@
         <v>0.67017000000000004</v>
       </c>
       <c r="D116" s="4">
-        <v>3801.6</v>
+        <v>3801.9</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
-        <v>5221</v>
+        <v>5300</v>
       </c>
       <c r="B117" s="3">
         <v>46100</v>
       </c>
       <c r="C117" s="2">
-        <v>0.67017000000000004</v>
+        <v>0.67020999999999997</v>
       </c>
       <c r="D117" s="4">
-        <v>3801.6</v>
+        <v>3974.4</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
-        <v>5289</v>
+        <v>5302</v>
       </c>
       <c r="B118" s="3">
         <v>46100</v>
       </c>
       <c r="C118" s="2">
-        <v>0.70416999999999996</v>
+        <v>0.67017000000000004</v>
       </c>
       <c r="D118" s="4">
-        <v>3801.6</v>
+        <v>4146</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
-        <v>5290</v>
+        <v>5309</v>
       </c>
       <c r="B119" s="3">
         <v>46100</v>
       </c>
       <c r="C119" s="2">
-        <v>0.70416999999999996</v>
+        <v>0.67017000000000004</v>
       </c>
       <c r="D119" s="4">
-        <v>3801.6</v>
+        <v>4114.95</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A120" s="2">
-        <v>5333</v>
+        <v>5310</v>
       </c>
       <c r="B120" s="3">
         <v>46100</v>
       </c>
       <c r="C120" s="2">
-        <v>0.70416999999999996</v>
+        <v>0.67017000000000004</v>
       </c>
       <c r="D120" s="4">
-        <v>3801.6</v>
+        <v>3832.95</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
-        <v>5336</v>
+        <v>5295</v>
       </c>
       <c r="B121" s="3">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="C121" s="2">
-        <v>0.70416999999999996</v>
+        <v>0.69108000000000003</v>
       </c>
       <c r="D121" s="4">
-        <v>3801.6</v>
+        <v>2537.4499999999998</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A122" s="2">
-        <v>5190</v>
+        <v>5344</v>
       </c>
       <c r="B122" s="3">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="C122" s="2">
-        <v>0.70416999999999996</v>
+        <v>0.69106999999999996</v>
       </c>
       <c r="D122" s="4">
-        <v>5175</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A123" s="2">
-        <v>5245</v>
+        <v>5349</v>
       </c>
       <c r="B123" s="3">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="C123" s="2">
-        <v>0.70416999999999996</v>
+        <v>0.69108000000000003</v>
       </c>
       <c r="D123" s="4">
-        <v>4143.4799999999996</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A124" s="2">
-        <v>5247</v>
+        <v>5373</v>
       </c>
       <c r="B124" s="3">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="C124" s="2">
-        <v>0.70416999999999996</v>
+        <v>0.69108000000000003</v>
       </c>
       <c r="D124" s="4">
-        <v>4276.74</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" s="2">
-        <v>5040</v>
+        <v>5222</v>
       </c>
       <c r="B125" s="3">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="C125" s="2">
-        <v>0.67017000000000004</v>
+        <v>0.69366000000000005</v>
       </c>
       <c r="D125" s="4">
         <v>3801.6</v>
@@ -2216,119 +2214,119 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A126" s="2">
-        <v>5297</v>
+        <v>5223</v>
       </c>
       <c r="B126" s="3">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="C126" s="2">
-        <v>0.67017000000000004</v>
+        <v>0.69366000000000005</v>
       </c>
       <c r="D126" s="4">
-        <v>4158</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A127" s="2">
-        <v>5298</v>
+        <v>5260</v>
       </c>
       <c r="B127" s="3">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="C127" s="2">
-        <v>0.67017000000000004</v>
+        <v>0.69366000000000005</v>
       </c>
       <c r="D127" s="4">
-        <v>4293</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128" s="2">
-        <v>5299</v>
+        <v>5143</v>
       </c>
       <c r="B128" s="3">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="C128" s="2">
-        <v>0.67017000000000004</v>
+        <v>0.69106999999999996</v>
       </c>
       <c r="D128" s="4">
-        <v>3801.9</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" s="2">
-        <v>5300</v>
+        <v>5146</v>
       </c>
       <c r="B129" s="3">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="C129" s="2">
-        <v>0.67020999999999997</v>
+        <v>0.69106999999999996</v>
       </c>
       <c r="D129" s="4">
-        <v>3974.4</v>
+        <v>8751.6</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" s="2">
-        <v>5302</v>
+        <v>5147</v>
       </c>
       <c r="B130" s="3">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="C130" s="2">
-        <v>0.67017000000000004</v>
+        <v>0.69106999999999996</v>
       </c>
       <c r="D130" s="4">
-        <v>4146</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" s="2">
-        <v>5309</v>
+        <v>5148</v>
       </c>
       <c r="B131" s="3">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="C131" s="2">
-        <v>0.67017000000000004</v>
+        <v>0.69108000000000003</v>
       </c>
       <c r="D131" s="4">
-        <v>4114.95</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" s="2">
-        <v>5310</v>
+        <v>5149</v>
       </c>
       <c r="B132" s="3">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="C132" s="2">
-        <v>0.67017000000000004</v>
+        <v>0.69108000000000003</v>
       </c>
       <c r="D132" s="4">
-        <v>3832.95</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" s="2">
-        <v>5344</v>
+        <v>5150</v>
       </c>
       <c r="B133" s="3">
         <v>46107</v>
       </c>
       <c r="C133" s="2">
-        <v>0.69106999999999996</v>
+        <v>0.69108000000000003</v>
       </c>
       <c r="D133" s="4">
-        <v>3801.6</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" s="2">
-        <v>5349</v>
+        <v>5151</v>
       </c>
       <c r="B134" s="3">
         <v>46107</v>
@@ -2337,12 +2335,12 @@
         <v>0.69108000000000003</v>
       </c>
       <c r="D134" s="4">
-        <v>3801.6</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135" s="2">
-        <v>5373</v>
+        <v>5152</v>
       </c>
       <c r="B135" s="3">
         <v>46107</v>
@@ -2351,46 +2349,46 @@
         <v>0.69108000000000003</v>
       </c>
       <c r="D135" s="4">
-        <v>3801.6</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136" s="2">
-        <v>5222</v>
+        <v>5168</v>
       </c>
       <c r="B136" s="3">
         <v>46107</v>
       </c>
       <c r="C136" s="2">
-        <v>0.69366000000000005</v>
+        <v>0.69108000000000003</v>
       </c>
       <c r="D136" s="4">
-        <v>3801.6</v>
+        <v>4375.8</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137" s="2">
-        <v>5223</v>
+        <v>5293</v>
       </c>
       <c r="B137" s="3">
         <v>46107</v>
       </c>
       <c r="C137" s="2">
-        <v>0.69366000000000005</v>
+        <v>0.66090000000000004</v>
       </c>
       <c r="D137" s="4">
-        <v>3801.6</v>
+        <v>5354.4</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" s="2">
-        <v>5260</v>
+        <v>5039</v>
       </c>
       <c r="B138" s="3">
         <v>46107</v>
       </c>
       <c r="C138" s="2">
-        <v>0.69366000000000005</v>
+        <v>0.69374000000000002</v>
       </c>
       <c r="D138" s="4">
         <v>3801.6</v>
@@ -2398,147 +2396,147 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" s="2">
-        <v>5143</v>
+        <v>5301</v>
       </c>
       <c r="B139" s="3">
         <v>46107</v>
       </c>
       <c r="C139" s="2">
-        <v>0.69106999999999996</v>
+        <v>0.69374000000000002</v>
       </c>
       <c r="D139" s="4">
-        <v>4375.8</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" s="2">
-        <v>5146</v>
+        <v>5304</v>
       </c>
       <c r="B140" s="3">
         <v>46107</v>
       </c>
       <c r="C140" s="2">
-        <v>0.69106999999999996</v>
+        <v>0.69374000000000002</v>
       </c>
       <c r="D140" s="4">
-        <v>8751.6</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" s="2">
-        <v>5147</v>
+        <v>5305</v>
       </c>
       <c r="B141" s="3">
         <v>46107</v>
       </c>
       <c r="C141" s="2">
-        <v>0.69106999999999996</v>
+        <v>0.69374000000000002</v>
       </c>
       <c r="D141" s="4">
-        <v>4375.8</v>
+        <v>4114.95</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" s="2">
-        <v>5148</v>
+        <v>5306</v>
       </c>
       <c r="B142" s="3">
         <v>46107</v>
       </c>
       <c r="C142" s="2">
-        <v>0.69108000000000003</v>
+        <v>0.69374000000000002</v>
       </c>
       <c r="D142" s="4">
-        <v>4375.8</v>
+        <v>3801.9</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" s="2">
-        <v>5149</v>
+        <v>5338</v>
       </c>
       <c r="B143" s="3">
         <v>46107</v>
       </c>
       <c r="C143" s="2">
-        <v>0.69108000000000003</v>
+        <v>0.69374000000000002</v>
       </c>
       <c r="D143" s="4">
-        <v>4375.8</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" s="2">
-        <v>5150</v>
+        <v>5339</v>
       </c>
       <c r="B144" s="3">
         <v>46107</v>
       </c>
       <c r="C144" s="2">
-        <v>0.69108000000000003</v>
+        <v>0.69374000000000002</v>
       </c>
       <c r="D144" s="4">
-        <v>4375.8</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A145" s="2">
-        <v>5151</v>
+        <v>5340</v>
       </c>
       <c r="B145" s="3">
         <v>46107</v>
       </c>
       <c r="C145" s="2">
-        <v>0.69108000000000003</v>
+        <v>0.69374000000000002</v>
       </c>
       <c r="D145" s="4">
-        <v>4375.8</v>
+        <v>4252.5</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146" s="2">
-        <v>5152</v>
+        <v>5341</v>
       </c>
       <c r="B146" s="3">
         <v>46107</v>
       </c>
       <c r="C146" s="2">
-        <v>0.69108000000000003</v>
+        <v>0.69374000000000002</v>
       </c>
       <c r="D146" s="4">
-        <v>4375.8</v>
+        <v>4401</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147" s="2">
-        <v>5168</v>
+        <v>5345</v>
       </c>
       <c r="B147" s="3">
         <v>46107</v>
       </c>
       <c r="C147" s="2">
-        <v>0.69108000000000003</v>
+        <v>0.69374000000000002</v>
       </c>
       <c r="D147" s="4">
-        <v>4375.8</v>
+        <v>3979.95</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A148" s="2">
-        <v>5293</v>
+        <v>5346</v>
       </c>
       <c r="B148" s="3">
         <v>46107</v>
       </c>
       <c r="C148" s="2">
-        <v>0.66090000000000004</v>
+        <v>0.69374000000000002</v>
       </c>
       <c r="D148" s="4">
-        <v>5354.4</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A149" s="2">
-        <v>5039</v>
+        <v>5347</v>
       </c>
       <c r="B149" s="3">
         <v>46107</v>
@@ -2547,12 +2545,12 @@
         <v>0.69374000000000002</v>
       </c>
       <c r="D149" s="4">
-        <v>3801.6</v>
+        <v>3832.8</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A150" s="2">
-        <v>5301</v>
+        <v>5350</v>
       </c>
       <c r="B150" s="3">
         <v>46107</v>
@@ -2561,12 +2559,12 @@
         <v>0.69374000000000002</v>
       </c>
       <c r="D150" s="4">
-        <v>3979.95</v>
+        <v>3824.35</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A151" s="2">
-        <v>5304</v>
+        <v>5351</v>
       </c>
       <c r="B151" s="3">
         <v>46107</v>
@@ -2575,12 +2573,12 @@
         <v>0.69374000000000002</v>
       </c>
       <c r="D151" s="4">
-        <v>4158</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A152" s="2">
-        <v>5305</v>
+        <v>5352</v>
       </c>
       <c r="B152" s="3">
         <v>46107</v>
@@ -2589,162 +2587,82 @@
         <v>0.69374000000000002</v>
       </c>
       <c r="D152" s="4">
-        <v>4114.95</v>
+        <v>3801.9</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A153" s="2">
-        <v>5306</v>
+        <v>4855</v>
       </c>
       <c r="B153" s="3">
-        <v>46107</v>
+        <v>46022</v>
       </c>
       <c r="C153" s="2">
-        <v>0.69374000000000002</v>
+        <v>0.65081</v>
       </c>
       <c r="D153" s="4">
-        <v>3801.9</v>
+        <v>14586</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A154" s="2">
-        <v>5338</v>
-      </c>
-      <c r="B154" s="3">
-        <v>46107</v>
-      </c>
-      <c r="C154" s="2">
-        <v>0.69374000000000002</v>
-      </c>
-      <c r="D154" s="4">
-        <v>4158</v>
-      </c>
+      <c r="A154" s="2"/>
+      <c r="B154" s="3"/>
+      <c r="C154" s="2"/>
+      <c r="D154" s="4"/>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A155" s="2">
-        <v>5339</v>
-      </c>
-      <c r="B155" s="3">
-        <v>46107</v>
-      </c>
-      <c r="C155" s="2">
-        <v>0.69374000000000002</v>
-      </c>
-      <c r="D155" s="4">
-        <v>3979.95</v>
-      </c>
+      <c r="A155" s="2"/>
+      <c r="B155" s="3"/>
+      <c r="C155" s="2"/>
+      <c r="D155" s="4"/>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A156" s="2">
-        <v>5340</v>
-      </c>
-      <c r="B156" s="3">
-        <v>46107</v>
-      </c>
-      <c r="C156" s="2">
-        <v>0.69374000000000002</v>
-      </c>
-      <c r="D156" s="4">
-        <v>4252.5</v>
-      </c>
+      <c r="A156" s="2"/>
+      <c r="B156" s="3"/>
+      <c r="C156" s="2"/>
+      <c r="D156" s="4"/>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A157" s="2">
-        <v>5341</v>
-      </c>
-      <c r="B157" s="3">
-        <v>46107</v>
-      </c>
-      <c r="C157" s="2">
-        <v>0.69374000000000002</v>
-      </c>
-      <c r="D157" s="4">
-        <v>4401</v>
-      </c>
+      <c r="A157" s="2"/>
+      <c r="B157" s="3"/>
+      <c r="C157" s="2"/>
+      <c r="D157" s="4"/>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A158" s="2">
-        <v>5345</v>
-      </c>
-      <c r="B158" s="3">
-        <v>46107</v>
-      </c>
-      <c r="C158" s="2">
-        <v>0.69374000000000002</v>
-      </c>
-      <c r="D158" s="4">
-        <v>3979.95</v>
-      </c>
+      <c r="A158" s="2"/>
+      <c r="B158" s="3"/>
+      <c r="C158" s="2"/>
+      <c r="D158" s="4"/>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A159" s="2">
-        <v>5346</v>
-      </c>
-      <c r="B159" s="3">
-        <v>46107</v>
-      </c>
-      <c r="C159" s="2">
-        <v>0.69374000000000002</v>
-      </c>
-      <c r="D159" s="4">
-        <v>4158</v>
-      </c>
+      <c r="A159" s="2"/>
+      <c r="B159" s="3"/>
+      <c r="C159" s="2"/>
+      <c r="D159" s="4"/>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A160" s="2">
-        <v>5347</v>
-      </c>
-      <c r="B160" s="3">
-        <v>46107</v>
-      </c>
-      <c r="C160" s="2">
-        <v>0.69374000000000002</v>
-      </c>
-      <c r="D160" s="4">
-        <v>3832.8</v>
-      </c>
+      <c r="A160" s="2"/>
+      <c r="B160" s="3"/>
+      <c r="C160" s="2"/>
+      <c r="D160" s="4"/>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A161" s="2">
-        <v>5350</v>
-      </c>
-      <c r="B161" s="3">
-        <v>46107</v>
-      </c>
-      <c r="C161" s="2">
-        <v>0.69374000000000002</v>
-      </c>
-      <c r="D161" s="4">
-        <v>3824.35</v>
-      </c>
+      <c r="A161" s="2"/>
+      <c r="B161" s="3"/>
+      <c r="C161" s="2"/>
+      <c r="D161" s="4"/>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A162" s="2">
-        <v>5351</v>
-      </c>
-      <c r="B162" s="3">
-        <v>46107</v>
-      </c>
-      <c r="C162" s="2">
-        <v>0.69374000000000002</v>
-      </c>
-      <c r="D162" s="4">
-        <v>4293</v>
-      </c>
+      <c r="A162" s="2"/>
+      <c r="B162" s="3"/>
+      <c r="C162" s="2"/>
+      <c r="D162" s="4"/>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A163" s="2">
-        <v>5352</v>
-      </c>
-      <c r="B163" s="3">
-        <v>46107</v>
-      </c>
-      <c r="C163" s="2">
-        <v>0.69374000000000002</v>
-      </c>
-      <c r="D163" s="4">
-        <v>3801.9</v>
-      </c>
+      <c r="A163" s="2"/>
+      <c r="B163" s="3"/>
+      <c r="C163" s="2"/>
+      <c r="D163" s="4"/>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A164" s="2"/>
